--- a/塗料メーカー_ヒアリング候補リスト.xlsx
+++ b/塗料メーカー_ヒアリング候補リスト.xlsx
@@ -13,7 +13,7 @@
     <sheet name="③カバレッジ確認" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'①候補リスト'!$A$4:$Z$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'①候補リスト'!$A$4:$Z$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -72,6 +72,18 @@
     <font>
       <name val="Yu Gothic"/>
       <b val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -139,12 +151,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6DCE4"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -154,12 +166,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EDEDED"/>
+        <fgColor rgb="00E4DFEC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00B4C7E7"/>
+        <fgColor rgb="00FFD966"/>
       </patternFill>
     </fill>
     <fill>
@@ -321,10 +333,13 @@
     <xf numFmtId="0" fontId="7" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -333,16 +348,13 @@
     <xf numFmtId="0" fontId="4" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -354,7 +366,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -378,49 +390,49 @@
     <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -788,7 +800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D22"/>
+  <dimension ref="B2:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -800,14 +812,14 @@
     <row r="2" ht="30" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>塗料メーカー ヒアリング候補リスト (網羅型)</t>
+          <t>塗料メーカー ヒアリング候補リスト (網羅型・50社)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>塗料製造フロー &amp; IN/OUT (別Excel) の記述を、塗料メーカー他へのヒアリングで検証するための候補企業リスト</t>
+          <t>塗料製造フロー &amp; IN/OUT (別Excel) の記述を、塗料メーカーへのヒアリングで検証するための候補企業リスト (業界団体・装置メーカーは含めず塗料メーカーのみ)</t>
         </is>
       </c>
     </row>
@@ -823,194 +835,235 @@
     <row r="6" ht="28" customHeight="1">
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>アプローチ</t>
+          <t>対象</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>A. 網羅型 (約30社)</t>
+          <t>塗料メーカーのみ 50社</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>5製品タイプ × 規模 × セグメントを網羅</t>
+          <t>業界団体・装置メーカーは除外</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>ヒアリング立場</t>
+          <t>アプローチ</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>業界関係者</t>
+          <t>A. 網羅型</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>取引先・関連事業者として既存ネットワーク活用</t>
+          <t>11カテゴリで 5製品タイプ × 規模 × セグメントを網羅</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>成果物</t>
+          <t>ヒアリング立場</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Plan-1: リスト Excel のみ</t>
+          <t>業界関係者</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>ヒアリング項目は別途自社で設計</t>
+          <t>取引先・関連事業者として既存ネットワーク活用</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="B9" s="6" t="inlineStr">
         <is>
+          <t>成果物</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Plan-1: リスト Excel のみ</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>ヒアリング項目は別途自社で設計</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="B10" s="6" t="inlineStr">
+        <is>
           <t>検証深さ</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>定性 + 定量</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>フロー/項目の正誤 + kWh/t・歩留・廃棄量の校正</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="9" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>フロー/項目正誤 + kWh/t・歩留・廃棄量校正</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>シート構成</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="35" customHeight="1">
-      <c r="B12" s="10" t="inlineStr">
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="38" customHeight="1">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>ヒアリング先 候補リスト</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>30社の候補。No./カテゴリ/企業名/規模/セグメント/製品タイプ適合/工場/連絡/優先度スコア/アプローチ etc.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="35" customHeight="1">
-      <c r="B13" s="10" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>ヒアリング先 候補リスト (50社)</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>11カテゴリ × 26列。基本情報・規模・5製品タイプ適合・工場・連絡・ヒアリング推奨工程・優先度スコア・アプローチ・既存関係 etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="38" customHeight="1">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>優先度スコアリング基準</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>100点満点の配点設計。カバレッジ・規模・公開度・アクセス・専門特化価値</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="35" customHeight="1">
-      <c r="B14" s="10" t="inlineStr">
+    <row r="15" ht="38" customHeight="1">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>③</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>カテゴリ別カバレッジ確認</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>5製品タイプの ◎/○/△/- 数を集計し、漏れがないか確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>リストの注意事項</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="5" t="n"/>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>・本リストの企業情報 (売上・従業員数・セグメント・適合製品タイプ) は 公開情報ベースの初期案。</t>
-        </is>
-      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>5製品タイプ × カテゴリ別の ◎/○ 保有社数を集計し、漏れ・偏りを確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>リスト利用時の重要注意事項</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="5" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>・実ヒアリング前に貴社の取引履歴・関係性で 「既存関係」「優先度スコア」「アプローチルート」 列を上書き校正してください。</t>
+          <t>・本リストの企業情報 (売上・従業員数・セグメント・適合製品タイプ) は 公開情報ベースの初期案 (推定値を含む)。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>・優先度スコアは 100 点満点。シート②に配点基準を記載。</t>
+          <t>・実ヒアリング前に貴社の取引履歴・関係性で 「既存関係」「優先度スコア」「アプローチルート」 列を必ず上書き校正してください。</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>・売上・従業員等は概算 (推定含む)。最新の有報・IR資料で適宜上書きしてください。</t>
+          <t>・「公開情報充実度」列に "(要確認)" がある企業は、基本情報の出典再確認が必要です。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>・◎=主力 / ○=取扱 / △=限定 / -=無し  (5製品タイプ別)。</t>
+          <t>・優先度スコアは 100 点満点。シート②に配点基準を記載。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="B22" s="7" t="inlineStr">
         <is>
+          <t>・売上・従業員等は推定含む。最新の有報・IR資料・帝国データバンク等で適宜上書きを推奨。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>・◎=主力 / ○=取扱 / △=限定 / -=無し  (5製品タイプ別)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="B24" s="7" t="inlineStr">
+        <is>
           <t>・「ヒアリング推奨工程」は別 Excel 「塗料メーカー_製造フローINOUT.xlsx」の工程番号と連動。</t>
         </is>
       </c>
     </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>・日ペグループ・関ペグループ子会社は、独立にアプローチせず親会社経由を推奨。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>・外資系日本法人は本社方針・グローバル機密の制約が強い。日本拠点での製造規模を要確認。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B11:D11"/>
+  <mergeCells count="14">
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B23:D23"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B24:D24"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B16:D16"/>
     <mergeCell ref="B20:D20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1023,28 +1076,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z32"/>
+  <dimension ref="A1:Z54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
     <col width="8" customWidth="1" min="13" max="13"/>
     <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="32" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="30" customWidth="1" min="19" max="19"/>
+    <col width="32" customWidth="1" min="19" max="19"/>
     <col width="10" customWidth="1" min="20" max="20"/>
     <col width="24" customWidth="1" min="21" max="21"/>
     <col width="22" customWidth="1" min="22" max="22"/>
@@ -1057,14 +1110,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>① 塗料メーカー ヒアリング先 候補リスト (網羅型 30社)</t>
+          <t>① 塗料メーカー ヒアリング先 候補リスト (網羅型 50社)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>◎=主力ライン / ○=取扱あり / △=限定的 / -=取扱なし  ｜  優先度スコアの基準はシート②を参照  ｜  数値・規模は推定含む</t>
+          <t>◎=主力ライン / ○=取扱あり / △=限定的 / -=取扱なし  ｜  優先度スコアの基準はシート②を参照  ｜  数値・規模は推定含む・要校正</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1253,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="65" customHeight="1">
+    <row r="5" ht="68" customHeight="1">
       <c r="A5" s="13" t="n">
         <v>1</v>
       </c>
@@ -1226,7 +1279,7 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>約1.5兆円 (2024)</t>
+          <t>約1.5兆円(2024)</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -1236,7 +1289,7 @@
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>汎用塗料(建築含む)・自動車・工業・船舶</t>
+          <t>汎用・自動車・工業・船舶 (世界4位級)</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -1276,22 +1329,22 @@
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
-          <t>IR部 / コーポレートコミュニケーション</t>
+          <t>IR部</t>
         </is>
       </c>
       <c r="Q5" s="14" t="inlineStr">
         <is>
-          <t>高 (統合報告書・サステナ報告書あり)</t>
+          <t>高 (統合報告書・サステナ報告書)</t>
         </is>
       </c>
       <c r="R5" s="8" t="inlineStr">
         <is>
-          <t>①〜⑨ 全工程 + 並行洗浄・排ガス処理</t>
+          <t>①〜⑨全工程 + 並行洗浄・排ガス処理</t>
         </is>
       </c>
       <c r="S5" s="8" t="inlineStr">
         <is>
-          <t>kWh/t・歩留・廃シンナー量・VOC排出・Scope1/2/3</t>
+          <t>kWh/t・歩留・廃シンナー量・VOC・Scope1/2/3</t>
         </is>
       </c>
       <c r="T5" s="18" t="n">
@@ -1299,28 +1352,28 @@
       </c>
       <c r="U5" s="8" t="inlineStr">
         <is>
-          <t>IR経由 → 技術本部 / R&amp;Dセンター</t>
+          <t>IR経由 → 技術本部/R&amp;Dセンター</t>
         </is>
       </c>
       <c r="V5" s="8" t="inlineStr">
         <is>
-          <t>業界団体経由 (JPMA)、共同セミナー</t>
+          <t>業界団体・共同セミナー</t>
         </is>
       </c>
       <c r="W5" s="8" t="inlineStr">
         <is>
-          <t>上場大手のためIR開示と機密情報の線引きが厳格。NDA必須。</t>
+          <t>上場大手のため機密の線引き厳格・NDA必須</t>
         </is>
       </c>
       <c r="X5" s="14" t="inlineStr"/>
       <c r="Y5" s="7" t="inlineStr"/>
       <c r="Z5" s="8" t="inlineStr">
         <is>
-          <t>M&amp;A 主導・海外拠点も検証視点に</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
+          <t>M&amp;A 主導、海外拠点も検証視点に</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="68" customHeight="1">
       <c r="A6" s="13" t="n">
         <v>2</v>
       </c>
@@ -1346,7 +1399,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>約5,500億円 (2024)</t>
+          <t>約5,500億円(2024)</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -1386,7 +1439,7 @@
       </c>
       <c r="N6" s="8" t="inlineStr">
         <is>
-          <t>大阪・滋賀・茨城 (姉ヶ崎) ほか</t>
+          <t>大阪・滋賀・茨城(姉ヶ崎) ほか</t>
         </is>
       </c>
       <c r="O6" s="17" t="inlineStr">
@@ -1396,22 +1449,22 @@
       </c>
       <c r="P6" s="7" t="inlineStr">
         <is>
-          <t>IR部 / 広報部</t>
+          <t>IR部/広報部</t>
         </is>
       </c>
       <c r="Q6" s="14" t="inlineStr">
         <is>
-          <t>高 (統合報告書・ESG資料あり)</t>
+          <t>高 (統合報告書・ESG資料)</t>
         </is>
       </c>
       <c r="R6" s="8" t="inlineStr">
         <is>
-          <t>①〜⑨ + 電着塗料・粉体塗料の特殊工程</t>
+          <t>①〜⑨ + 電着・粉体の特殊工程</t>
         </is>
       </c>
       <c r="S6" s="8" t="inlineStr">
         <is>
-          <t>電着塗料のMEQ・UF回収率、粉体歩留、CCM導入率</t>
+          <t>電着MEQ/UF回収率、粉体歩留、CCM導入率</t>
         </is>
       </c>
       <c r="T6" s="18" t="n">
@@ -1424,12 +1477,12 @@
       </c>
       <c r="V6" s="8" t="inlineStr">
         <is>
-          <t>業界団体・学会経由、装置メーカー紹介</t>
+          <t>業界団体・装置メーカー紹介</t>
         </is>
       </c>
       <c r="W6" s="8" t="inlineStr">
         <is>
-          <t>海外子会社(印・南ア)情報も範囲に入れるか検討</t>
+          <t>海外子会社(印・南ア)情報の範囲を要相談</t>
         </is>
       </c>
       <c r="X6" s="14" t="inlineStr"/>
@@ -1440,7 +1493,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="65" customHeight="1">
+    <row r="7" ht="68" customHeight="1">
       <c r="A7" s="19" t="n">
         <v>3</v>
       </c>
@@ -1451,116 +1504,116 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>エスケー化研 (SK化研)</t>
+          <t>大日本塗料 (DNT)</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>大阪府茨木市</t>
+          <t>東京都品川区</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>非上場 (独立系)</t>
+          <t>東証スタンダード</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>約1,800億円 (推定)</t>
+          <t>約750億円(2024)</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>約1,400人</t>
+          <t>約1,800人(連結)</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>建築用塗料 国内首位</t>
-        </is>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
+          <t>防食・構造物・蛍光塗料・粉体</t>
+        </is>
+      </c>
+      <c r="I7" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="J7" s="16" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J7" s="15" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="K7" s="20" t="inlineStr">
+      <c r="K7" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L7" s="20" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="L7" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M7" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="M7" s="20" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="N7" s="8" t="inlineStr">
         <is>
-          <t>大阪・茨木 ほか全国</t>
+          <t>大阪・東京・愛知(小牧)</t>
         </is>
       </c>
       <c r="O7" s="17" t="inlineStr">
         <is>
-          <t>https://www.sk-kaken.co.jp/</t>
+          <t>https://www.dnt.co.jp/</t>
         </is>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
-          <t>本社・各支店</t>
+          <t>IR室</t>
         </is>
       </c>
       <c r="Q7" s="14" t="inlineStr">
         <is>
-          <t>中 (非上場のためIR限定的)</t>
+          <t>中〜高 (有報・統合報告書)</t>
         </is>
       </c>
       <c r="R7" s="8" t="inlineStr">
         <is>
-          <t>水性塗料 ②③④調色 + ⑥ろ過 + 設備洗浄</t>
+          <t>厚膜防食の③④調色・⑦検査・⑧充填</t>
         </is>
       </c>
       <c r="S7" s="8" t="inlineStr">
         <is>
-          <t>水性ベース塗料の歩留、CCM普及率、防腐剤添加量</t>
-        </is>
-      </c>
-      <c r="T7" s="18" t="n">
-        <v>88</v>
+          <t>厚塗り防食の固形分・粘度、ジンクリッチプライマー</t>
+        </is>
+      </c>
+      <c r="T7" s="21" t="n">
+        <v>82</v>
       </c>
       <c r="U7" s="8" t="inlineStr">
         <is>
-          <t>技術部門 / 営業窓口</t>
+          <t>営業・技術 / IR</t>
         </is>
       </c>
       <c r="V7" s="8" t="inlineStr">
         <is>
-          <t>業界団体 (JPMA) 経由が確実</t>
+          <t>インフラ顧客経由</t>
         </is>
       </c>
       <c r="W7" s="8" t="inlineStr">
         <is>
-          <t>非上場のため定量データの開示範囲が要相談</t>
+          <t>構造物向け特殊配合は機密性高</t>
         </is>
       </c>
       <c r="X7" s="14" t="inlineStr"/>
       <c r="Y7" s="7" t="inlineStr"/>
       <c r="Z7" s="8" t="inlineStr">
         <is>
-          <t>建築用水性塗料のリファレンスとして最重要</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
+          <t>ジンクリッチ・蛍光塗料のニッチ例</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="68" customHeight="1">
       <c r="A8" s="19" t="n">
         <v>4</v>
       </c>
@@ -1571,32 +1624,32 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>大日本塗料 (DNT)</t>
+          <t>中国塗料 (CMP)</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>東京都品川区</t>
+          <t>東京都千代田区</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>東証スタンダード</t>
+          <t>東証プライム</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>約750億円 (2024)</t>
+          <t>約1,100億円(2024)</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>約1,800人(連結)</t>
+          <t>約2,500人(連結)</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>防食・構造物・蛍光塗料・粉体</t>
+          <t>船舶用塗料(世界4強)・工業防食</t>
         </is>
       </c>
       <c r="I8" s="15" t="inlineStr">
@@ -1609,78 +1662,78 @@
           <t>○</t>
         </is>
       </c>
-      <c r="K8" s="16" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="L8" s="20" t="inlineStr">
+      <c r="K8" s="20" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="M8" s="20" t="inlineStr">
-        <is>
-          <t>△</t>
+      <c r="L8" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M8" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="N8" s="8" t="inlineStr">
         <is>
-          <t>大阪・東京・愛知 (小牧) ほか</t>
+          <t>兵庫・愛媛 ほか</t>
         </is>
       </c>
       <c r="O8" s="17" t="inlineStr">
         <is>
-          <t>https://www.dnt.co.jp/</t>
+          <t>https://www.cmp.co.jp/</t>
         </is>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
-          <t>IR室</t>
+          <t>IR部</t>
         </is>
       </c>
       <c r="Q8" s="14" t="inlineStr">
         <is>
-          <t>中〜高 (有報・統合報告書あり)</t>
+          <t>高</t>
         </is>
       </c>
       <c r="R8" s="8" t="inlineStr">
         <is>
-          <t>厚膜防食の③④調色・⑦検査・⑧充填</t>
+          <t>船舶塗料の③④(低摩擦・防汚機能の分散)</t>
         </is>
       </c>
       <c r="S8" s="8" t="inlineStr">
         <is>
-          <t>厚塗り防食の固形分・粘度管理、ジンクリッチプライマー充填</t>
-        </is>
-      </c>
-      <c r="T8" s="21" t="n">
-        <v>82</v>
+          <t>防汚剤添加量・厚膜塗装の充填精度</t>
+        </is>
+      </c>
+      <c r="T8" s="18" t="n">
+        <v>88</v>
       </c>
       <c r="U8" s="8" t="inlineStr">
         <is>
-          <t>営業・技術 / IR</t>
+          <t>IR / 技術センター</t>
         </is>
       </c>
       <c r="V8" s="8" t="inlineStr">
         <is>
-          <t>インフラ系顧客経由のコネクション</t>
+          <t>造船所経由</t>
         </is>
       </c>
       <c r="W8" s="8" t="inlineStr">
         <is>
-          <t>構造物向け特殊配合は機密性高</t>
+          <t>防汚剤組成は競争力源・機密性高</t>
         </is>
       </c>
       <c r="X8" s="14" t="inlineStr"/>
       <c r="Y8" s="7" t="inlineStr"/>
       <c r="Z8" s="8" t="inlineStr">
         <is>
-          <t>ジンクリッチ・蛍光塗料の特殊例として有効</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
+          <t>船舶・防食の世界トップ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="68" customHeight="1">
       <c r="A9" s="19" t="n">
         <v>5</v>
       </c>
@@ -1766,12 +1819,12 @@
       </c>
       <c r="R9" s="8" t="inlineStr">
         <is>
-          <t>鉄道用塗装ライン向け①〜⑨, 電着塗料の③配合</t>
+          <t>鉄道用塗装ライン①〜⑨、電着塗料の③配合</t>
         </is>
       </c>
       <c r="S9" s="8" t="inlineStr">
         <is>
-          <t>鉄道車両用塗料の歩留、電着塗料の電気伝導度管理</t>
+          <t>鉄道塗料の歩留、電着塗料の電気伝導度管理</t>
         </is>
       </c>
       <c r="T9" s="21" t="n">
@@ -1800,7 +1853,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
+    <row r="10" ht="68" customHeight="1">
       <c r="A10" s="19" t="n">
         <v>6</v>
       </c>
@@ -1811,32 +1864,32 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>立川塗料</t>
+          <t>日本特殊塗料 (NTC)</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>兵庫県川西市</t>
+          <t>東京都北区</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>非上場</t>
+          <t>東証スタンダード</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>約100億円規模 (推定)</t>
+          <t>約580億円</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>約300人</t>
+          <t>約1,800人(連結)</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>工業用・自動車部品・建設機械</t>
+          <t>建築防音材・自動車防音・特殊塗料</t>
         </is>
       </c>
       <c r="I10" s="15" t="inlineStr">
@@ -1859,119 +1912,119 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M10" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="M10" s="20" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="N10" s="8" t="inlineStr">
         <is>
-          <t>川西・三田</t>
+          <t>東京・愛知・滋賀 ほか</t>
         </is>
       </c>
       <c r="O10" s="17" t="inlineStr">
         <is>
-          <t>https://www.tachikawatoryo.co.jp/</t>
+          <t>https://www.ntpaint.co.jp/</t>
         </is>
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
-          <t>本社窓口</t>
+          <t>IR室</t>
         </is>
       </c>
       <c r="Q10" s="14" t="inlineStr">
         <is>
-          <t>低 (非上場・コーポレートサイトのみ)</t>
+          <t>中〜高</t>
         </is>
       </c>
       <c r="R10" s="8" t="inlineStr">
         <is>
-          <t>工業用塗料の①計量〜⑧充填</t>
+          <t>建築防水塗料・自動車制振塗料の③④⑤</t>
         </is>
       </c>
       <c r="S10" s="8" t="inlineStr">
         <is>
-          <t>中ロット工業塗料の歩留・在庫回転</t>
-        </is>
-      </c>
-      <c r="T10" s="22" t="n">
-        <v>65</v>
+          <t>厚膜塗料の塗布量、車両用制振材の充填</t>
+        </is>
+      </c>
+      <c r="T10" s="21" t="n">
+        <v>78</v>
       </c>
       <c r="U10" s="8" t="inlineStr">
         <is>
-          <t>業界団体経由・既存取引先紹介</t>
+          <t>IR / 技術部門</t>
         </is>
       </c>
       <c r="V10" s="8" t="inlineStr">
         <is>
-          <t>建機メーカー経由</t>
+          <t>建築・自動車業界経由</t>
         </is>
       </c>
       <c r="W10" s="8" t="inlineStr">
         <is>
-          <t>中小規模のため工場見学の受入余力要確認</t>
+          <t>防音材事業との切り分けが必要</t>
         </is>
       </c>
       <c r="X10" s="14" t="inlineStr"/>
       <c r="Y10" s="7" t="inlineStr"/>
       <c r="Z10" s="8" t="inlineStr">
         <is>
-          <t>中堅独立系の代表例</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="23" t="n">
+          <t>防音・制振との複合用途が特徴</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="68" customHeight="1">
+      <c r="A11" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t>建築特化</t>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>中堅総合</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>アトミクス</t>
+          <t>エスケー化研 (SK化研)</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>東京都荒川区</t>
+          <t>大阪府茨木市</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>非上場</t>
+          <t>非上場(独立系)</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>約180億円規模 (推定)</t>
+          <t>約1,800億円(推定)</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>約500人</t>
+          <t>約1,400人</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>床用塗料・建築・水性</t>
-        </is>
-      </c>
-      <c r="I11" s="15" t="inlineStr">
+          <t>建築用塗料 国内首位</t>
+        </is>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J11" s="15" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="J11" s="15" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="K11" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="K11" s="20" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="L11" s="10" t="inlineStr">
@@ -1979,74 +2032,74 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M11" s="20" t="inlineStr">
-        <is>
-          <t>△</t>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="N11" s="8" t="inlineStr">
         <is>
-          <t>茨城・千葉</t>
+          <t>大阪・茨木 ほか全国</t>
         </is>
       </c>
       <c r="O11" s="17" t="inlineStr">
         <is>
-          <t>https://www.atomix.co.jp/</t>
+          <t>https://www.sk-kaken.co.jp/</t>
         </is>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
-          <t>本社問合せ</t>
+          <t>本社・各支店</t>
         </is>
       </c>
       <c r="Q11" s="14" t="inlineStr">
         <is>
-          <t>低〜中</t>
+          <t>中 (非上場のためIR限定的)</t>
         </is>
       </c>
       <c r="R11" s="8" t="inlineStr">
         <is>
-          <t>水性床塗料の②分散・⑤調色</t>
+          <t>水性塗料 ②③④調色 + ⑥ろ過 + 設備洗浄</t>
         </is>
       </c>
       <c r="S11" s="8" t="inlineStr">
         <is>
-          <t>床用塗料の固形分・耐摩耗性管理</t>
-        </is>
-      </c>
-      <c r="T11" s="22" t="n">
-        <v>68</v>
+          <t>水性ベースの歩留、CCM普及率、防腐剤添加量</t>
+        </is>
+      </c>
+      <c r="T11" s="18" t="n">
+        <v>88</v>
       </c>
       <c r="U11" s="8" t="inlineStr">
         <is>
-          <t>営業・技術窓口</t>
+          <t>技術部門 / 営業窓口</t>
         </is>
       </c>
       <c r="V11" s="8" t="inlineStr">
         <is>
-          <t>ゼネコン経由</t>
+          <t>業界団体 (JPMA) 経由が確実</t>
         </is>
       </c>
       <c r="W11" s="8" t="inlineStr">
         <is>
-          <t>床塗料特化のため一般用との差異に注意</t>
+          <t>非上場のため定量データ開示範囲を要相談</t>
         </is>
       </c>
       <c r="X11" s="14" t="inlineStr"/>
       <c r="Y11" s="7" t="inlineStr"/>
       <c r="Z11" s="8" t="inlineStr">
         <is>
-          <t>床塗料のニッチ事例として</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="24" t="n">
+          <t>建築用水性塗料のリファレンスとして最重要</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="68" customHeight="1">
+      <c r="A12" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="24" t="inlineStr">
-        <is>
-          <t>自動車補修</t>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>中堅総合</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -2066,7 +2119,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>約220億円規模 (推定)</t>
+          <t>約220億円規模(推定)</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
@@ -2139,7 +2192,7 @@
       </c>
       <c r="U12" s="8" t="inlineStr">
         <is>
-          <t>営業 / 全国の補修工場経由</t>
+          <t>営業 / 補修工場経由</t>
         </is>
       </c>
       <c r="V12" s="8" t="inlineStr">
@@ -2160,23 +2213,23 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="24" t="n">
+    <row r="13" ht="68" customHeight="1">
+      <c r="A13" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="24" t="inlineStr">
-        <is>
-          <t>自動車補修</t>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>中堅総合</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>イサム塗料</t>
+          <t>武蔵塗料ホールディングス</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>大阪市住之江区</t>
+          <t>東京都北区</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
@@ -2186,137 +2239,137 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>約160億円規模 (推定)</t>
+          <t>約300億円規模(推定)</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>約450人</t>
+          <t>約800人(連結)</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>自動車補修・工業</t>
-        </is>
-      </c>
-      <c r="I13" s="15" t="inlineStr">
+          <t>工業用・電子部品・粉体・海外展開</t>
+        </is>
+      </c>
+      <c r="I13" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J13" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="K13" s="15" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="J13" s="20" t="inlineStr">
+      <c r="L13" s="20" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="K13" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L13" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M13" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="M13" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="N13" s="8" t="inlineStr">
         <is>
-          <t>大阪・茨城</t>
+          <t>栃木・東京・海外(中国・東南アジア)</t>
         </is>
       </c>
       <c r="O13" s="17" t="inlineStr">
         <is>
-          <t>https://www.isamu.co.jp/</t>
+          <t>https://www.musashipaint.co.jp/</t>
         </is>
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
-          <t>本社問合せ</t>
+          <t>本社</t>
         </is>
       </c>
       <c r="Q13" s="14" t="inlineStr">
         <is>
-          <t>低〜中</t>
+          <t>中</t>
         </is>
       </c>
       <c r="R13" s="8" t="inlineStr">
         <is>
-          <t>補修塗料の④⑤調色・⑥ろ過</t>
+          <t>粉体塗料の①〜⑦, 海外工場比較</t>
         </is>
       </c>
       <c r="S13" s="8" t="inlineStr">
         <is>
-          <t>小ロット調色のサンプル廃棄率</t>
-        </is>
-      </c>
-      <c r="T13" s="22" t="n">
-        <v>70</v>
+          <t>押出機消費電力・粉砕粒度管理・分級ロス率</t>
+        </is>
+      </c>
+      <c r="T13" s="21" t="n">
+        <v>80</v>
       </c>
       <c r="U13" s="8" t="inlineStr">
         <is>
-          <t>営業・既存取引</t>
+          <t>技術部門 / 海外拠点</t>
         </is>
       </c>
       <c r="V13" s="8" t="inlineStr">
         <is>
-          <t>板金塗装業界経由</t>
+          <t>家電・電子業界経由</t>
         </is>
       </c>
       <c r="W13" s="8" t="inlineStr">
         <is>
-          <t>ロックペイントと役割が重なる場合あり</t>
+          <t>海外グループの統一データ取得は難</t>
         </is>
       </c>
       <c r="X13" s="14" t="inlineStr"/>
       <c r="Y13" s="7" t="inlineStr"/>
       <c r="Z13" s="8" t="inlineStr">
         <is>
-          <t>ロックペイントとの比較対象</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="25" t="n">
+          <t>粉体塗料の代表ヒアリング先</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="68" customHeight="1">
+      <c r="A14" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="25" t="inlineStr">
-        <is>
-          <t>防食・構造物</t>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>中堅総合</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>中国塗料</t>
+          <t>立川塗料</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>東京都千代田区</t>
+          <t>兵庫県川西市</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>東証プライム</t>
+          <t>非上場</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>約1,100億円 (2024)</t>
+          <t>約100億円規模(推定)</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>約2,500人(連結)</t>
+          <t>約300人</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>船舶用塗料 (世界4強) + 工業防食</t>
+          <t>工業用・自動車部品・建設機械</t>
         </is>
       </c>
       <c r="I14" s="15" t="inlineStr">
@@ -2346,197 +2399,197 @@
       </c>
       <c r="N14" s="8" t="inlineStr">
         <is>
-          <t>兵庫・愛媛 ほか</t>
+          <t>川西・三田</t>
         </is>
       </c>
       <c r="O14" s="17" t="inlineStr">
         <is>
-          <t>https://www.cmp.co.jp/</t>
+          <t>https://www.tachikawatoryo.co.jp/</t>
         </is>
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
-          <t>IR部</t>
+          <t>本社窓口</t>
         </is>
       </c>
       <c r="Q14" s="14" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低 (非上場・コーポレートサイトのみ)</t>
         </is>
       </c>
       <c r="R14" s="8" t="inlineStr">
         <is>
-          <t>船舶塗料の③④ (低摩擦・防汚機能の分散)</t>
+          <t>工業用塗料の①計量〜⑧充填</t>
         </is>
       </c>
       <c r="S14" s="8" t="inlineStr">
         <is>
-          <t>防汚剤添加量・厚膜塗装の充填精度</t>
-        </is>
-      </c>
-      <c r="T14" s="18" t="n">
-        <v>85</v>
+          <t>中ロット工業塗料の歩留・在庫回転</t>
+        </is>
+      </c>
+      <c r="T14" s="22" t="n">
+        <v>65</v>
       </c>
       <c r="U14" s="8" t="inlineStr">
         <is>
-          <t>IR / 技術センター</t>
+          <t>業界団体経由・取引先紹介</t>
         </is>
       </c>
       <c r="V14" s="8" t="inlineStr">
         <is>
-          <t>造船所経由</t>
+          <t>建機メーカー経由</t>
         </is>
       </c>
       <c r="W14" s="8" t="inlineStr">
         <is>
-          <t>防汚剤組成は競争力源で機密性高</t>
+          <t>中小規模のため工場見学受入余力要確認</t>
         </is>
       </c>
       <c r="X14" s="14" t="inlineStr"/>
       <c r="Y14" s="7" t="inlineStr"/>
       <c r="Z14" s="8" t="inlineStr">
         <is>
-          <t>船舶・防食ニッチの世界トップ</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="26" t="n">
+          <t>中堅独立系の代表例</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="68" customHeight="1">
+      <c r="A15" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="26" t="inlineStr">
-        <is>
-          <t>UV・特殊</t>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>自動車補修</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>大日精化工業</t>
+          <t>イサム塗料</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>東京都中央区</t>
+          <t>大阪市住之江区</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>東証プライム</t>
+          <t>非上場</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>約1,300億円</t>
+          <t>約160億円規模(推定)</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>約3,000人(連結)</t>
+          <t>約450人</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>顔料・着色剤・特殊塗料・UV インキ</t>
-        </is>
-      </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="J15" s="16" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="K15" s="20" t="inlineStr">
+          <t>自動車補修・工業</t>
+        </is>
+      </c>
+      <c r="I15" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="J15" s="20" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
+      <c r="K15" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="L15" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M15" s="15" t="inlineStr">
-        <is>
-          <t>◎</t>
+      <c r="M15" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="N15" s="8" t="inlineStr">
         <is>
-          <t>千葉・茨城 ほか</t>
+          <t>大阪・茨城</t>
         </is>
       </c>
       <c r="O15" s="17" t="inlineStr">
         <is>
-          <t>https://www.daicolorchem.com/</t>
+          <t>https://www.isamu.co.jp/</t>
         </is>
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
-          <t>IR室</t>
+          <t>本社問合せ</t>
         </is>
       </c>
       <c r="Q15" s="14" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低〜中</t>
         </is>
       </c>
       <c r="R15" s="8" t="inlineStr">
         <is>
-          <t>顔料分散③ + UV 硬化塗料の①〜⑦</t>
+          <t>補修塗料の④⑤調色・⑥ろ過</t>
         </is>
       </c>
       <c r="S15" s="8" t="inlineStr">
         <is>
-          <t>顔料分散のビーズ条件・UV硬化のドーズ</t>
-        </is>
-      </c>
-      <c r="T15" s="21" t="n">
-        <v>82</v>
+          <t>小ロット調色のサンプル廃棄率</t>
+        </is>
+      </c>
+      <c r="T15" s="22" t="n">
+        <v>70</v>
       </c>
       <c r="U15" s="8" t="inlineStr">
         <is>
-          <t>技術部門 / IR</t>
+          <t>営業・既存取引</t>
         </is>
       </c>
       <c r="V15" s="8" t="inlineStr">
         <is>
-          <t>印刷インキ業界経由</t>
+          <t>板金塗装業界経由</t>
         </is>
       </c>
       <c r="W15" s="8" t="inlineStr">
         <is>
-          <t>インキ事業との切り分けが必要</t>
+          <t>ロックペイントと役割が重なる場合あり</t>
         </is>
       </c>
       <c r="X15" s="14" t="inlineStr"/>
       <c r="Y15" s="7" t="inlineStr"/>
       <c r="Z15" s="8" t="inlineStr">
         <is>
-          <t>顔料-塗料の上下流連結の例</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="26" t="n">
+          <t>ロックペイントとの比較対象</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="68" customHeight="1">
+      <c r="A16" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="26" t="inlineStr">
-        <is>
-          <t>UV・特殊</t>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>自動車補修</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>オキツモ</t>
+          <t>ホーマー技研</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>三重県名張市</t>
+          <t>東京都品川区</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
@@ -2546,29 +2599,29 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>約60億円規模 (推定)</t>
+          <t>数十億円規模(推定)</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>約200人</t>
+          <t>約100人(推定)</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>耐熱塗料・特殊塗料</t>
-        </is>
-      </c>
-      <c r="I16" s="15" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="J16" s="16" t="inlineStr">
+          <t>自動車補修副資材・特殊塗料</t>
+        </is>
+      </c>
+      <c r="I16" s="16" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
       <c r="K16" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -2579,19 +2632,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M16" s="20" t="inlineStr">
-        <is>
-          <t>△</t>
+      <c r="M16" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="N16" s="8" t="inlineStr">
         <is>
-          <t>三重・名張</t>
+          <t>(要確認)</t>
         </is>
       </c>
       <c r="O16" s="17" t="inlineStr">
         <is>
-          <t>https://www.okitsumo.co.jp/</t>
+          <t>https://www.homer-jp.com/</t>
         </is>
       </c>
       <c r="P16" s="7" t="inlineStr">
@@ -2599,84 +2652,84 @@
           <t>本社問合せ</t>
         </is>
       </c>
-      <c r="Q16" s="14" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="Q16" s="24" t="inlineStr">
+        <is>
+          <t>低 (要確認)</t>
         </is>
       </c>
       <c r="R16" s="8" t="inlineStr">
         <is>
-          <t>耐熱塗料の③分散・⑦検査 (耐熱試験)</t>
+          <t>補修副資材の充填工程</t>
         </is>
       </c>
       <c r="S16" s="8" t="inlineStr">
         <is>
-          <t>シリコーン樹脂の取扱、耐熱顔料の分散</t>
-        </is>
-      </c>
-      <c r="T16" s="27" t="n">
-        <v>60</v>
+          <t>副資材の SKU 数・小ロット運用</t>
+        </is>
+      </c>
+      <c r="T16" s="25" t="n">
+        <v>55</v>
       </c>
       <c r="U16" s="8" t="inlineStr">
         <is>
-          <t>技術部門</t>
+          <t>営業窓口</t>
         </is>
       </c>
       <c r="V16" s="8" t="inlineStr">
         <is>
-          <t>プラント・自動車排気系経由</t>
+          <t>板金塗装業界経由</t>
         </is>
       </c>
       <c r="W16" s="8" t="inlineStr">
         <is>
-          <t>ニッチ専業のため一般化は注意</t>
+          <t>塗料本体ではなく補修副資材寄りの可能性</t>
         </is>
       </c>
       <c r="X16" s="14" t="inlineStr"/>
       <c r="Y16" s="7" t="inlineStr"/>
       <c r="Z16" s="8" t="inlineStr">
         <is>
-          <t>耐熱塗料のニッチ事例</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="28" t="n">
+          <t>周辺領域として参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="68" customHeight="1">
+      <c r="A17" s="26" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="28" t="inlineStr">
-        <is>
-          <t>電着特化</t>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>建築・仕上塗材</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>日本ペイント・インダストリアルコーティングス</t>
+          <t>スズカファイン</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>大阪市北区 (日ペHD系列)</t>
+          <t>三重県鈴鹿市</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>非上場(子会社)</t>
+          <t>非上場</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>日ペHD 内訳</t>
+          <t>約230億円規模(推定)</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>数千人 (日ペ系列の一部)</t>
+          <t>約600人</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>自動車OEM・電着・工業</t>
+          <t>建築仕上塗材・水性塗料</t>
         </is>
       </c>
       <c r="I17" s="16" t="inlineStr">
@@ -2684,119 +2737,119 @@
           <t>○</t>
         </is>
       </c>
-      <c r="J17" s="16" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="K17" s="16" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="L17" s="15" t="inlineStr">
+      <c r="J17" s="15" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="M17" s="20" t="inlineStr">
+      <c r="K17" s="20" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
+      <c r="L17" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M17" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="N17" s="8" t="inlineStr">
         <is>
-          <t>東京・愛知・大阪</t>
+          <t>鈴鹿・関東</t>
         </is>
       </c>
       <c r="O17" s="17" t="inlineStr">
         <is>
-          <t>https://www.nipponpaint-industrialcoatings.co.jp/</t>
+          <t>https://www.suzukafine.co.jp/</t>
         </is>
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>日ペHD IR経由</t>
+          <t>本社問合せ</t>
         </is>
       </c>
       <c r="Q17" s="14" t="inlineStr">
         <is>
-          <t>中 (親会社IRに含む)</t>
+          <t>中</t>
         </is>
       </c>
       <c r="R17" s="8" t="inlineStr">
         <is>
-          <t>電着塗料 ①〜⑥全工程, OEM 直販</t>
+          <t>仕上塗材の②分散・⑤調色</t>
         </is>
       </c>
       <c r="S17" s="8" t="inlineStr">
         <is>
-          <t>電着塗料のMEQ・UF・塗着効率、OEM JIT配送</t>
-        </is>
-      </c>
-      <c r="T17" s="18" t="n">
-        <v>90</v>
+          <t>仕上塗材の粒径管理・水性化率</t>
+        </is>
+      </c>
+      <c r="T17" s="21" t="n">
+        <v>76</v>
       </c>
       <c r="U17" s="8" t="inlineStr">
         <is>
-          <t>親会社 (日ペHD) 経由</t>
+          <t>技術部門</t>
         </is>
       </c>
       <c r="V17" s="8" t="inlineStr">
         <is>
-          <t>自動車OEM経由</t>
+          <t>ゼネコン経由</t>
         </is>
       </c>
       <c r="W17" s="8" t="inlineStr">
         <is>
-          <t>親会社の方針に従う</t>
+          <t>仕上塗材は塗料分類で特殊な扱い</t>
         </is>
       </c>
       <c r="X17" s="14" t="inlineStr"/>
       <c r="Y17" s="7" t="inlineStr"/>
       <c r="Z17" s="8" t="inlineStr">
         <is>
-          <t>電着の最重要ヒアリング先候補</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="29" t="n">
+          <t>建築仕上塗材の代表</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="68" customHeight="1">
+      <c r="A18" s="26" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="29" t="inlineStr">
-        <is>
-          <t>粉体特化</t>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>建築・仕上塗材</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>武蔵塗料ホールディングス</t>
+          <t>菊水化学工業</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>東京都北区</t>
+          <t>名古屋市中区</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>非上場</t>
+          <t>東証スタンダード</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>約300億円規模 (推定)</t>
+          <t>約220億円</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>約800人(連結)</t>
+          <t>約500人(連結)</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>工業用・電子部品・粉体・海外展開</t>
+          <t>建築仕上塗材・防水・耐火塗料</t>
         </is>
       </c>
       <c r="I18" s="16" t="inlineStr">
@@ -2804,119 +2857,119 @@
           <t>○</t>
         </is>
       </c>
-      <c r="J18" s="16" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="K18" s="15" t="inlineStr">
+      <c r="J18" s="15" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="L18" s="20" t="inlineStr">
+      <c r="K18" s="20" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="M18" s="16" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="L18" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M18" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="N18" s="8" t="inlineStr">
         <is>
-          <t>栃木・東京・海外 (中国・東南アジア)</t>
+          <t>愛知・茨城</t>
         </is>
       </c>
       <c r="O18" s="17" t="inlineStr">
         <is>
-          <t>https://www.musashipaint.co.jp/</t>
+          <t>https://www.kikusui-chem.co.jp/</t>
         </is>
       </c>
       <c r="P18" s="7" t="inlineStr">
         <is>
-          <t>本社・海外拠点</t>
+          <t>IR担当</t>
         </is>
       </c>
       <c r="Q18" s="14" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>中〜高</t>
         </is>
       </c>
       <c r="R18" s="8" t="inlineStr">
         <is>
-          <t>粉体塗料の①〜⑦, 海外工場比較</t>
+          <t>仕上塗材・防水材の③④⑤</t>
         </is>
       </c>
       <c r="S18" s="8" t="inlineStr">
         <is>
-          <t>押出機消費電力・粉砕の粒度管理・分級ロス率</t>
-        </is>
-      </c>
-      <c r="T18" s="21" t="n">
-        <v>80</v>
+          <t>防水材の固形分管理、耐火塗料の塗膜厚</t>
+        </is>
+      </c>
+      <c r="T18" s="22" t="n">
+        <v>74</v>
       </c>
       <c r="U18" s="8" t="inlineStr">
         <is>
-          <t>技術部門 / 海外拠点</t>
+          <t>IR / 技術部門</t>
         </is>
       </c>
       <c r="V18" s="8" t="inlineStr">
         <is>
-          <t>家電・電子業界経由</t>
+          <t>ゼネコン経由</t>
         </is>
       </c>
       <c r="W18" s="8" t="inlineStr">
         <is>
-          <t>海外グループの統一データ取得難</t>
+          <t>耐火塗料は機密性高</t>
         </is>
       </c>
       <c r="X18" s="14" t="inlineStr"/>
       <c r="Y18" s="7" t="inlineStr"/>
       <c r="Z18" s="8" t="inlineStr">
         <is>
-          <t>粉体塗料の代表ヒアリング先</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="29" t="n">
+          <t>上場の建築特化メーカー</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="68" customHeight="1">
+      <c r="A19" s="26" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="29" t="inlineStr">
-        <is>
-          <t>粉体特化</t>
+      <c r="B19" s="26" t="inlineStr">
+        <is>
+          <t>建築・仕上塗材</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>ユシロ化学工業 (塗料事業) または興亜工業</t>
+          <t>フッコー</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>東京都ほか</t>
+          <t>兵庫県神戸市</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>(社により異なる)</t>
+          <t>非上場</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>塗料事業100億円規模程度</t>
+          <t>約60億円規模(推定)</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>粉体部門 数十〜数百人</t>
+          <t>約200人</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>粉体塗料・特殊塗料</t>
+          <t>建築仕上塗材</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -2924,16 +2977,16 @@
           <t>△</t>
         </is>
       </c>
-      <c r="J19" s="20" t="inlineStr">
+      <c r="J19" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="K19" s="20" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="K19" s="15" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
       <c r="L19" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -2946,12 +2999,12 @@
       </c>
       <c r="N19" s="8" t="inlineStr">
         <is>
-          <t>関東</t>
-        </is>
-      </c>
-      <c r="O19" s="7" t="inlineStr">
-        <is>
-          <t>(社により異なる)</t>
+          <t>兵庫・関東</t>
+        </is>
+      </c>
+      <c r="O19" s="17" t="inlineStr">
+        <is>
+          <t>https://www.fukko.co.jp/</t>
         </is>
       </c>
       <c r="P19" s="7" t="inlineStr">
@@ -2961,62 +3014,62 @@
       </c>
       <c r="Q19" s="14" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>低〜中</t>
         </is>
       </c>
       <c r="R19" s="8" t="inlineStr">
         <is>
-          <t>粉体専業の②押出〜⑤分級</t>
+          <t>仕上塗材の②分散・⑤調色</t>
         </is>
       </c>
       <c r="S19" s="8" t="inlineStr">
         <is>
-          <t>中小規模粉体プラントのスケール感</t>
-        </is>
-      </c>
-      <c r="T19" s="27" t="n">
-        <v>55</v>
+          <t>仕上塗材中小プラントの規模感</t>
+        </is>
+      </c>
+      <c r="T19" s="25" t="n">
+        <v>58</v>
       </c>
       <c r="U19" s="8" t="inlineStr">
         <is>
-          <t>業界団体経由</t>
+          <t>営業窓口</t>
         </is>
       </c>
       <c r="V19" s="8" t="inlineStr">
         <is>
-          <t>粉体塗装業界経由</t>
+          <t>建材販売店経由</t>
         </is>
       </c>
       <c r="W19" s="8" t="inlineStr">
         <is>
-          <t>事業規模・継続性を要確認</t>
+          <t>中小規模ゆえスケール感に注意</t>
         </is>
       </c>
       <c r="X19" s="14" t="inlineStr"/>
       <c r="Y19" s="7" t="inlineStr"/>
       <c r="Z19" s="8" t="inlineStr">
         <is>
-          <t>中小粉体メーカーのスコープ確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
+          <t>中小建築塗材の補強</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="68" customHeight="1">
       <c r="A20" s="26" t="n">
         <v>16</v>
       </c>
       <c r="B20" s="26" t="inlineStr">
         <is>
-          <t>UV・特殊</t>
+          <t>建築・仕上塗材</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>十条ケミカル</t>
+          <t>アトミクス</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>東京都北区</t>
+          <t>東京都荒川区</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
@@ -3026,52 +3079,52 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>約100億円規模 (推定)</t>
+          <t>約180億円規模(推定)</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>約300人</t>
+          <t>約500人</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>UV インキ・UV 塗料・印刷</t>
-        </is>
-      </c>
-      <c r="I20" s="20" t="inlineStr">
+          <t>床用塗料・建築・水性</t>
+        </is>
+      </c>
+      <c r="I20" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="J20" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="K20" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L20" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M20" s="20" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="J20" s="20" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="K20" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L20" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M20" s="15" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
       <c r="N20" s="8" t="inlineStr">
         <is>
-          <t>東京・埼玉</t>
+          <t>茨城・千葉</t>
         </is>
       </c>
       <c r="O20" s="17" t="inlineStr">
         <is>
-          <t>https://www.jujochemical.co.jp/</t>
+          <t>https://www.atomix.co.jp/</t>
         </is>
       </c>
       <c r="P20" s="7" t="inlineStr">
@@ -3081,302 +3134,302 @@
       </c>
       <c r="Q20" s="14" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低〜中</t>
         </is>
       </c>
       <c r="R20" s="8" t="inlineStr">
         <is>
-          <t>UV塗料の①遮光下計量・②分散・⑤ろ過・⑦充填</t>
+          <t>水性床塗料の②分散・⑤調色</t>
         </is>
       </c>
       <c r="S20" s="8" t="inlineStr">
         <is>
-          <t>光開始剤の取扱・UV照射ドーズ・遮光容器仕様</t>
-        </is>
-      </c>
-      <c r="T20" s="21" t="n">
-        <v>78</v>
+          <t>床用塗料の固形分・耐摩耗性管理</t>
+        </is>
+      </c>
+      <c r="T20" s="22" t="n">
+        <v>68</v>
       </c>
       <c r="U20" s="8" t="inlineStr">
         <is>
-          <t>技術 / 営業</t>
+          <t>営業・技術窓口</t>
         </is>
       </c>
       <c r="V20" s="8" t="inlineStr">
         <is>
-          <t>印刷業界経由</t>
+          <t>ゼネコン経由</t>
         </is>
       </c>
       <c r="W20" s="8" t="inlineStr">
         <is>
-          <t>UVインキとUV塗料の境界に注意</t>
+          <t>床塗料特化のため一般用との差異に注意</t>
         </is>
       </c>
       <c r="X20" s="14" t="inlineStr"/>
       <c r="Y20" s="7" t="inlineStr"/>
       <c r="Z20" s="8" t="inlineStr">
         <is>
-          <t>UV硬化の最重要ヒアリング先</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
+          <t>床塗料のニッチ事例</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="68" customHeight="1">
       <c r="A21" s="26" t="n">
         <v>17</v>
       </c>
       <c r="B21" s="26" t="inlineStr">
         <is>
-          <t>UV・特殊</t>
+          <t>建築・仕上塗材</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>太陽ホールディングス (太陽インキ製造)</t>
+          <t>大同塗料</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>埼玉県嵐山町</t>
+          <t>大阪市西成区</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>東証プライム</t>
+          <t>非上場</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>約820億円</t>
+          <t>約100億円規模(推定)</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>約2,200人(連結)</t>
+          <t>約300人</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>電子用UVインキ・ソルダーレジスト・UV塗料</t>
-        </is>
-      </c>
-      <c r="I21" s="20" t="inlineStr">
+          <t>建築・橋梁・構造物</t>
+        </is>
+      </c>
+      <c r="I21" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="J21" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="K21" s="20" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="J21" s="20" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="K21" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="L21" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M21" s="15" t="inlineStr">
-        <is>
-          <t>◎</t>
+      <c r="M21" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="N21" s="8" t="inlineStr">
         <is>
-          <t>埼玉・台湾・中国</t>
+          <t>大阪・茨城</t>
         </is>
       </c>
       <c r="O21" s="17" t="inlineStr">
         <is>
-          <t>https://www.taiyo-hd.co.jp/</t>
+          <t>https://www.daidotoryo.co.jp/</t>
         </is>
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
-          <t>IR室</t>
+          <t>本社問合せ</t>
         </is>
       </c>
       <c r="Q21" s="14" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="R21" s="8" t="inlineStr">
         <is>
-          <t>電子用UV塗料の③分散・⑤ろ過・⑦充填</t>
+          <t>重防食塗料の③④⑤・⑧充填</t>
         </is>
       </c>
       <c r="S21" s="8" t="inlineStr">
         <is>
-          <t>電子用の微粒子分散・高純度フィルター</t>
-        </is>
-      </c>
-      <c r="T21" s="21" t="n">
-        <v>80</v>
+          <t>重防食塗料の固形分管理</t>
+        </is>
+      </c>
+      <c r="T21" s="25" t="n">
+        <v>64</v>
       </c>
       <c r="U21" s="8" t="inlineStr">
         <is>
-          <t>IR / 技術部門</t>
+          <t>営業窓口</t>
         </is>
       </c>
       <c r="V21" s="8" t="inlineStr">
         <is>
-          <t>電子業界経由</t>
+          <t>橋梁・構造物業界経由</t>
         </is>
       </c>
       <c r="W21" s="8" t="inlineStr">
         <is>
-          <t>電子用は機密性高</t>
+          <t>DNTと顧客領域が重なる</t>
         </is>
       </c>
       <c r="X21" s="14" t="inlineStr"/>
       <c r="Y21" s="7" t="inlineStr"/>
       <c r="Z21" s="8" t="inlineStr">
         <is>
-          <t>電子用UVのリファレンス</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="26" t="n">
+          <t>中堅防食メーカーの補強</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="68" customHeight="1">
+      <c r="A22" s="27" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="26" t="inlineStr">
-        <is>
-          <t>UV・特殊</t>
+      <c r="B22" s="27" t="inlineStr">
+        <is>
+          <t>機能・特殊</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>帝国インキ製造</t>
+          <t>オキツモ</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>埼玉県川口市</t>
+          <t>三重県名張市</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>東証スタンダード</t>
+          <t>非上場</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>約180億円</t>
+          <t>約60億円規模(推定)</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>約450人(連結)</t>
+          <t>約200人</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>印刷インキ・UV インキ・特殊塗料</t>
-        </is>
-      </c>
-      <c r="I22" s="20" t="inlineStr">
+          <t>耐熱塗料・特殊塗料</t>
+        </is>
+      </c>
+      <c r="I22" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="K22" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L22" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M22" s="20" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="J22" s="20" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="K22" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L22" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M22" s="15" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
       <c r="N22" s="8" t="inlineStr">
         <is>
-          <t>川口・千葉</t>
+          <t>三重・名張</t>
         </is>
       </c>
       <c r="O22" s="17" t="inlineStr">
         <is>
-          <t>https://www.teikokuink.com/</t>
+          <t>https://www.okitsumo.co.jp/</t>
         </is>
       </c>
       <c r="P22" s="7" t="inlineStr">
         <is>
-          <t>IR室</t>
+          <t>本社問合せ</t>
         </is>
       </c>
       <c r="Q22" s="14" t="inlineStr">
         <is>
-          <t>中〜高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="R22" s="8" t="inlineStr">
         <is>
-          <t>UVインキの③分散・⑦充填</t>
+          <t>耐熱塗料の③分散・⑦検査 (耐熱試験)</t>
         </is>
       </c>
       <c r="S22" s="8" t="inlineStr">
         <is>
-          <t>UVインキの分散条件・歩留</t>
-        </is>
-      </c>
-      <c r="T22" s="22" t="n">
-        <v>70</v>
+          <t>シリコーン樹脂取扱、耐熱顔料の分散</t>
+        </is>
+      </c>
+      <c r="T22" s="25" t="n">
+        <v>60</v>
       </c>
       <c r="U22" s="8" t="inlineStr">
         <is>
-          <t>IR / 技術</t>
+          <t>技術部門</t>
         </is>
       </c>
       <c r="V22" s="8" t="inlineStr">
         <is>
-          <t>印刷業界経由</t>
+          <t>プラント・自動車排気系経由</t>
         </is>
       </c>
       <c r="W22" s="8" t="inlineStr">
         <is>
-          <t>塗料との境界線</t>
+          <t>ニッチ専業のため一般化に注意</t>
         </is>
       </c>
       <c r="X22" s="14" t="inlineStr"/>
       <c r="Y22" s="7" t="inlineStr"/>
       <c r="Z22" s="8" t="inlineStr">
         <is>
-          <t>UV インキ視点での補強</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="30" t="n">
+          <t>耐熱塗料のニッチ事例</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="68" customHeight="1">
+      <c r="A23" s="27" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="30" t="inlineStr">
-        <is>
-          <t>DIY・小口</t>
+      <c r="B23" s="27" t="inlineStr">
+        <is>
+          <t>機能・特殊</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>アサヒペン</t>
+          <t>シンロイヒ</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>大阪市鶴見区</t>
+          <t>東京都品川区</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
@@ -3386,17 +3439,17 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>約280億円規模 (推定)</t>
+          <t>約30億円規模(推定)</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>約600人</t>
+          <t>約100人</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>DIY・小口・ホームセンター</t>
+          <t>蛍光塗料・特殊塗料</t>
         </is>
       </c>
       <c r="I23" s="15" t="inlineStr">
@@ -3404,9 +3457,9 @@
           <t>◎</t>
         </is>
       </c>
-      <c r="J23" s="15" t="inlineStr">
-        <is>
-          <t>◎</t>
+      <c r="J23" s="20" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="K23" s="10" t="inlineStr">
@@ -3426,12 +3479,12 @@
       </c>
       <c r="N23" s="8" t="inlineStr">
         <is>
-          <t>大阪・茨城</t>
+          <t>栃木</t>
         </is>
       </c>
       <c r="O23" s="17" t="inlineStr">
         <is>
-          <t>https://www.asahipen.jp/</t>
+          <t>https://www.sinloihi.co.jp/</t>
         </is>
       </c>
       <c r="P23" s="7" t="inlineStr">
@@ -3446,77 +3499,77 @@
       </c>
       <c r="R23" s="8" t="inlineStr">
         <is>
-          <t>小容量缶 (1L/4L) の⑧充填・⑨保管</t>
+          <t>蛍光顔料の分散・希釈・充填</t>
         </is>
       </c>
       <c r="S23" s="8" t="inlineStr">
         <is>
-          <t>小容量充填のスループット・歩留</t>
-        </is>
-      </c>
-      <c r="T23" s="27" t="n">
-        <v>60</v>
+          <t>蛍光顔料の取扱・退色管理</t>
+        </is>
+      </c>
+      <c r="T23" s="25" t="n">
+        <v>58</v>
       </c>
       <c r="U23" s="8" t="inlineStr">
         <is>
-          <t>営業窓口</t>
+          <t>技術部門</t>
         </is>
       </c>
       <c r="V23" s="8" t="inlineStr">
         <is>
-          <t>ホームセンター経由</t>
+          <t>安全標識・印刷業界経由</t>
         </is>
       </c>
       <c r="W23" s="8" t="inlineStr">
         <is>
-          <t>プロ向けと差別化必要</t>
+          <t>蛍光特殊で一般化困難</t>
         </is>
       </c>
       <c r="X23" s="14" t="inlineStr"/>
       <c r="Y23" s="7" t="inlineStr"/>
       <c r="Z23" s="8" t="inlineStr">
         <is>
-          <t>DIY 流通の代表</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="30" t="n">
+          <t>蛍光特殊事例</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="68" customHeight="1">
+      <c r="A24" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="30" t="inlineStr">
-        <is>
-          <t>DIY・小口</t>
+      <c r="B24" s="27" t="inlineStr">
+        <is>
+          <t>機能・特殊</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>カンペハピオ (関ペ子会社)</t>
+          <t>ナトコ</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>大阪市東淀川区</t>
+          <t>名古屋市西区</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>非上場 (関ペ系列)</t>
+          <t>非上場</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>数百億円規模</t>
+          <t>約170億円規模(推定)</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>数百人</t>
+          <t>約450人</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>DIY・ホームセンター・小口</t>
+          <t>機能性塗料・特殊コーティング</t>
         </is>
       </c>
       <c r="I24" s="15" t="inlineStr">
@@ -3524,14 +3577,14 @@
           <t>◎</t>
         </is>
       </c>
-      <c r="J24" s="15" t="inlineStr">
-        <is>
-          <t>◎</t>
-        </is>
-      </c>
-      <c r="K24" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J24" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="K24" s="20" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="L24" s="10" t="inlineStr">
@@ -3539,24 +3592,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M24" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="M24" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="N24" s="8" t="inlineStr">
         <is>
-          <t>大阪・関西ペイント工場併設</t>
+          <t>愛知・茨城</t>
         </is>
       </c>
       <c r="O24" s="17" t="inlineStr">
         <is>
-          <t>https://www.kanpe.co.jp/</t>
+          <t>https://www.natoco.co.jp/</t>
         </is>
       </c>
       <c r="P24" s="7" t="inlineStr">
         <is>
-          <t>関ペ広報経由</t>
+          <t>本社問合せ</t>
         </is>
       </c>
       <c r="Q24" s="14" t="inlineStr">
@@ -3566,92 +3619,92 @@
       </c>
       <c r="R24" s="8" t="inlineStr">
         <is>
-          <t>DIY 缶の⑤調色・⑧充填</t>
+          <t>機能塗料の③分散・⑦検査</t>
         </is>
       </c>
       <c r="S24" s="8" t="inlineStr">
         <is>
-          <t>小容量缶のSKU・色種数・回転</t>
-        </is>
-      </c>
-      <c r="T24" s="27" t="n">
-        <v>58</v>
+          <t>機能塗料の品質規格・小ロット運用</t>
+        </is>
+      </c>
+      <c r="T24" s="22" t="n">
+        <v>72</v>
       </c>
       <c r="U24" s="8" t="inlineStr">
         <is>
-          <t>親会社 (関西ペイント) 経由</t>
+          <t>技術部門</t>
         </is>
       </c>
       <c r="V24" s="8" t="inlineStr">
         <is>
-          <t>ホームセンター業界経由</t>
+          <t>電子・自動車・建材業界経由</t>
         </is>
       </c>
       <c r="W24" s="8" t="inlineStr">
         <is>
-          <t>親会社の方針に従う</t>
+          <t>機能特化のため標準フローと差異あり</t>
         </is>
       </c>
       <c r="X24" s="14" t="inlineStr"/>
       <c r="Y24" s="7" t="inlineStr"/>
       <c r="Z24" s="8" t="inlineStr">
         <is>
-          <t>DIY 流通の補強</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="31" t="n">
+          <t>機能塗料の補強</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="68" customHeight="1">
+      <c r="A25" s="27" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="31" t="inlineStr">
-        <is>
-          <t>業界団体</t>
+      <c r="B25" s="27" t="inlineStr">
+        <is>
+          <t>機能・特殊</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>日本塗料工業会 (JPMA)</t>
+          <t>大日精化工業</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>東京都港区</t>
+          <t>東京都中央区</t>
         </is>
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>業界団体</t>
+          <t>東証プライム</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>約1,300億円</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>事務局 数十人</t>
+          <t>約3,000人(連結)</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>塗料業界の自主規制・統計・規格</t>
-        </is>
-      </c>
-      <c r="I25" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J25" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K25" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>顔料・着色剤・UV インキ・特殊塗料</t>
+        </is>
+      </c>
+      <c r="I25" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="K25" s="20" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="L25" s="10" t="inlineStr">
@@ -3659,114 +3712,114 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M25" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="M25" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
         </is>
       </c>
       <c r="N25" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>千葉・茨城 ほか</t>
         </is>
       </c>
       <c r="O25" s="17" t="inlineStr">
         <is>
-          <t>https://www.toryo.or.jp/</t>
+          <t>https://www.daicolorchem.com/</t>
         </is>
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
-          <t>事務局</t>
+          <t>IR室</t>
         </is>
       </c>
       <c r="Q25" s="14" t="inlineStr">
         <is>
-          <t>高 (業界統計・コーティングケア指標公開)</t>
+          <t>高</t>
         </is>
       </c>
       <c r="R25" s="8" t="inlineStr">
         <is>
-          <t>全工程の業界平均値・VOC統計・廃棄物統計</t>
+          <t>顔料分散③ + UV 硬化塗料の①〜⑦</t>
         </is>
       </c>
       <c r="S25" s="8" t="inlineStr">
         <is>
-          <t>コーティングケア環境管理指標、VOC排出実態推計</t>
-        </is>
-      </c>
-      <c r="T25" s="18" t="n">
-        <v>92</v>
+          <t>顔料分散のビーズ条件・UV ドーズ</t>
+        </is>
+      </c>
+      <c r="T25" s="21" t="n">
+        <v>82</v>
       </c>
       <c r="U25" s="8" t="inlineStr">
         <is>
-          <t>事務局直接 / 加盟社経由</t>
+          <t>技術部門 / IR</t>
         </is>
       </c>
       <c r="V25" s="8" t="inlineStr">
         <is>
-          <t>加盟社経由</t>
+          <t>印刷インキ業界経由</t>
         </is>
       </c>
       <c r="W25" s="8" t="inlineStr">
         <is>
-          <t>個社データではなく業界平均</t>
+          <t>インキ事業との切り分けが必要</t>
         </is>
       </c>
       <c r="X25" s="14" t="inlineStr"/>
       <c r="Y25" s="7" t="inlineStr"/>
       <c r="Z25" s="8" t="inlineStr">
         <is>
-          <t>業界横断校正の起点</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="31" t="n">
+          <t>顔料-塗料の上下流連結の例</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="68" customHeight="1">
+      <c r="A26" s="27" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="31" t="inlineStr">
-        <is>
-          <t>業界団体</t>
+      <c r="B26" s="27" t="inlineStr">
+        <is>
+          <t>機能・特殊</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>関東塗料工業組合</t>
+          <t>染めQテクノロジィ</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>東京都中央区</t>
+          <t>千葉県四街道市</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>業界団体</t>
+          <t>非上場</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>約30億円規模(推定)</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>事務局</t>
+          <t>約100人</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>関東圏中小塗料メーカーの組合</t>
-        </is>
-      </c>
-      <c r="I26" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J26" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>ナノテク特殊塗料・密着剤</t>
+        </is>
+      </c>
+      <c r="I26" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="J26" s="20" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="K26" s="10" t="inlineStr">
@@ -3786,107 +3839,107 @@
       </c>
       <c r="N26" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>千葉</t>
         </is>
       </c>
       <c r="O26" s="17" t="inlineStr">
         <is>
-          <t>https://kantoko.com/</t>
+          <t>https://somayq.com/</t>
         </is>
       </c>
       <c r="P26" s="7" t="inlineStr">
         <is>
-          <t>事務局</t>
+          <t>本社問合せ</t>
         </is>
       </c>
       <c r="Q26" s="14" t="inlineStr">
         <is>
-          <t>中 (ブログ・年次資料公開)</t>
+          <t>低〜中</t>
         </is>
       </c>
       <c r="R26" s="8" t="inlineStr">
         <is>
-          <t>中小規模工場の運用実態</t>
+          <t>特殊塗料の②分散・⑤調色・⑧充填(エアゾール)</t>
         </is>
       </c>
       <c r="S26" s="8" t="inlineStr">
         <is>
-          <t>中小工場のVOC削減取組、廃棄物処理事例</t>
-        </is>
-      </c>
-      <c r="T26" s="21" t="n">
-        <v>78</v>
+          <t>密着剤の薄膜形成、エアゾール充填精度</t>
+        </is>
+      </c>
+      <c r="T26" s="25" t="n">
+        <v>60</v>
       </c>
       <c r="U26" s="8" t="inlineStr">
         <is>
-          <t>事務局直接</t>
+          <t>営業窓口</t>
         </is>
       </c>
       <c r="V26" s="8" t="inlineStr">
         <is>
-          <t>中小メーカー経由</t>
+          <t>DIY・補修業界経由</t>
         </is>
       </c>
       <c r="W26" s="8" t="inlineStr">
         <is>
-          <t>JPMAとの役割分担に注意</t>
+          <t>エアゾール充填が含まれ標準フローと一部異なる</t>
         </is>
       </c>
       <c r="X26" s="14" t="inlineStr"/>
       <c r="Y26" s="7" t="inlineStr"/>
       <c r="Z26" s="8" t="inlineStr">
         <is>
-          <t>中小事例の補完</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="31" t="n">
+          <t>ナノテク特殊事例</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="68" customHeight="1">
+      <c r="A27" s="27" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="31" t="inlineStr">
-        <is>
-          <t>業界団体</t>
+      <c r="B27" s="27" t="inlineStr">
+        <is>
+          <t>機能・特殊</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>日本塗装技術協会 (JCOT)</t>
+          <t>AGCコーテック</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>東京都千代田区</t>
         </is>
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>学術・業界団体</t>
+          <t>非上場(AGC系)</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>約60億円規模(推定)</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>事務局</t>
+          <t>約200人</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>塗装技術の研究・標準化</t>
-        </is>
-      </c>
-      <c r="I27" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J27" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>フッ素樹脂塗料・耐候性塗料</t>
+        </is>
+      </c>
+      <c r="I27" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="J27" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="K27" s="10" t="inlineStr">
@@ -3906,107 +3959,107 @@
       </c>
       <c r="N27" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>千葉・福岡</t>
         </is>
       </c>
       <c r="O27" s="17" t="inlineStr">
         <is>
-          <t>https://jcot.or.jp/</t>
+          <t>https://www.agccoatech.co.jp/</t>
         </is>
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
-          <t>事務局</t>
+          <t>本社問合せ</t>
         </is>
       </c>
       <c r="Q27" s="14" t="inlineStr">
         <is>
-          <t>中 (用語辞典・技術資料公開)</t>
+          <t>中 (AGC連結に含む)</t>
         </is>
       </c>
       <c r="R27" s="8" t="inlineStr">
         <is>
-          <t>塗装側 (顧客側) のフロー・要求仕様</t>
+          <t>フッ素樹脂塗料の③④⑤</t>
         </is>
       </c>
       <c r="S27" s="8" t="inlineStr">
         <is>
-          <t>塗装現場での歩留・塗着効率・VOC</t>
+          <t>フッ素樹脂取扱・耐候性試験</t>
         </is>
       </c>
       <c r="T27" s="22" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="U27" s="8" t="inlineStr">
         <is>
-          <t>事務局・参加企業経由</t>
+          <t>技術部門 / AGC経由</t>
         </is>
       </c>
       <c r="V27" s="8" t="inlineStr">
         <is>
-          <t>塗装ユーザー業界経由</t>
+          <t>建築・インフラ業界経由</t>
         </is>
       </c>
       <c r="W27" s="8" t="inlineStr">
         <is>
-          <t>塗装側に重点があり、製造側情報は限定的</t>
+          <t>フッ素樹脂特化のため一般化に注意</t>
         </is>
       </c>
       <c r="X27" s="14" t="inlineStr"/>
       <c r="Y27" s="7" t="inlineStr"/>
       <c r="Z27" s="8" t="inlineStr">
         <is>
-          <t>顧客側の補強</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="31" t="n">
+          <t>高耐候塗料のニッチ事例</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="68" customHeight="1">
+      <c r="A28" s="28" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="31" t="inlineStr">
-        <is>
-          <t>業界団体</t>
+      <c r="B28" s="28" t="inlineStr">
+        <is>
+          <t>UV・印刷インキ</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>色材協会</t>
+          <t>十条ケミカル</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>東京都</t>
+          <t>東京都北区</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>学術団体</t>
+          <t>非上場</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>約100億円規模(推定)</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>事務局</t>
+          <t>約300人</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>色材・塗料・印刷インキの学術</t>
-        </is>
-      </c>
-      <c r="I28" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J28" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>UV インキ・UV 塗料・印刷</t>
+        </is>
+      </c>
+      <c r="I28" s="20" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="J28" s="20" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="K28" s="10" t="inlineStr">
@@ -4019,114 +4072,114 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M28" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="M28" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
         </is>
       </c>
       <c r="N28" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>東京・埼玉</t>
         </is>
       </c>
       <c r="O28" s="17" t="inlineStr">
         <is>
-          <t>https://www.shikizai.org/</t>
+          <t>https://www.jujochemical.co.jp/</t>
         </is>
       </c>
       <c r="P28" s="7" t="inlineStr">
         <is>
-          <t>事務局</t>
+          <t>本社問合せ</t>
         </is>
       </c>
       <c r="Q28" s="14" t="inlineStr">
         <is>
-          <t>高 (色材協会誌 J-Stage)</t>
+          <t>中</t>
         </is>
       </c>
       <c r="R28" s="8" t="inlineStr">
         <is>
-          <t>学術視点での③分散・⑤調色</t>
+          <t>UV塗料の①遮光下計量・②分散・⑤ろ過・⑦充填</t>
         </is>
       </c>
       <c r="S28" s="8" t="inlineStr">
         <is>
-          <t>学会発表事例・分散基礎データ</t>
-        </is>
-      </c>
-      <c r="T28" s="22" t="n">
-        <v>68</v>
+          <t>光開始剤の取扱・UV照射ドーズ・遮光容器仕様</t>
+        </is>
+      </c>
+      <c r="T28" s="21" t="n">
+        <v>78</v>
       </c>
       <c r="U28" s="8" t="inlineStr">
         <is>
-          <t>学会員経由</t>
+          <t>技術 / 営業</t>
         </is>
       </c>
       <c r="V28" s="8" t="inlineStr">
         <is>
-          <t>技術者経由</t>
+          <t>印刷業界経由</t>
         </is>
       </c>
       <c r="W28" s="8" t="inlineStr">
         <is>
-          <t>学術重点で実プラント数値は限定的</t>
+          <t>UVインキとUV塗料の境界に注意</t>
         </is>
       </c>
       <c r="X28" s="14" t="inlineStr"/>
       <c r="Y28" s="7" t="inlineStr"/>
       <c r="Z28" s="8" t="inlineStr">
         <is>
-          <t>学術背景の校正</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="32" t="n">
+          <t>UV硬化の最重要ヒアリング先</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="68" customHeight="1">
+      <c r="A29" s="28" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="32" t="inlineStr">
-        <is>
-          <t>装置メーカー</t>
+      <c r="B29" s="28" t="inlineStr">
+        <is>
+          <t>UV・印刷インキ</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>アシザワ・ファインテック</t>
+          <t>太陽ホールディングス</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>千葉県習志野市</t>
+          <t>埼玉県嵐山町</t>
         </is>
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>非上場</t>
+          <t>東証プライム</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>約100億円規模 (推定)</t>
+          <t>約820億円</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>約300人</t>
+          <t>約2,200人(連結)</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>ビーズミル・分散機メーカー</t>
-        </is>
-      </c>
-      <c r="I29" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J29" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>電子用UVインキ・ソルダーレジスト・UV塗料</t>
+        </is>
+      </c>
+      <c r="I29" s="20" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="J29" s="20" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="K29" s="10" t="inlineStr">
@@ -4139,114 +4192,114 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M29" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="M29" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
         </is>
       </c>
       <c r="N29" s="8" t="inlineStr">
         <is>
-          <t>習志野・つくば</t>
+          <t>埼玉・台湾・中国</t>
         </is>
       </c>
       <c r="O29" s="17" t="inlineStr">
         <is>
-          <t>https://ashizawa.com/</t>
+          <t>https://www.taiyo-hd.co.jp/</t>
         </is>
       </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
-          <t>本社問合せ</t>
+          <t>IR室</t>
         </is>
       </c>
       <c r="Q29" s="14" t="inlineStr">
         <is>
-          <t>高 (技術資料充実)</t>
+          <t>高</t>
         </is>
       </c>
       <c r="R29" s="8" t="inlineStr">
         <is>
-          <t>③分散・練肉 の装置設計・運転条件</t>
+          <t>電子用UV塗料の③分散・⑤ろ過・⑦充填</t>
         </is>
       </c>
       <c r="S29" s="8" t="inlineStr">
         <is>
-          <t>ビーズミル消費電力・周速・歩留</t>
-        </is>
-      </c>
-      <c r="T29" s="18" t="n">
-        <v>88</v>
+          <t>電子用の微粒子分散・高純度フィルター</t>
+        </is>
+      </c>
+      <c r="T29" s="21" t="n">
+        <v>80</v>
       </c>
       <c r="U29" s="8" t="inlineStr">
         <is>
-          <t>技術営業</t>
+          <t>IR / 技術部門</t>
         </is>
       </c>
       <c r="V29" s="8" t="inlineStr">
         <is>
-          <t>顧客 (塗料メーカー) 経由</t>
+          <t>電子業界経由</t>
         </is>
       </c>
       <c r="W29" s="8" t="inlineStr">
         <is>
-          <t>個別顧客名は出せない</t>
+          <t>電子用は機密性高</t>
         </is>
       </c>
       <c r="X29" s="14" t="inlineStr"/>
       <c r="Y29" s="7" t="inlineStr"/>
       <c r="Z29" s="8" t="inlineStr">
         <is>
-          <t>分散工程の校正に必須</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="32" t="n">
+          <t>電子用UVのリファレンス</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="68" customHeight="1">
+      <c r="A30" s="28" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="32" t="inlineStr">
-        <is>
-          <t>装置メーカー</t>
+      <c r="B30" s="28" t="inlineStr">
+        <is>
+          <t>UV・印刷インキ</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>淺田鉄工</t>
+          <t>帝国インキ製造</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>兵庫県尼崎市</t>
+          <t>埼玉県川口市</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>非上場</t>
+          <t>東証スタンダード</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>約80億円規模 (推定)</t>
+          <t>約180億円</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>約200人</t>
+          <t>約450人(連結)</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>分散機・撹拌機・ビーズミル</t>
-        </is>
-      </c>
-      <c r="I30" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J30" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>印刷インキ・UV インキ・特殊塗料</t>
+        </is>
+      </c>
+      <c r="I30" s="20" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="J30" s="20" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="K30" s="10" t="inlineStr">
@@ -4259,24 +4312,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M30" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="M30" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
         </is>
       </c>
       <c r="N30" s="8" t="inlineStr">
         <is>
-          <t>尼崎</t>
+          <t>川口・千葉</t>
         </is>
       </c>
       <c r="O30" s="17" t="inlineStr">
         <is>
-          <t>https://www.asadatekko.co.jp/</t>
+          <t>https://www.teikokuink.com/</t>
         </is>
       </c>
       <c r="P30" s="7" t="inlineStr">
         <is>
-          <t>本社問合せ</t>
+          <t>IR室</t>
         </is>
       </c>
       <c r="Q30" s="14" t="inlineStr">
@@ -4286,87 +4339,87 @@
       </c>
       <c r="R30" s="8" t="inlineStr">
         <is>
-          <t>②予備混合・③分散の装置</t>
+          <t>UVインキの③分散・⑦充填</t>
         </is>
       </c>
       <c r="S30" s="8" t="inlineStr">
         <is>
-          <t>撹拌機の消費電力・分散時間</t>
-        </is>
-      </c>
-      <c r="T30" s="21" t="n">
-        <v>75</v>
+          <t>UVインキの分散条件・歩留</t>
+        </is>
+      </c>
+      <c r="T30" s="22" t="n">
+        <v>70</v>
       </c>
       <c r="U30" s="8" t="inlineStr">
         <is>
-          <t>技術営業</t>
+          <t>IR / 技術</t>
         </is>
       </c>
       <c r="V30" s="8" t="inlineStr">
         <is>
-          <t>顧客経由</t>
+          <t>印刷業界経由</t>
         </is>
       </c>
       <c r="W30" s="8" t="inlineStr">
         <is>
-          <t>顧客機密</t>
+          <t>塗料との境界線</t>
         </is>
       </c>
       <c r="X30" s="14" t="inlineStr"/>
       <c r="Y30" s="7" t="inlineStr"/>
       <c r="Z30" s="8" t="inlineStr">
         <is>
-          <t>分散・撹拌の補強</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="32" t="n">
+          <t>UV インキ視点の補強</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="68" customHeight="1">
+      <c r="A31" s="28" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="32" t="inlineStr">
-        <is>
-          <t>装置メーカー</t>
+      <c r="B31" s="28" t="inlineStr">
+        <is>
+          <t>UV・印刷インキ</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>日本コークス工業 化工機事業部</t>
+          <t>T&amp;K TOKA</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>東京都江東区</t>
+          <t>埼玉県狭山市</t>
         </is>
       </c>
       <c r="E31" s="14" t="inlineStr">
         <is>
-          <t>東証プライム (本体)</t>
+          <t>東証スタンダード</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>化工機部門 数十億円規模</t>
+          <t>約260億円</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>化工機 数百人</t>
+          <t>約700人(連結)</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>混合・分散・粉砕装置</t>
-        </is>
-      </c>
-      <c r="I31" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J31" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>印刷インキ・UV インキ・コーティング</t>
+        </is>
+      </c>
+      <c r="I31" s="20" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="J31" s="20" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="K31" s="10" t="inlineStr">
@@ -4379,119 +4432,119 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M31" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="M31" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
         </is>
       </c>
       <c r="N31" s="8" t="inlineStr">
         <is>
-          <t>千葉</t>
+          <t>埼玉・大阪</t>
         </is>
       </c>
       <c r="O31" s="17" t="inlineStr">
         <is>
-          <t>https://www.nc-kakouki.co.jp/</t>
+          <t>https://www.tk-toka.co.jp/</t>
         </is>
       </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
-          <t>化工機営業</t>
+          <t>IR室</t>
         </is>
       </c>
       <c r="Q31" s="14" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>中〜高</t>
         </is>
       </c>
       <c r="R31" s="8" t="inlineStr">
         <is>
-          <t>②③④ + 粉体の押出・粉砕</t>
+          <t>UVコーティングの②分散・⑦充填</t>
         </is>
       </c>
       <c r="S31" s="8" t="inlineStr">
         <is>
-          <t>混合・粉砕設備の能力・歩留</t>
+          <t>UV コーティングのドーズ・密着試験</t>
         </is>
       </c>
       <c r="T31" s="22" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="U31" s="8" t="inlineStr">
         <is>
-          <t>営業窓口</t>
+          <t>IR / 技術</t>
         </is>
       </c>
       <c r="V31" s="8" t="inlineStr">
         <is>
-          <t>顧客経由</t>
+          <t>印刷業界経由</t>
         </is>
       </c>
       <c r="W31" s="8" t="inlineStr">
         <is>
-          <t>コークス事業との切り分け</t>
+          <t>塗料との境界が曖昧</t>
         </is>
       </c>
       <c r="X31" s="14" t="inlineStr"/>
       <c r="Y31" s="7" t="inlineStr"/>
       <c r="Z31" s="8" t="inlineStr">
         <is>
-          <t>粉砕・粉体プラントの補強</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="32" t="n">
+          <t>UV コーティング系の補強</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="68" customHeight="1">
+      <c r="A32" s="28" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="32" t="inlineStr">
-        <is>
-          <t>装置メーカー</t>
+      <c r="B32" s="28" t="inlineStr">
+        <is>
+          <t>UV・印刷インキ</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>三井三池製作所 / 寿工業 (粉体塗料用押出機)</t>
+          <t>東洋インキSCホールディングス</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>(各社の本社)</t>
+          <t>東京都中央区</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>(社により異なる)</t>
+          <t>東証プライム</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>粉体設備事業 数十〜100億円</t>
+          <t>約3,400億円(連結)</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>数百人</t>
+          <t>約8,000人(連結)</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>粉体塗料用 押出機・粉砕機</t>
-        </is>
-      </c>
-      <c r="I32" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J32" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K32" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>印刷インキ・コーティング・ポリマー・色材</t>
+        </is>
+      </c>
+      <c r="I32" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J32" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="K32" s="20" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="L32" s="10" t="inlineStr">
@@ -4499,69 +4552,2709 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M32" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="M32" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
         </is>
       </c>
       <c r="N32" s="8" t="inlineStr">
         <is>
-          <t>(社により異なる)</t>
-        </is>
-      </c>
-      <c r="O32" s="7" t="inlineStr">
-        <is>
-          <t>(社により異なる)</t>
+          <t>埼玉・茨城 ほか</t>
+        </is>
+      </c>
+      <c r="O32" s="17" t="inlineStr">
+        <is>
+          <t>https://schd.toyoinkgroup.com/</t>
         </is>
       </c>
       <c r="P32" s="7" t="inlineStr">
         <is>
-          <t>技術営業</t>
+          <t>IR室</t>
         </is>
       </c>
       <c r="Q32" s="14" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="R32" s="8" t="inlineStr">
         <is>
-          <t>粉体塗料の②押出混練 設備設計</t>
+          <t>色材③分散 + UV/水性塗料の②〜⑦</t>
         </is>
       </c>
       <c r="S32" s="8" t="inlineStr">
         <is>
-          <t>押出機消費電力・能力 (t/h)・温度プロファイル</t>
-        </is>
-      </c>
-      <c r="T32" s="22" t="n">
-        <v>70</v>
+          <t>顔料分散のスケール、ポリマー設計</t>
+        </is>
+      </c>
+      <c r="T32" s="21" t="n">
+        <v>82</v>
       </c>
       <c r="U32" s="8" t="inlineStr">
         <is>
-          <t>技術営業</t>
+          <t>IR / 技術部門</t>
         </is>
       </c>
       <c r="V32" s="8" t="inlineStr">
         <is>
-          <t>粉体塗料メーカー経由</t>
+          <t>印刷インキ業界経由</t>
         </is>
       </c>
       <c r="W32" s="8" t="inlineStr">
         <is>
-          <t>粉体専門領域に絞った会話に</t>
+          <t>塗料はグループ事業の一部</t>
         </is>
       </c>
       <c r="X32" s="14" t="inlineStr"/>
       <c r="Y32" s="7" t="inlineStr"/>
       <c r="Z32" s="8" t="inlineStr">
         <is>
-          <t>粉体製造装置の補強</t>
+          <t>インキ大手の塗料領域比較対象</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="68" customHeight="1">
+      <c r="A33" s="28" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="28" t="inlineStr">
+        <is>
+          <t>UV・印刷インキ</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>サカタインクス</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>大阪市西区</t>
+        </is>
+      </c>
+      <c r="E33" s="14" t="inlineStr">
+        <is>
+          <t>東証プライム</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>約1,700億円(連結)</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>約4,000人(連結)</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>印刷インキ・UV インキ・コーティング</t>
+        </is>
+      </c>
+      <c r="I33" s="20" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="J33" s="20" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="K33" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L33" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M33" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="N33" s="8" t="inlineStr">
+        <is>
+          <t>大阪・東京 ほか</t>
+        </is>
+      </c>
+      <c r="O33" s="17" t="inlineStr">
+        <is>
+          <t>https://www.inx.co.jp/</t>
+        </is>
+      </c>
+      <c r="P33" s="7" t="inlineStr">
+        <is>
+          <t>IR室</t>
+        </is>
+      </c>
+      <c r="Q33" s="14" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="R33" s="8" t="inlineStr">
+        <is>
+          <t>UVインキの②分散・⑤ろ過・⑦充填</t>
+        </is>
+      </c>
+      <c r="S33" s="8" t="inlineStr">
+        <is>
+          <t>印刷インキ生産の歩留・廃棄物</t>
+        </is>
+      </c>
+      <c r="T33" s="21" t="n">
+        <v>75</v>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>IR / 技術</t>
+        </is>
+      </c>
+      <c r="V33" s="8" t="inlineStr">
+        <is>
+          <t>印刷業界経由</t>
+        </is>
+      </c>
+      <c r="W33" s="8" t="inlineStr">
+        <is>
+          <t>塗料事業は限定的</t>
+        </is>
+      </c>
+      <c r="X33" s="14" t="inlineStr"/>
+      <c r="Y33" s="7" t="inlineStr"/>
+      <c r="Z33" s="8" t="inlineStr">
+        <is>
+          <t>インキ大手の比較材料</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="68" customHeight="1">
+      <c r="A34" s="28" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="28" t="inlineStr">
+        <is>
+          <t>UV・印刷インキ</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>オリジン</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>東京都板橋区</t>
+        </is>
+      </c>
+      <c r="E34" s="14" t="inlineStr">
+        <is>
+          <t>東証スタンダード</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>約260億円</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>約800人(連結)</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>UV 塗料・電着・電子用塗料</t>
+        </is>
+      </c>
+      <c r="I34" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J34" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="K34" s="20" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="L34" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="M34" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="N34" s="8" t="inlineStr">
+        <is>
+          <t>東京・神奈川</t>
+        </is>
+      </c>
+      <c r="O34" s="17" t="inlineStr">
+        <is>
+          <t>https://www.origin.co.jp/</t>
+        </is>
+      </c>
+      <c r="P34" s="7" t="inlineStr">
+        <is>
+          <t>IR室</t>
+        </is>
+      </c>
+      <c r="Q34" s="14" t="inlineStr">
+        <is>
+          <t>中〜高</t>
+        </is>
+      </c>
+      <c r="R34" s="8" t="inlineStr">
+        <is>
+          <t>UV・電着塗料の②③⑤⑦</t>
+        </is>
+      </c>
+      <c r="S34" s="8" t="inlineStr">
+        <is>
+          <t>UV ドーズ管理、電着の電気伝導度</t>
+        </is>
+      </c>
+      <c r="T34" s="21" t="n">
+        <v>80</v>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>IR / 技術</t>
+        </is>
+      </c>
+      <c r="V34" s="8" t="inlineStr">
+        <is>
+          <t>電子業界経由</t>
+        </is>
+      </c>
+      <c r="W34" s="8" t="inlineStr">
+        <is>
+          <t>電気事業との切り分け</t>
+        </is>
+      </c>
+      <c r="X34" s="14" t="inlineStr"/>
+      <c r="Y34" s="7" t="inlineStr"/>
+      <c r="Z34" s="8" t="inlineStr">
+        <is>
+          <t>UV と電着の双方を持つ稀少例</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="68" customHeight="1">
+      <c r="A35" s="28" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="28" t="inlineStr">
+        <is>
+          <t>UV・印刷インキ</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>DICグラフィックス</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>東京都中央区</t>
+        </is>
+      </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>非上場(DIC子会社)</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>約2,000億円規模(推定)</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>約3,000人</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>印刷インキ・UV・特殊インキ</t>
+        </is>
+      </c>
+      <c r="I35" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J35" s="20" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="K35" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L35" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M35" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="N35" s="8" t="inlineStr">
+        <is>
+          <t>千葉・滋賀 ほか</t>
+        </is>
+      </c>
+      <c r="O35" s="17" t="inlineStr">
+        <is>
+          <t>https://www.dic-graphics.co.jp/</t>
+        </is>
+      </c>
+      <c r="P35" s="7" t="inlineStr">
+        <is>
+          <t>DIC IR経由</t>
+        </is>
+      </c>
+      <c r="Q35" s="14" t="inlineStr">
+        <is>
+          <t>中〜高 (DIC連結に含む)</t>
+        </is>
+      </c>
+      <c r="R35" s="8" t="inlineStr">
+        <is>
+          <t>UV/水性インキの②③⑦</t>
+        </is>
+      </c>
+      <c r="S35" s="8" t="inlineStr">
+        <is>
+          <t>印刷インキの大量生産工程</t>
+        </is>
+      </c>
+      <c r="T35" s="22" t="n">
+        <v>72</v>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>親会社(DIC) 経由</t>
+        </is>
+      </c>
+      <c r="V35" s="8" t="inlineStr">
+        <is>
+          <t>印刷業界経由</t>
+        </is>
+      </c>
+      <c r="W35" s="8" t="inlineStr">
+        <is>
+          <t>塗料との境界が曖昧</t>
+        </is>
+      </c>
+      <c r="X35" s="14" t="inlineStr"/>
+      <c r="Y35" s="7" t="inlineStr"/>
+      <c r="Z35" s="8" t="inlineStr">
+        <is>
+          <t>DIC系のインキ生産規模感</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="68" customHeight="1">
+      <c r="A36" s="28" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="28" t="inlineStr">
+        <is>
+          <t>UV・印刷インキ</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>トウペ</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>大阪市平野区</t>
+        </is>
+      </c>
+      <c r="E36" s="14" t="inlineStr">
+        <is>
+          <t>非上場</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>約120億円規模(推定)</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>約400人</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>工業用塗料・UV 塗料・電子部品向け</t>
+        </is>
+      </c>
+      <c r="I36" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J36" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="K36" s="20" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="L36" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M36" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="N36" s="8" t="inlineStr">
+        <is>
+          <t>大阪・栃木</t>
+        </is>
+      </c>
+      <c r="O36" s="17" t="inlineStr">
+        <is>
+          <t>https://www.toupe.co.jp/</t>
+        </is>
+      </c>
+      <c r="P36" s="7" t="inlineStr">
+        <is>
+          <t>本社問合せ</t>
+        </is>
+      </c>
+      <c r="Q36" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="R36" s="8" t="inlineStr">
+        <is>
+          <t>工業用塗料の②③④, UV ⑤⑦</t>
+        </is>
+      </c>
+      <c r="S36" s="8" t="inlineStr">
+        <is>
+          <t>電子向け工業塗料の小ロット運用</t>
+        </is>
+      </c>
+      <c r="T36" s="22" t="n">
+        <v>65</v>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>営業・技術</t>
+        </is>
+      </c>
+      <c r="V36" s="8" t="inlineStr">
+        <is>
+          <t>電子・自動車部品業界経由</t>
+        </is>
+      </c>
+      <c r="W36" s="8" t="inlineStr">
+        <is>
+          <t>ニッチ工業塗料は機密性高</t>
+        </is>
+      </c>
+      <c r="X36" s="14" t="inlineStr"/>
+      <c r="Y36" s="7" t="inlineStr"/>
+      <c r="Z36" s="8" t="inlineStr">
+        <is>
+          <t>工業×UVの中堅事例</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="68" customHeight="1">
+      <c r="A37" s="29" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="29" t="inlineStr">
+        <is>
+          <t>DIY・小口</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>アサヒペン</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>大阪市鶴見区</t>
+        </is>
+      </c>
+      <c r="E37" s="14" t="inlineStr">
+        <is>
+          <t>非上場</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>約280億円規模(推定)</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>約600人</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>DIY・小口・ホームセンター</t>
+        </is>
+      </c>
+      <c r="I37" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="J37" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="K37" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L37" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M37" s="20" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="N37" s="8" t="inlineStr">
+        <is>
+          <t>大阪・茨城</t>
+        </is>
+      </c>
+      <c r="O37" s="17" t="inlineStr">
+        <is>
+          <t>https://www.asahipen.jp/</t>
+        </is>
+      </c>
+      <c r="P37" s="7" t="inlineStr">
+        <is>
+          <t>本社問合せ</t>
+        </is>
+      </c>
+      <c r="Q37" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="R37" s="8" t="inlineStr">
+        <is>
+          <t>小容量缶(1L/4L)の⑧充填・⑨保管</t>
+        </is>
+      </c>
+      <c r="S37" s="8" t="inlineStr">
+        <is>
+          <t>小容量充填のスループット・歩留</t>
+        </is>
+      </c>
+      <c r="T37" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>営業窓口</t>
+        </is>
+      </c>
+      <c r="V37" s="8" t="inlineStr">
+        <is>
+          <t>ホームセンター経由</t>
+        </is>
+      </c>
+      <c r="W37" s="8" t="inlineStr">
+        <is>
+          <t>プロ向けと差別化必要</t>
+        </is>
+      </c>
+      <c r="X37" s="14" t="inlineStr"/>
+      <c r="Y37" s="7" t="inlineStr"/>
+      <c r="Z37" s="8" t="inlineStr">
+        <is>
+          <t>DIY 流通の代表</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="68" customHeight="1">
+      <c r="A38" s="29" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="29" t="inlineStr">
+        <is>
+          <t>DIY・小口</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>カンペハピオ</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>大阪市東淀川区</t>
+        </is>
+      </c>
+      <c r="E38" s="14" t="inlineStr">
+        <is>
+          <t>非上場(関ペ系列)</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>数百億円規模</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>数百人</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>DIY・ホームセンター・小口</t>
+        </is>
+      </c>
+      <c r="I38" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="J38" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="K38" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L38" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M38" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="8" t="inlineStr">
+        <is>
+          <t>大阪・関ペ工場併設</t>
+        </is>
+      </c>
+      <c r="O38" s="17" t="inlineStr">
+        <is>
+          <t>https://www.kanpe.co.jp/</t>
+        </is>
+      </c>
+      <c r="P38" s="7" t="inlineStr">
+        <is>
+          <t>関ペ広報経由</t>
+        </is>
+      </c>
+      <c r="Q38" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="R38" s="8" t="inlineStr">
+        <is>
+          <t>DIY 缶の⑤調色・⑧充填</t>
+        </is>
+      </c>
+      <c r="S38" s="8" t="inlineStr">
+        <is>
+          <t>小容量缶のSKU・色種数・回転</t>
+        </is>
+      </c>
+      <c r="T38" s="25" t="n">
+        <v>58</v>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>親会社(関ペ) 経由</t>
+        </is>
+      </c>
+      <c r="V38" s="8" t="inlineStr">
+        <is>
+          <t>ホームセンター業界経由</t>
+        </is>
+      </c>
+      <c r="W38" s="8" t="inlineStr">
+        <is>
+          <t>親会社の方針に従う</t>
+        </is>
+      </c>
+      <c r="X38" s="14" t="inlineStr"/>
+      <c r="Y38" s="7" t="inlineStr"/>
+      <c r="Z38" s="8" t="inlineStr">
+        <is>
+          <t>DIY 流通の補強</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="68" customHeight="1">
+      <c r="A39" s="29" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="29" t="inlineStr">
+        <is>
+          <t>DIY・小口</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>ニッペホームプロダクツ</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>東京都北区</t>
+        </is>
+      </c>
+      <c r="E39" s="14" t="inlineStr">
+        <is>
+          <t>非上場(日ペ系列)</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>数百億円規模</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>数百人</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>DIY・小口・ホームセンター</t>
+        </is>
+      </c>
+      <c r="I39" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="J39" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="K39" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L39" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M39" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="8" t="inlineStr">
+        <is>
+          <t>東京・関東</t>
+        </is>
+      </c>
+      <c r="O39" s="17" t="inlineStr">
+        <is>
+          <t>https://www.nippehome.co.jp/</t>
+        </is>
+      </c>
+      <c r="P39" s="7" t="inlineStr">
+        <is>
+          <t>日ペ広報経由</t>
+        </is>
+      </c>
+      <c r="Q39" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="R39" s="8" t="inlineStr">
+        <is>
+          <t>DIY 缶の⑤調色・⑧充填</t>
+        </is>
+      </c>
+      <c r="S39" s="8" t="inlineStr">
+        <is>
+          <t>DIY SKU・小容量充填</t>
+        </is>
+      </c>
+      <c r="T39" s="25" t="n">
+        <v>58</v>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>親会社(日ペHD) 経由</t>
+        </is>
+      </c>
+      <c r="V39" s="8" t="inlineStr">
+        <is>
+          <t>ホームセンター業界経由</t>
+        </is>
+      </c>
+      <c r="W39" s="8" t="inlineStr">
+        <is>
+          <t>親会社の方針に従う</t>
+        </is>
+      </c>
+      <c r="X39" s="14" t="inlineStr"/>
+      <c r="Y39" s="7" t="inlineStr"/>
+      <c r="Z39" s="8" t="inlineStr">
+        <is>
+          <t>DIY 流通の補強(日ペ系)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="68" customHeight="1">
+      <c r="A40" s="30" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="30" t="inlineStr">
+        <is>
+          <t>日ペグループ</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>日本ペイント・オートモーティブコーティングス</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>大阪市北区(日ペHD系)</t>
+        </is>
+      </c>
+      <c r="E40" s="14" t="inlineStr">
+        <is>
+          <t>非上場(子会社)</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>日ペHD連結内</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>数千人(日ペ系列)</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>自動車OEM 塗料 (世界トップクラス)</t>
+        </is>
+      </c>
+      <c r="I40" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J40" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="K40" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L40" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="M40" s="20" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="N40" s="8" t="inlineStr">
+        <is>
+          <t>東京・愛知・大阪</t>
+        </is>
+      </c>
+      <c r="O40" s="17" t="inlineStr">
+        <is>
+          <t>https://www.nipponpaint-automotive.com/</t>
+        </is>
+      </c>
+      <c r="P40" s="7" t="inlineStr">
+        <is>
+          <t>日ペHD IR経由</t>
+        </is>
+      </c>
+      <c r="Q40" s="14" t="inlineStr">
+        <is>
+          <t>中 (親会社IRに含む)</t>
+        </is>
+      </c>
+      <c r="R40" s="8" t="inlineStr">
+        <is>
+          <t>OEM 向け電着・中塗り・上塗りの①〜⑥</t>
+        </is>
+      </c>
+      <c r="S40" s="8" t="inlineStr">
+        <is>
+          <t>OEM JIT配送、塗着効率、CCM</t>
+        </is>
+      </c>
+      <c r="T40" s="18" t="n">
+        <v>92</v>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>親会社(日ペHD) 経由</t>
+        </is>
+      </c>
+      <c r="V40" s="8" t="inlineStr">
+        <is>
+          <t>自動車OEM経由</t>
+        </is>
+      </c>
+      <c r="W40" s="8" t="inlineStr">
+        <is>
+          <t>親会社の方針に従う</t>
+        </is>
+      </c>
+      <c r="X40" s="14" t="inlineStr"/>
+      <c r="Y40" s="7" t="inlineStr"/>
+      <c r="Z40" s="8" t="inlineStr">
+        <is>
+          <t>自動車OEM の最重要</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="68" customHeight="1">
+      <c r="A41" s="30" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="30" t="inlineStr">
+        <is>
+          <t>日ペグループ</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>日本ペイント・インダストリアルコーティングス</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>大阪市北区(日ペHD系)</t>
+        </is>
+      </c>
+      <c r="E41" s="14" t="inlineStr">
+        <is>
+          <t>非上場(子会社)</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>日ペHD連結内</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>数千人</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>工業・電着・特殊塗料</t>
+        </is>
+      </c>
+      <c r="I41" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J41" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="K41" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L41" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="M41" s="20" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="N41" s="8" t="inlineStr">
+        <is>
+          <t>東京・愛知・大阪</t>
+        </is>
+      </c>
+      <c r="O41" s="17" t="inlineStr">
+        <is>
+          <t>https://www.nipponpaint-industrialcoatings.co.jp/</t>
+        </is>
+      </c>
+      <c r="P41" s="7" t="inlineStr">
+        <is>
+          <t>日ペHD IR経由</t>
+        </is>
+      </c>
+      <c r="Q41" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="R41" s="8" t="inlineStr">
+        <is>
+          <t>工業塗料 ①〜⑨, 電着の特殊工程</t>
+        </is>
+      </c>
+      <c r="S41" s="8" t="inlineStr">
+        <is>
+          <t>電着MEQ・UF・塗着効率、工業ライン</t>
+        </is>
+      </c>
+      <c r="T41" s="18" t="n">
+        <v>88</v>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t>親会社経由</t>
+        </is>
+      </c>
+      <c r="V41" s="8" t="inlineStr">
+        <is>
+          <t>工業顧客経由</t>
+        </is>
+      </c>
+      <c r="W41" s="8" t="inlineStr">
+        <is>
+          <t>親会社の方針に従う</t>
+        </is>
+      </c>
+      <c r="X41" s="14" t="inlineStr"/>
+      <c r="Y41" s="7" t="inlineStr"/>
+      <c r="Z41" s="8" t="inlineStr">
+        <is>
+          <t>電着・工業の最重要</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="68" customHeight="1">
+      <c r="A42" s="30" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="30" t="inlineStr">
+        <is>
+          <t>日ペグループ</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>日本ペイントマリン</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>兵庫県神戸市(日ペHD系)</t>
+        </is>
+      </c>
+      <c r="E42" s="14" t="inlineStr">
+        <is>
+          <t>非上場(子会社)</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>日ペHD連結内</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>数千人</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>船舶用塗料</t>
+        </is>
+      </c>
+      <c r="I42" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="J42" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="K42" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L42" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M42" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="8" t="inlineStr">
+        <is>
+          <t>兵庫・愛媛</t>
+        </is>
+      </c>
+      <c r="O42" s="17" t="inlineStr">
+        <is>
+          <t>https://www.nipponpaint-marine.com/</t>
+        </is>
+      </c>
+      <c r="P42" s="7" t="inlineStr">
+        <is>
+          <t>日ペHD IR経由</t>
+        </is>
+      </c>
+      <c r="Q42" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="R42" s="8" t="inlineStr">
+        <is>
+          <t>船舶塗料の③④(防汚機能の分散)</t>
+        </is>
+      </c>
+      <c r="S42" s="8" t="inlineStr">
+        <is>
+          <t>防汚剤・低摩擦塗料の組成</t>
+        </is>
+      </c>
+      <c r="T42" s="21" t="n">
+        <v>78</v>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t>親会社経由</t>
+        </is>
+      </c>
+      <c r="V42" s="8" t="inlineStr">
+        <is>
+          <t>造船業界経由</t>
+        </is>
+      </c>
+      <c r="W42" s="8" t="inlineStr">
+        <is>
+          <t>中国塗料・関ペマリンと競合</t>
+        </is>
+      </c>
+      <c r="X42" s="14" t="inlineStr"/>
+      <c r="Y42" s="7" t="inlineStr"/>
+      <c r="Z42" s="8" t="inlineStr">
+        <is>
+          <t>船舶塗料の比較対象</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="68" customHeight="1">
+      <c r="A43" s="30" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="30" t="inlineStr">
+        <is>
+          <t>日ペグループ</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>日本ペイント・サーフケミカルズ</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>大阪市北区(日ペHD系)</t>
+        </is>
+      </c>
+      <c r="E43" s="14" t="inlineStr">
+        <is>
+          <t>非上場(子会社)</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>日ペHD連結内</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>数百人</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t>表面処理薬剤(塗装前処理)</t>
+        </is>
+      </c>
+      <c r="I43" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J43" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="K43" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L43" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M43" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="8" t="inlineStr">
+        <is>
+          <t>東京・大阪</t>
+        </is>
+      </c>
+      <c r="O43" s="17" t="inlineStr">
+        <is>
+          <t>https://www.nipponpaint-surf.co.jp/</t>
+        </is>
+      </c>
+      <c r="P43" s="7" t="inlineStr">
+        <is>
+          <t>日ペHD IR経由</t>
+        </is>
+      </c>
+      <c r="Q43" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="R43" s="8" t="inlineStr">
+        <is>
+          <t>塗装前処理薬剤の③配合・⑤希釈</t>
+        </is>
+      </c>
+      <c r="S43" s="8" t="inlineStr">
+        <is>
+          <t>前処理薬剤の濃度管理、リンス回収</t>
+        </is>
+      </c>
+      <c r="T43" s="22" t="n">
+        <v>68</v>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>親会社経由</t>
+        </is>
+      </c>
+      <c r="V43" s="8" t="inlineStr">
+        <is>
+          <t>OEM・工業顧客経由</t>
+        </is>
+      </c>
+      <c r="W43" s="8" t="inlineStr">
+        <is>
+          <t>塗料本体ではなく前処理特化</t>
+        </is>
+      </c>
+      <c r="X43" s="14" t="inlineStr"/>
+      <c r="Y43" s="7" t="inlineStr"/>
+      <c r="Z43" s="8" t="inlineStr">
+        <is>
+          <t>前処理工程の補強</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="68" customHeight="1">
+      <c r="A44" s="30" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="30" t="inlineStr">
+        <is>
+          <t>日ペグループ</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>ニッペ・オートリフィニッシュ</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>大阪市北区(日ペHD系)</t>
+        </is>
+      </c>
+      <c r="E44" s="14" t="inlineStr">
+        <is>
+          <t>非上場(子会社)</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>日ペHD連結内</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>数百人</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>自動車補修塗料</t>
+        </is>
+      </c>
+      <c r="I44" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="J44" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="K44" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L44" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M44" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="8" t="inlineStr">
+        <is>
+          <t>東京・大阪</t>
+        </is>
+      </c>
+      <c r="O44" s="17" t="inlineStr">
+        <is>
+          <t>https://www.nipponpaint-autorefinish.com/</t>
+        </is>
+      </c>
+      <c r="P44" s="7" t="inlineStr">
+        <is>
+          <t>日ペHD IR経由</t>
+        </is>
+      </c>
+      <c r="Q44" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="R44" s="8" t="inlineStr">
+        <is>
+          <t>補修塗料の④⑤調色・⑧充填</t>
+        </is>
+      </c>
+      <c r="S44" s="8" t="inlineStr">
+        <is>
+          <t>小ロット補修の歩留、CCM</t>
+        </is>
+      </c>
+      <c r="T44" s="21" t="n">
+        <v>75</v>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>親会社経由</t>
+        </is>
+      </c>
+      <c r="V44" s="8" t="inlineStr">
+        <is>
+          <t>板金塗装業界経由</t>
+        </is>
+      </c>
+      <c r="W44" s="8" t="inlineStr">
+        <is>
+          <t>ロックペイント・イサムと競合</t>
+        </is>
+      </c>
+      <c r="X44" s="14" t="inlineStr"/>
+      <c r="Y44" s="7" t="inlineStr"/>
+      <c r="Z44" s="8" t="inlineStr">
+        <is>
+          <t>自動車補修の比較対象</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="68" customHeight="1">
+      <c r="A45" s="31" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="31" t="inlineStr">
+        <is>
+          <t>関ペグループ</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>関西ペイントマリン</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>大阪市中央区(関ペ系)</t>
+        </is>
+      </c>
+      <c r="E45" s="14" t="inlineStr">
+        <is>
+          <t>非上場(関ペ系)</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>関ペ連結内</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>数百人</t>
+        </is>
+      </c>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>船舶用塗料</t>
+        </is>
+      </c>
+      <c r="I45" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="J45" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="K45" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L45" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M45" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="8" t="inlineStr">
+        <is>
+          <t>大阪・神奈川</t>
+        </is>
+      </c>
+      <c r="O45" s="17" t="inlineStr">
+        <is>
+          <t>https://www.kansaipaint-marine.com/</t>
+        </is>
+      </c>
+      <c r="P45" s="7" t="inlineStr">
+        <is>
+          <t>関ペ広報経由</t>
+        </is>
+      </c>
+      <c r="Q45" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="R45" s="8" t="inlineStr">
+        <is>
+          <t>船舶塗料の③④(防汚機能の分散)</t>
+        </is>
+      </c>
+      <c r="S45" s="8" t="inlineStr">
+        <is>
+          <t>防汚剤管理、厚膜塗装</t>
+        </is>
+      </c>
+      <c r="T45" s="21" t="n">
+        <v>76</v>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>親会社経由</t>
+        </is>
+      </c>
+      <c r="V45" s="8" t="inlineStr">
+        <is>
+          <t>造船業界経由</t>
+        </is>
+      </c>
+      <c r="W45" s="8" t="inlineStr">
+        <is>
+          <t>中国塗料・日ペマリンと競合</t>
+        </is>
+      </c>
+      <c r="X45" s="14" t="inlineStr"/>
+      <c r="Y45" s="7" t="inlineStr"/>
+      <c r="Z45" s="8" t="inlineStr">
+        <is>
+          <t>船舶塗料の比較対象</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="68" customHeight="1">
+      <c r="A46" s="32" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="32" t="inlineStr">
+        <is>
+          <t>外資系・日本法人</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>PPGコーティングスジャパン</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>大阪市住之江区</t>
+        </is>
+      </c>
+      <c r="E46" s="14" t="inlineStr">
+        <is>
+          <t>非上場(米PPG子会社)</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>PPG 連結内</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>数千人(日本)</t>
+        </is>
+      </c>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>自動車補修・工業・航空・船舶</t>
+        </is>
+      </c>
+      <c r="I46" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="J46" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="K46" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L46" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="M46" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="N46" s="8" t="inlineStr">
+        <is>
+          <t>大阪・愛知 ほか</t>
+        </is>
+      </c>
+      <c r="O46" s="17" t="inlineStr">
+        <is>
+          <t>https://www.ppgpaint.jp/</t>
+        </is>
+      </c>
+      <c r="P46" s="7" t="inlineStr">
+        <is>
+          <t>本社問合せ</t>
+        </is>
+      </c>
+      <c r="Q46" s="14" t="inlineStr">
+        <is>
+          <t>中 (米親会社IRに開示あり)</t>
+        </is>
+      </c>
+      <c r="R46" s="8" t="inlineStr">
+        <is>
+          <t>OEM・補修・工業塗料の①〜⑦</t>
+        </is>
+      </c>
+      <c r="S46" s="8" t="inlineStr">
+        <is>
+          <t>グローバル標準と日本現場のギャップ</t>
+        </is>
+      </c>
+      <c r="T46" s="21" t="n">
+        <v>82</v>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>技術部門 / 営業</t>
+        </is>
+      </c>
+      <c r="V46" s="8" t="inlineStr">
+        <is>
+          <t>OEM・補修・工業経由</t>
+        </is>
+      </c>
+      <c r="W46" s="8" t="inlineStr">
+        <is>
+          <t>親会社の方針に従う・グローバル機密</t>
+        </is>
+      </c>
+      <c r="X46" s="14" t="inlineStr"/>
+      <c r="Y46" s="7" t="inlineStr"/>
+      <c r="Z46" s="8" t="inlineStr">
+        <is>
+          <t>外資系の代表</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="68" customHeight="1">
+      <c r="A47" s="32" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="32" t="inlineStr">
+        <is>
+          <t>外資系・日本法人</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>アクゾノーベル・ジャパン</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>東京都港区</t>
+        </is>
+      </c>
+      <c r="E47" s="14" t="inlineStr">
+        <is>
+          <t>非上場(蘭AkzoNobel子会社)</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>AkzoNobel連結内</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>数百人(日本)</t>
+        </is>
+      </c>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>建築・船舶・工業・粉体</t>
+        </is>
+      </c>
+      <c r="I47" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="J47" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="K47" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="L47" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="M47" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="N47" s="8" t="inlineStr">
+        <is>
+          <t>東京・大阪 ほか</t>
+        </is>
+      </c>
+      <c r="O47" s="17" t="inlineStr">
+        <is>
+          <t>https://www.akzonobel.com/ja/</t>
+        </is>
+      </c>
+      <c r="P47" s="7" t="inlineStr">
+        <is>
+          <t>本社問合せ</t>
+        </is>
+      </c>
+      <c r="Q47" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="R47" s="8" t="inlineStr">
+        <is>
+          <t>粉体・水性建築塗料の②〜⑦</t>
+        </is>
+      </c>
+      <c r="S47" s="8" t="inlineStr">
+        <is>
+          <t>粉体グローバル標準の歩留・能力</t>
+        </is>
+      </c>
+      <c r="T47" s="21" t="n">
+        <v>78</v>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>技術部門 / 営業</t>
+        </is>
+      </c>
+      <c r="V47" s="8" t="inlineStr">
+        <is>
+          <t>業界団体・OEM経由</t>
+        </is>
+      </c>
+      <c r="W47" s="8" t="inlineStr">
+        <is>
+          <t>親会社方針・グローバル機密</t>
+        </is>
+      </c>
+      <c r="X47" s="14" t="inlineStr"/>
+      <c r="Y47" s="7" t="inlineStr"/>
+      <c r="Z47" s="8" t="inlineStr">
+        <is>
+          <t>粉体の世界トップの日本拠点</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="68" customHeight="1">
+      <c r="A48" s="32" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="32" t="inlineStr">
+        <is>
+          <t>外資系・日本法人</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>シャーウィン・ウィリアムズ・ジャパン</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="E48" s="14" t="inlineStr">
+        <is>
+          <t>非上場(米SW子会社)</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>SW連結内</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>数百人(日本)</t>
+        </is>
+      </c>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>建築・工業・自動車補修</t>
+        </is>
+      </c>
+      <c r="I48" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J48" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="K48" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L48" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="M48" s="20" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="N48" s="8" t="inlineStr">
+        <is>
+          <t>(要確認)</t>
+        </is>
+      </c>
+      <c r="O48" s="17" t="inlineStr">
+        <is>
+          <t>https://www.sherwin-williams.com/</t>
+        </is>
+      </c>
+      <c r="P48" s="7" t="inlineStr">
+        <is>
+          <t>本社問合せ</t>
+        </is>
+      </c>
+      <c r="Q48" s="24" t="inlineStr">
+        <is>
+          <t>低〜中 (要確認)</t>
+        </is>
+      </c>
+      <c r="R48" s="8" t="inlineStr">
+        <is>
+          <t>建築塗料 (米国基準) と日本基準の比較</t>
+        </is>
+      </c>
+      <c r="S48" s="8" t="inlineStr">
+        <is>
+          <t>米国基準塗料の日本現場運用</t>
+        </is>
+      </c>
+      <c r="T48" s="22" t="n">
+        <v>70</v>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>本社経由</t>
+        </is>
+      </c>
+      <c r="V48" s="8" t="inlineStr">
+        <is>
+          <t>(限定的)</t>
+        </is>
+      </c>
+      <c r="W48" s="8" t="inlineStr">
+        <is>
+          <t>事業規模は要確認</t>
+        </is>
+      </c>
+      <c r="X48" s="14" t="inlineStr"/>
+      <c r="Y48" s="7" t="inlineStr"/>
+      <c r="Z48" s="8" t="inlineStr">
+        <is>
+          <t>外資建築塗料の参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="68" customHeight="1">
+      <c r="A49" s="32" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="32" t="inlineStr">
+        <is>
+          <t>外資系・日本法人</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>アクサルタコーティングシステムズ・ジャパン</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>横浜市</t>
+        </is>
+      </c>
+      <c r="E49" s="14" t="inlineStr">
+        <is>
+          <t>非上場(米Axalta子会社)</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>Axalta連結内</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>数百人(日本)</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>自動車OEM・補修・工業</t>
+        </is>
+      </c>
+      <c r="I49" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="J49" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="K49" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L49" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="M49" s="20" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="N49" s="8" t="inlineStr">
+        <is>
+          <t>横浜・大阪</t>
+        </is>
+      </c>
+      <c r="O49" s="17" t="inlineStr">
+        <is>
+          <t>https://www.axalta.com/jp/</t>
+        </is>
+      </c>
+      <c r="P49" s="7" t="inlineStr">
+        <is>
+          <t>本社問合せ</t>
+        </is>
+      </c>
+      <c r="Q49" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="R49" s="8" t="inlineStr">
+        <is>
+          <t>OEM・補修・電着の①〜⑥</t>
+        </is>
+      </c>
+      <c r="S49" s="8" t="inlineStr">
+        <is>
+          <t>電着のグローバル標準、OEM JIT</t>
+        </is>
+      </c>
+      <c r="T49" s="21" t="n">
+        <v>78</v>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>技術部門 / 営業</t>
+        </is>
+      </c>
+      <c r="V49" s="8" t="inlineStr">
+        <is>
+          <t>OEM・補修経由</t>
+        </is>
+      </c>
+      <c r="W49" s="8" t="inlineStr">
+        <is>
+          <t>親会社方針・グローバル機密</t>
+        </is>
+      </c>
+      <c r="X49" s="14" t="inlineStr"/>
+      <c r="Y49" s="7" t="inlineStr"/>
+      <c r="Z49" s="8" t="inlineStr">
+        <is>
+          <t>電着・OEM の外資比較対象</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="68" customHeight="1">
+      <c r="A50" s="32" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="32" t="inlineStr">
+        <is>
+          <t>外資系・日本法人</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>BASFジャパン コーティングス事業</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>東京都中央区</t>
+        </is>
+      </c>
+      <c r="E50" s="14" t="inlineStr">
+        <is>
+          <t>非上場(独BASF子会社)</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>BASF Coatings連結内</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>数百人(日本)</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>自動車OEM・補修・特殊</t>
+        </is>
+      </c>
+      <c r="I50" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="J50" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="K50" s="20" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="L50" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="M50" s="20" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="N50" s="8" t="inlineStr">
+        <is>
+          <t>(要確認・事業再編動向あり)</t>
+        </is>
+      </c>
+      <c r="O50" s="17" t="inlineStr">
+        <is>
+          <t>https://www.basf-coatings.com/</t>
+        </is>
+      </c>
+      <c r="P50" s="7" t="inlineStr">
+        <is>
+          <t>本社問合せ</t>
+        </is>
+      </c>
+      <c r="Q50" s="24" t="inlineStr">
+        <is>
+          <t>低〜中 (事業再編動向で要確認)</t>
+        </is>
+      </c>
+      <c r="R50" s="8" t="inlineStr">
+        <is>
+          <t>OEM 塗料の①〜⑥</t>
+        </is>
+      </c>
+      <c r="S50" s="8" t="inlineStr">
+        <is>
+          <t>OEM 塗料の高機能化動向</t>
+        </is>
+      </c>
+      <c r="T50" s="22" t="n">
+        <v>72</v>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>本社経由</t>
+        </is>
+      </c>
+      <c r="V50" s="8" t="inlineStr">
+        <is>
+          <t>自動車OEM経由</t>
+        </is>
+      </c>
+      <c r="W50" s="8" t="inlineStr">
+        <is>
+          <t>コーティング事業の売却動向 (2024〜) に注意</t>
+        </is>
+      </c>
+      <c r="X50" s="14" t="inlineStr"/>
+      <c r="Y50" s="7" t="inlineStr"/>
+      <c r="Z50" s="8" t="inlineStr">
+        <is>
+          <t>事業再編動向の継続確認が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="68" customHeight="1">
+      <c r="A51" s="32" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="32" t="inlineStr">
+        <is>
+          <t>外資系・日本法人</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>ヘンペル・ジャパン</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>横浜市</t>
+        </is>
+      </c>
+      <c r="E51" s="14" t="inlineStr">
+        <is>
+          <t>非上場(デンマークHempel子会社)</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>Hempel連結内</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>数十人(日本)</t>
+        </is>
+      </c>
+      <c r="H51" s="8" t="inlineStr">
+        <is>
+          <t>船舶・防食・コンテナ用塗料</t>
+        </is>
+      </c>
+      <c r="I51" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="J51" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="K51" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L51" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M51" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="8" t="inlineStr">
+        <is>
+          <t>横浜</t>
+        </is>
+      </c>
+      <c r="O51" s="17" t="inlineStr">
+        <is>
+          <t>https://www.hempel.com/ja-jp/</t>
+        </is>
+      </c>
+      <c r="P51" s="7" t="inlineStr">
+        <is>
+          <t>本社問合せ</t>
+        </is>
+      </c>
+      <c r="Q51" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="R51" s="8" t="inlineStr">
+        <is>
+          <t>船舶塗料の③④</t>
+        </is>
+      </c>
+      <c r="S51" s="8" t="inlineStr">
+        <is>
+          <t>船舶塗料グローバル標準</t>
+        </is>
+      </c>
+      <c r="T51" s="22" t="n">
+        <v>65</v>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>本社経由</t>
+        </is>
+      </c>
+      <c r="V51" s="8" t="inlineStr">
+        <is>
+          <t>造船・港湾経由</t>
+        </is>
+      </c>
+      <c r="W51" s="8" t="inlineStr">
+        <is>
+          <t>本社方針優先</t>
+        </is>
+      </c>
+      <c r="X51" s="14" t="inlineStr"/>
+      <c r="Y51" s="7" t="inlineStr"/>
+      <c r="Z51" s="8" t="inlineStr">
+        <is>
+          <t>船舶塗料の欧州比較</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="68" customHeight="1">
+      <c r="A52" s="32" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" s="32" t="inlineStr">
+        <is>
+          <t>外資系・日本法人</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>ヨトゥン・ジャパン</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>横浜市</t>
+        </is>
+      </c>
+      <c r="E52" s="14" t="inlineStr">
+        <is>
+          <t>非上場(ノルウェーJotun子会社)</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>Jotun連結内</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>数十人(日本)</t>
+        </is>
+      </c>
+      <c r="H52" s="8" t="inlineStr">
+        <is>
+          <t>船舶・防食・建築用塗料</t>
+        </is>
+      </c>
+      <c r="I52" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="J52" s="16" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="K52" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L52" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M52" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="8" t="inlineStr">
+        <is>
+          <t>横浜</t>
+        </is>
+      </c>
+      <c r="O52" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jotun.com/jp/</t>
+        </is>
+      </c>
+      <c r="P52" s="7" t="inlineStr">
+        <is>
+          <t>本社問合せ</t>
+        </is>
+      </c>
+      <c r="Q52" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="R52" s="8" t="inlineStr">
+        <is>
+          <t>船舶塗料の③④, 建築水性②⑤</t>
+        </is>
+      </c>
+      <c r="S52" s="8" t="inlineStr">
+        <is>
+          <t>船舶・建築双方のグローバル標準</t>
+        </is>
+      </c>
+      <c r="T52" s="22" t="n">
+        <v>65</v>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
+        <is>
+          <t>本社経由</t>
+        </is>
+      </c>
+      <c r="V52" s="8" t="inlineStr">
+        <is>
+          <t>造船・建築業界経由</t>
+        </is>
+      </c>
+      <c r="W52" s="8" t="inlineStr">
+        <is>
+          <t>本社方針優先</t>
+        </is>
+      </c>
+      <c r="X52" s="14" t="inlineStr"/>
+      <c r="Y52" s="7" t="inlineStr"/>
+      <c r="Z52" s="8" t="inlineStr">
+        <is>
+          <t>船舶・建築の欧州比較</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="68" customHeight="1">
+      <c r="A53" s="32" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" s="32" t="inlineStr">
+        <is>
+          <t>外資系・日本法人</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>ベンジャミンムーア・ジャパン</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="E53" s="14" t="inlineStr">
+        <is>
+          <t>非上場(米BM子会社)</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>BM連結内</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>数十人(日本)</t>
+        </is>
+      </c>
+      <c r="H53" s="8" t="inlineStr">
+        <is>
+          <t>建築用高級水性塗料</t>
+        </is>
+      </c>
+      <c r="I53" s="20" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="J53" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="K53" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L53" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M53" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="8" t="inlineStr">
+        <is>
+          <t>(輸入主体)</t>
+        </is>
+      </c>
+      <c r="O53" s="17" t="inlineStr">
+        <is>
+          <t>https://benjaminmoore.jp/</t>
+        </is>
+      </c>
+      <c r="P53" s="7" t="inlineStr">
+        <is>
+          <t>本社問合せ</t>
+        </is>
+      </c>
+      <c r="Q53" s="14" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="R53" s="8" t="inlineStr">
+        <is>
+          <t>建築水性塗料の調色・小口販売</t>
+        </is>
+      </c>
+      <c r="S53" s="8" t="inlineStr">
+        <is>
+          <t>米国の調色機普及・小口運用</t>
+        </is>
+      </c>
+      <c r="T53" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>輸入代理店経由</t>
+        </is>
+      </c>
+      <c r="V53" s="8" t="inlineStr">
+        <is>
+          <t>建材専門店経由</t>
+        </is>
+      </c>
+      <c r="W53" s="8" t="inlineStr">
+        <is>
+          <t>輸入主体で国内製造は限定的</t>
+        </is>
+      </c>
+      <c r="X53" s="14" t="inlineStr"/>
+      <c r="Y53" s="7" t="inlineStr"/>
+      <c r="Z53" s="8" t="inlineStr">
+        <is>
+          <t>輸入塗料の参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="68" customHeight="1">
+      <c r="A54" s="27" t="n">
+        <v>50</v>
+      </c>
+      <c r="B54" s="27" t="inlineStr">
+        <is>
+          <t>機能・特殊</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>ターナー色彩</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>大阪府吹田市</t>
+        </is>
+      </c>
+      <c r="E54" s="14" t="inlineStr">
+        <is>
+          <t>非上場</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>約60億円規模(推定)</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>約200人</t>
+        </is>
+      </c>
+      <c r="H54" s="8" t="inlineStr">
+        <is>
+          <t>アクリル絵具・アート用塗料・建築仕上げ</t>
+        </is>
+      </c>
+      <c r="I54" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="J54" s="15" t="inlineStr">
+        <is>
+          <t>◎</t>
+        </is>
+      </c>
+      <c r="K54" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L54" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M54" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="8" t="inlineStr">
+        <is>
+          <t>大阪・吹田</t>
+        </is>
+      </c>
+      <c r="O54" s="17" t="inlineStr">
+        <is>
+          <t>https://www.turner.co.jp/</t>
+        </is>
+      </c>
+      <c r="P54" s="7" t="inlineStr">
+        <is>
+          <t>本社問合せ</t>
+        </is>
+      </c>
+      <c r="Q54" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="R54" s="8" t="inlineStr">
+        <is>
+          <t>アクリル系塗料の③④⑤⑧(チューブ・ボトル充填)</t>
+        </is>
+      </c>
+      <c r="S54" s="8" t="inlineStr">
+        <is>
+          <t>小ロット多品種(色数)管理、特殊容器充填</t>
+        </is>
+      </c>
+      <c r="T54" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
+          <t>営業窓口</t>
+        </is>
+      </c>
+      <c r="V54" s="8" t="inlineStr">
+        <is>
+          <t>画材・建材販売店経由</t>
+        </is>
+      </c>
+      <c r="W54" s="8" t="inlineStr">
+        <is>
+          <t>アート用と建築用の両方を持つ特殊性</t>
+        </is>
+      </c>
+      <c r="X54" s="14" t="inlineStr"/>
+      <c r="Y54" s="7" t="inlineStr"/>
+      <c r="Z54" s="8" t="inlineStr">
+        <is>
+          <t>多品種小ロットの極端例</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:Z32"/>
+  <autoFilter ref="A4:Z54"/>
   <mergeCells count="2">
     <mergeCell ref="A1:Z1"/>
     <mergeCell ref="A2:Z2"/>
@@ -4581,18 +7274,42 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId50"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -4679,7 +7396,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>統合報告書・環境/サステナ報告書・IR充実度。高=20 / 中=12 / 低=6</t>
+          <t>統合報告書・環境/サステナ報告書・IR充実度。高=20 / 中=12 / 低=6 / 要確認=減点</t>
         </is>
       </c>
     </row>
@@ -4709,7 +7426,7 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>他で代替不可能な情報源 (船舶・電着・UV等のニッチ専門性)。高=15 / 中=10 / 低=5</t>
+          <t>他で代替不可能な情報源(船舶・電着・UV・粉体・耐熱等)。高=15 / 中=10 / 低=5</t>
         </is>
       </c>
     </row>
@@ -4820,17 +7537,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H17"/>
+  <dimension ref="B2:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="2" ht="28" customHeight="1">
@@ -4843,7 +7561,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>各製品タイプの ◎ または ○ 保有社数。漏れがないか、過剰でないかを確認するための集計表。</t>
+          <t>各製品タイプの ◎ または ○ 保有社数を集計。漏れ・過剰がないか確認するための表。</t>
         </is>
       </c>
     </row>
@@ -4880,6 +7598,11 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
+          <t>社数</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
           <t>備考</t>
         </is>
       </c>
@@ -4887,7 +7610,7 @@
     <row r="6" ht="26" customHeight="1">
       <c r="B6" s="44" t="inlineStr">
         <is>
-          <t>DIY・小口 (2社)</t>
+          <t>大手総合</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
@@ -4902,78 +7625,84 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>◎1 / ○1</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>◎2 / ○0</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr"/>
+          <t>◎0 / ○2</t>
+        </is>
+      </c>
+      <c r="H6" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" s="7" t="inlineStr"/>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="B7" s="45" t="inlineStr">
         <is>
-          <t>UV・特殊 (5社)</t>
+          <t>中堅総合</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
+          <t>◎6 / ○2</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>◎1 / ○7</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
           <t>◎1 / ○1</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>◎0 / ○2</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>◎0 / ○1</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>◎4 / ○0</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr"/>
+          <t>◎0 / ○1</t>
+        </is>
+      </c>
+      <c r="H7" s="33" t="n">
+        <v>8</v>
+      </c>
+      <c r="I7" s="7" t="inlineStr"/>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="B8" s="46" t="inlineStr">
         <is>
-          <t>中堅総合 (4社)</t>
+          <t>自動車補修</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>◎3 / ○1</t>
+          <t>◎1 / ○1</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>◎1 / ○3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>◎0 / ○1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>◎0 / ○1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -4981,55 +7710,61 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr"/>
+      <c r="H8" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" s="7" t="inlineStr"/>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="B9" s="47" t="inlineStr">
         <is>
-          <t>大手総合 (2社)</t>
+          <t>建築・仕上塗材</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>◎2 / ○0</t>
+          <t>◎2 / ○2</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>◎2 / ○0</t>
+          <t>◎4 / ○1</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>◎1 / ○1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>◎2 / ○0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>◎0 / ○2</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" s="7" t="inlineStr"/>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="B10" s="48" t="inlineStr">
         <is>
-          <t>建築特化 (1社)</t>
+          <t>機能・特殊</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>◎1 / ○0</t>
+          <t>◎6 / ○1</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>◎1 / ○0</t>
+          <t>◎1 / ○4</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
@@ -5044,25 +7779,28 @@
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr"/>
+          <t>◎1 / ○1</t>
+        </is>
+      </c>
+      <c r="H10" s="33" t="n">
+        <v>7</v>
+      </c>
+      <c r="I10" s="7" t="inlineStr"/>
     </row>
     <row r="11" ht="26" customHeight="1">
       <c r="B11" s="49" t="inlineStr">
         <is>
-          <t>業界団体 (4社)</t>
+          <t>UV・印刷インキ</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>◎0 / ○4</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>◎0 / ○3</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
@@ -5072,35 +7810,38 @@
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>◎0 / ○1</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr"/>
+          <t>◎7 / ○2</t>
+        </is>
+      </c>
+      <c r="H11" s="33" t="n">
+        <v>9</v>
+      </c>
+      <c r="I11" s="7" t="inlineStr"/>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="B12" s="50" t="inlineStr">
         <is>
-          <t>粉体特化 (2社)</t>
+          <t>DIY・小口</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>◎0 / ○1</t>
+          <t>◎3 / ○0</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>◎0 / ○1</t>
+          <t>◎3 / ○0</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>◎2 / ○0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
@@ -5110,58 +7851,64 @@
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>◎0 / ○1</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" s="7" t="inlineStr"/>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="B13" s="51" t="inlineStr">
         <is>
-          <t>自動車補修 (2社)</t>
+          <t>日ペグループ</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
+          <t>◎2 / ○2</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>◎0 / ○5</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>◎0 / ○2</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
           <t>◎2 / ○0</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>◎0 / ○1</t>
-        </is>
-      </c>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr"/>
+      <c r="H13" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="I13" s="7" t="inlineStr"/>
     </row>
     <row r="14" ht="26" customHeight="1">
       <c r="B14" s="52" t="inlineStr">
         <is>
-          <t>装置メーカー (4社)</t>
+          <t>関ペグループ</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>◎1 / ○0</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>◎0 / ○1</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
@@ -5179,106 +7926,82 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr"/>
+      <c r="H14" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="7" t="inlineStr"/>
     </row>
     <row r="15" ht="26" customHeight="1">
       <c r="B15" s="53" t="inlineStr">
         <is>
-          <t>防食・構造物 (1社)</t>
+          <t>外資系・日本法人</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>◎1 / ○0</t>
+          <t>◎6 / ○1</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>◎0 / ○1</t>
+          <t>◎4 / ○4</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>◎1 / ○3</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>◎2 / ○3</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr"/>
+          <t>◎0 / ○2</t>
+        </is>
+      </c>
+      <c r="H15" s="33" t="n">
+        <v>8</v>
+      </c>
+      <c r="I15" s="7" t="inlineStr"/>
     </row>
     <row r="16" ht="26" customHeight="1">
       <c r="B16" s="54" t="inlineStr">
         <is>
-          <t>電着特化 (1社)</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="inlineStr">
-        <is>
-          <t>◎0 / ○1</t>
-        </is>
-      </c>
-      <c r="D16" s="14" t="inlineStr">
-        <is>
-          <t>◎0 / ○1</t>
-        </is>
-      </c>
-      <c r="E16" s="14" t="inlineStr">
-        <is>
-          <t>◎0 / ○1</t>
-        </is>
-      </c>
-      <c r="F16" s="14" t="inlineStr">
-        <is>
-          <t>◎1 / ○0</t>
-        </is>
-      </c>
-      <c r="G16" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr"/>
-    </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="B17" s="55" t="inlineStr">
-        <is>
           <t>全社合計</t>
         </is>
       </c>
-      <c r="C17" s="56" t="inlineStr">
-        <is>
-          <t>◎12 / ○4</t>
-        </is>
-      </c>
-      <c r="D17" s="56" t="inlineStr">
-        <is>
-          <t>◎6 / ○9</t>
-        </is>
-      </c>
-      <c r="E17" s="56" t="inlineStr">
-        <is>
-          <t>◎3 / ○3</t>
-        </is>
-      </c>
-      <c r="F17" s="56" t="inlineStr">
-        <is>
-          <t>◎3 / ○1</t>
-        </is>
-      </c>
-      <c r="G17" s="56" t="inlineStr">
-        <is>
-          <t>◎4 / ○3</t>
-        </is>
-      </c>
-      <c r="H17" s="35" t="inlineStr">
+      <c r="C16" s="55" t="inlineStr">
+        <is>
+          <t>◎29 / ○13</t>
+        </is>
+      </c>
+      <c r="D16" s="55" t="inlineStr">
+        <is>
+          <t>◎15 / ○25</t>
+        </is>
+      </c>
+      <c r="E16" s="55" t="inlineStr">
+        <is>
+          <t>◎3 / ○7</t>
+        </is>
+      </c>
+      <c r="F16" s="55" t="inlineStr">
+        <is>
+          <t>◎6 / ○5</t>
+        </is>
+      </c>
+      <c r="G16" s="55" t="inlineStr">
+        <is>
+          <t>◎8 / ○8</t>
+        </is>
+      </c>
+      <c r="H16" s="56" t="n">
+        <v>50</v>
+      </c>
+      <c r="I16" s="35" t="inlineStr">
         <is>
           <t>◎○ 合計が 5 社未満の製品タイプは要補強</t>
         </is>
@@ -5286,8 +8009,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="B2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/塗料メーカー_ヒアリング候補リスト.xlsx
+++ b/塗料メーカー_ヒアリング候補リスト.xlsx
@@ -13,7 +13,7 @@
     <sheet name="③カバレッジ確認" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'①候補リスト'!$A$4:$Z$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'①候補リスト'!$A$4:$AA$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,6 +56,12 @@
       <i val="1"/>
       <color rgb="00555555"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="14"/>
     </font>
     <font>
       <name val="Yu Gothic"/>
@@ -269,7 +275,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -306,6 +312,9 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -315,10 +324,13 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -327,19 +339,19 @@
     <xf numFmtId="0" fontId="3" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -363,10 +375,10 @@
     <xf numFmtId="0" fontId="4" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -429,10 +441,10 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -800,7 +812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D26"/>
+  <dimension ref="B2:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1010,55 +1022,79 @@
     <row r="21" ht="22" customHeight="1">
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>・優先度スコアは 100 点満点。シート②に配点基準を記載。</t>
+          <t>・「過去契約有無」列は kintone 取引明細 (2026/05/11 抽出) との突合結果。○ 印=過去契約あり。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>・売上・従業員等は推定含む。最新の有報・IR資料・帝国データバンク等で適宜上書きを推奨。</t>
+          <t xml:space="preserve">  突合は親会社のみ厳密マッチ。日ペHDの取引があっても子会社5社には自動付与しない (逆も同様)。</t>
         </is>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>・◎=主力 / ○=取扱 / △=限定 / -=無し  (5製品タイプ別)。</t>
+          <t xml:space="preserve">  ○ 印が付いた企業: 8社/50社 (関西ペイント, ロックペイント, ナトコ, シンロイヒ, 大日精化工業, サカタインクス, トウペ, 日本ペイント・インダストリアルコーティングス)</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>・「ヒアリング推奨工程」は別 Excel 「塗料メーカー_製造フローINOUT.xlsx」の工程番号と連動。</t>
+          <t>・優先度スコアは 100 点満点。シート②に配点基準を記載。</t>
         </is>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>・日ペグループ・関ペグループ子会社は、独立にアプローチせず親会社経由を推奨。</t>
+          <t>・売上・従業員等は推定含む。最新の有報・IR資料・帝国データバンク等で適宜上書きを推奨。</t>
         </is>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="B26" s="7" t="inlineStr">
         <is>
+          <t>・◎=主力 / ○=取扱 / △=限定 / -=無し  (5製品タイプ別)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>・「ヒアリング推奨工程」は別 Excel 「塗料メーカー_製造フローINOUT.xlsx」の工程番号と連動。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>・日ペグループ・関ペグループ子会社は、独立にアプローチせず親会社経由を推奨。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="B29" s="7" t="inlineStr">
+        <is>
           <t>・外資系日本法人は本社方針・グローバル機密の制約が強い。日本拠点での製造規模を要確認。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="17">
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="B25:D25"/>
@@ -1076,35 +1112,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z54"/>
+  <dimension ref="A1:AA54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
     <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="32" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="32" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
-    <col width="24" customWidth="1" min="21" max="21"/>
-    <col width="22" customWidth="1" min="22" max="22"/>
-    <col width="30" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="20" customWidth="1" min="25" max="25"/>
-    <col width="24" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="30" customWidth="1" min="19" max="19"/>
+    <col width="32" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="24" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="30" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="20" customWidth="1" min="26" max="26"/>
+    <col width="24" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1139,115 +1176,120 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>過去契約有無</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>本社所在地</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>上場区分</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>売上規模(連結)</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>従業員数(概数)</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>主要セグメント</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>溶剤系</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>水性</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>粉体</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>電着</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>UV硬化</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>主要工場(代表)</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>IR/問合せ窓口</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="R4" s="3" t="inlineStr">
         <is>
           <t>公開情報充実度</t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr">
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t>ヒアリング推奨工程</t>
         </is>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="T4" s="3" t="inlineStr">
         <is>
           <t>確認したい定量項目</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="U4" s="3" t="inlineStr">
         <is>
           <t>優先度スコア</t>
         </is>
       </c>
-      <c r="U4" s="3" t="inlineStr">
+      <c r="V4" s="3" t="inlineStr">
         <is>
           <t>推奨アプローチルート</t>
         </is>
       </c>
-      <c r="V4" s="3" t="inlineStr">
+      <c r="W4" s="3" t="inlineStr">
         <is>
           <t>既存関係(想定)</t>
         </is>
       </c>
-      <c r="W4" s="3" t="inlineStr">
+      <c r="X4" s="3" t="inlineStr">
         <is>
           <t>留意点・ハードル</t>
         </is>
       </c>
-      <c r="X4" s="3" t="inlineStr">
+      <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>進捗ステータス</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
+      <c r="Z4" s="3" t="inlineStr">
         <is>
           <t>次アクション</t>
         </is>
       </c>
-      <c r="Z4" s="3" t="inlineStr">
+      <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>メモ</t>
         </is>
@@ -1267,107 +1309,108 @@
           <t>日本ペイントホールディングス</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr"/>
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>大阪市北区</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>東証プライム</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>約1.5兆円(2024)</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>約40,000人(連結)</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>汎用・自動車・工業・船舶 (世界4位級)</t>
         </is>
       </c>
-      <c r="I5" s="15" t="inlineStr">
+      <c r="J5" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="J5" s="15" t="inlineStr">
+      <c r="K5" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="K5" s="16" t="inlineStr">
+      <c r="L5" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="L5" s="15" t="inlineStr">
+      <c r="M5" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="M5" s="16" t="inlineStr">
+      <c r="N5" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="N5" s="8" t="inlineStr">
+      <c r="O5" s="8" t="inlineStr">
         <is>
           <t>大阪・東京・愛知 ほか国内10数拠点</t>
         </is>
       </c>
-      <c r="O5" s="17" t="inlineStr">
+      <c r="P5" s="18" t="inlineStr">
         <is>
           <t>https://www.nipponpaint-holdings.com/</t>
         </is>
       </c>
-      <c r="P5" s="7" t="inlineStr">
+      <c r="Q5" s="7" t="inlineStr">
         <is>
           <t>IR部</t>
         </is>
       </c>
-      <c r="Q5" s="14" t="inlineStr">
+      <c r="R5" s="15" t="inlineStr">
         <is>
           <t>高 (統合報告書・サステナ報告書)</t>
         </is>
       </c>
-      <c r="R5" s="8" t="inlineStr">
+      <c r="S5" s="8" t="inlineStr">
         <is>
           <t>①〜⑨全工程 + 並行洗浄・排ガス処理</t>
         </is>
       </c>
-      <c r="S5" s="8" t="inlineStr">
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>kWh/t・歩留・廃シンナー量・VOC・Scope1/2/3</t>
         </is>
       </c>
-      <c r="T5" s="18" t="n">
+      <c r="U5" s="19" t="n">
         <v>95</v>
       </c>
-      <c r="U5" s="8" t="inlineStr">
+      <c r="V5" s="8" t="inlineStr">
         <is>
           <t>IR経由 → 技術本部/R&amp;Dセンター</t>
         </is>
       </c>
-      <c r="V5" s="8" t="inlineStr">
+      <c r="W5" s="8" t="inlineStr">
         <is>
           <t>業界団体・共同セミナー</t>
         </is>
       </c>
-      <c r="W5" s="8" t="inlineStr">
+      <c r="X5" s="8" t="inlineStr">
         <is>
           <t>上場大手のため機密の線引き厳格・NDA必須</t>
         </is>
       </c>
-      <c r="X5" s="14" t="inlineStr"/>
-      <c r="Y5" s="7" t="inlineStr"/>
-      <c r="Z5" s="8" t="inlineStr">
+      <c r="Y5" s="15" t="inlineStr"/>
+      <c r="Z5" s="7" t="inlineStr"/>
+      <c r="AA5" s="8" t="inlineStr">
         <is>
           <t>M&amp;A 主導、海外拠点も検証視点に</t>
         </is>
@@ -1387,117 +1430,122 @@
           <t>関西ペイント</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>大阪市中央区</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>東証プライム</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>約5,500億円(2024)</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>約15,000人(連結)</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>自動車OEM・補修・工業・船舶・電着</t>
         </is>
       </c>
-      <c r="I6" s="15" t="inlineStr">
+      <c r="J6" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="J6" s="15" t="inlineStr">
+      <c r="K6" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="K6" s="15" t="inlineStr">
+      <c r="L6" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="L6" s="15" t="inlineStr">
+      <c r="M6" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="M6" s="16" t="inlineStr">
+      <c r="N6" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="N6" s="8" t="inlineStr">
+      <c r="O6" s="8" t="inlineStr">
         <is>
           <t>大阪・滋賀・茨城(姉ヶ崎) ほか</t>
         </is>
       </c>
-      <c r="O6" s="17" t="inlineStr">
+      <c r="P6" s="18" t="inlineStr">
         <is>
           <t>https://www.kansai.co.jp/</t>
         </is>
       </c>
-      <c r="P6" s="7" t="inlineStr">
+      <c r="Q6" s="7" t="inlineStr">
         <is>
           <t>IR部/広報部</t>
         </is>
       </c>
-      <c r="Q6" s="14" t="inlineStr">
+      <c r="R6" s="15" t="inlineStr">
         <is>
           <t>高 (統合報告書・ESG資料)</t>
         </is>
       </c>
-      <c r="R6" s="8" t="inlineStr">
+      <c r="S6" s="8" t="inlineStr">
         <is>
           <t>①〜⑨ + 電着・粉体の特殊工程</t>
         </is>
       </c>
-      <c r="S6" s="8" t="inlineStr">
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>電着MEQ/UF回収率、粉体歩留、CCM導入率</t>
         </is>
       </c>
-      <c r="T6" s="18" t="n">
+      <c r="U6" s="19" t="n">
         <v>95</v>
       </c>
-      <c r="U6" s="8" t="inlineStr">
+      <c r="V6" s="8" t="inlineStr">
         <is>
           <t>技術部門直接 + IR</t>
         </is>
       </c>
-      <c r="V6" s="8" t="inlineStr">
+      <c r="W6" s="8" t="inlineStr">
         <is>
           <t>業界団体・装置メーカー紹介</t>
         </is>
       </c>
-      <c r="W6" s="8" t="inlineStr">
+      <c r="X6" s="8" t="inlineStr">
         <is>
           <t>海外子会社(印・南ア)情報の範囲を要相談</t>
         </is>
       </c>
-      <c r="X6" s="14" t="inlineStr"/>
-      <c r="Y6" s="7" t="inlineStr"/>
-      <c r="Z6" s="8" t="inlineStr">
+      <c r="Y6" s="15" t="inlineStr"/>
+      <c r="Z6" s="7" t="inlineStr"/>
+      <c r="AA6" s="8" t="inlineStr">
         <is>
           <t>EV用電池絶縁の R&amp;D 動向も併せて確認可</t>
         </is>
       </c>
     </row>
     <row r="7" ht="68" customHeight="1">
-      <c r="A7" s="19" t="n">
+      <c r="A7" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>中堅総合</t>
         </is>
@@ -1507,117 +1555,118 @@
           <t>大日本塗料 (DNT)</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr"/>
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>東京都品川区</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>東証スタンダード</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>約750億円(2024)</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>約1,800人(連結)</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>防食・構造物・蛍光塗料・粉体</t>
         </is>
       </c>
-      <c r="I7" s="15" t="inlineStr">
+      <c r="J7" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="J7" s="16" t="inlineStr">
+      <c r="K7" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="K7" s="16" t="inlineStr">
+      <c r="L7" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="L7" s="20" t="inlineStr">
+      <c r="M7" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="M7" s="20" t="inlineStr">
+      <c r="N7" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="N7" s="8" t="inlineStr">
+      <c r="O7" s="8" t="inlineStr">
         <is>
           <t>大阪・東京・愛知(小牧)</t>
         </is>
       </c>
-      <c r="O7" s="17" t="inlineStr">
+      <c r="P7" s="18" t="inlineStr">
         <is>
           <t>https://www.dnt.co.jp/</t>
         </is>
       </c>
-      <c r="P7" s="7" t="inlineStr">
+      <c r="Q7" s="7" t="inlineStr">
         <is>
           <t>IR室</t>
         </is>
       </c>
-      <c r="Q7" s="14" t="inlineStr">
+      <c r="R7" s="15" t="inlineStr">
         <is>
           <t>中〜高 (有報・統合報告書)</t>
         </is>
       </c>
-      <c r="R7" s="8" t="inlineStr">
+      <c r="S7" s="8" t="inlineStr">
         <is>
           <t>厚膜防食の③④調色・⑦検査・⑧充填</t>
         </is>
       </c>
-      <c r="S7" s="8" t="inlineStr">
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>厚塗り防食の固形分・粘度、ジンクリッチプライマー</t>
         </is>
       </c>
-      <c r="T7" s="21" t="n">
+      <c r="U7" s="23" t="n">
         <v>82</v>
       </c>
-      <c r="U7" s="8" t="inlineStr">
+      <c r="V7" s="8" t="inlineStr">
         <is>
           <t>営業・技術 / IR</t>
         </is>
       </c>
-      <c r="V7" s="8" t="inlineStr">
+      <c r="W7" s="8" t="inlineStr">
         <is>
           <t>インフラ顧客経由</t>
         </is>
       </c>
-      <c r="W7" s="8" t="inlineStr">
+      <c r="X7" s="8" t="inlineStr">
         <is>
           <t>構造物向け特殊配合は機密性高</t>
         </is>
       </c>
-      <c r="X7" s="14" t="inlineStr"/>
-      <c r="Y7" s="7" t="inlineStr"/>
-      <c r="Z7" s="8" t="inlineStr">
+      <c r="Y7" s="15" t="inlineStr"/>
+      <c r="Z7" s="7" t="inlineStr"/>
+      <c r="AA7" s="8" t="inlineStr">
         <is>
           <t>ジンクリッチ・蛍光塗料のニッチ例</t>
         </is>
       </c>
     </row>
     <row r="8" ht="68" customHeight="1">
-      <c r="A8" s="19" t="n">
+      <c r="A8" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>中堅総合</t>
         </is>
@@ -1627,117 +1676,118 @@
           <t>中国塗料 (CMP)</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr"/>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>東京都千代田区</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="F8" s="15" t="inlineStr">
         <is>
           <t>東証プライム</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>約1,100億円(2024)</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>約2,500人(連結)</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>船舶用塗料(世界4強)・工業防食</t>
         </is>
       </c>
-      <c r="I8" s="15" t="inlineStr">
+      <c r="J8" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="K8" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="K8" s="20" t="inlineStr">
+      <c r="L8" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="L8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="M8" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N8" s="8" t="inlineStr">
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O8" s="8" t="inlineStr">
         <is>
           <t>兵庫・愛媛 ほか</t>
         </is>
       </c>
-      <c r="O8" s="17" t="inlineStr">
+      <c r="P8" s="18" t="inlineStr">
         <is>
           <t>https://www.cmp.co.jp/</t>
         </is>
       </c>
-      <c r="P8" s="7" t="inlineStr">
+      <c r="Q8" s="7" t="inlineStr">
         <is>
           <t>IR部</t>
         </is>
       </c>
-      <c r="Q8" s="14" t="inlineStr">
+      <c r="R8" s="15" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="R8" s="8" t="inlineStr">
+      <c r="S8" s="8" t="inlineStr">
         <is>
           <t>船舶塗料の③④(低摩擦・防汚機能の分散)</t>
         </is>
       </c>
-      <c r="S8" s="8" t="inlineStr">
+      <c r="T8" s="8" t="inlineStr">
         <is>
           <t>防汚剤添加量・厚膜塗装の充填精度</t>
         </is>
       </c>
-      <c r="T8" s="18" t="n">
+      <c r="U8" s="19" t="n">
         <v>88</v>
       </c>
-      <c r="U8" s="8" t="inlineStr">
+      <c r="V8" s="8" t="inlineStr">
         <is>
           <t>IR / 技術センター</t>
         </is>
       </c>
-      <c r="V8" s="8" t="inlineStr">
+      <c r="W8" s="8" t="inlineStr">
         <is>
           <t>造船所経由</t>
         </is>
       </c>
-      <c r="W8" s="8" t="inlineStr">
+      <c r="X8" s="8" t="inlineStr">
         <is>
           <t>防汚剤組成は競争力源・機密性高</t>
         </is>
       </c>
-      <c r="X8" s="14" t="inlineStr"/>
-      <c r="Y8" s="7" t="inlineStr"/>
-      <c r="Z8" s="8" t="inlineStr">
+      <c r="Y8" s="15" t="inlineStr"/>
+      <c r="Z8" s="7" t="inlineStr"/>
+      <c r="AA8" s="8" t="inlineStr">
         <is>
           <t>船舶・防食の世界トップ</t>
         </is>
       </c>
     </row>
     <row r="9" ht="68" customHeight="1">
-      <c r="A9" s="19" t="n">
+      <c r="A9" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>中堅総合</t>
         </is>
@@ -1747,117 +1797,118 @@
           <t>神東塗料</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr"/>
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>兵庫県尼崎市</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>東証スタンダード</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>約280億円</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>約700人(連結)</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>鉄道車両・工業・電着</t>
         </is>
       </c>
-      <c r="I9" s="15" t="inlineStr">
+      <c r="J9" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="J9" s="16" t="inlineStr">
+      <c r="K9" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="K9" s="20" t="inlineStr">
+      <c r="L9" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="L9" s="16" t="inlineStr">
+      <c r="M9" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="M9" s="20" t="inlineStr">
+      <c r="N9" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="N9" s="8" t="inlineStr">
+      <c r="O9" s="8" t="inlineStr">
         <is>
           <t>尼崎・千葉</t>
         </is>
       </c>
-      <c r="O9" s="17" t="inlineStr">
+      <c r="P9" s="18" t="inlineStr">
         <is>
           <t>https://www.shintopaint.co.jp/</t>
         </is>
       </c>
-      <c r="P9" s="7" t="inlineStr">
+      <c r="Q9" s="7" t="inlineStr">
         <is>
           <t>総務・IR担当</t>
         </is>
       </c>
-      <c r="Q9" s="14" t="inlineStr">
+      <c r="R9" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="R9" s="8" t="inlineStr">
+      <c r="S9" s="8" t="inlineStr">
         <is>
           <t>鉄道用塗装ライン①〜⑨、電着塗料の③配合</t>
         </is>
       </c>
-      <c r="S9" s="8" t="inlineStr">
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>鉄道塗料の歩留、電着塗料の電気伝導度管理</t>
         </is>
       </c>
-      <c r="T9" s="21" t="n">
+      <c r="U9" s="23" t="n">
         <v>76</v>
       </c>
-      <c r="U9" s="8" t="inlineStr">
+      <c r="V9" s="8" t="inlineStr">
         <is>
           <t>技術部門 / IR</t>
         </is>
       </c>
-      <c r="V9" s="8" t="inlineStr">
+      <c r="W9" s="8" t="inlineStr">
         <is>
           <t>鉄道車両メーカー経由</t>
         </is>
       </c>
-      <c r="W9" s="8" t="inlineStr">
+      <c r="X9" s="8" t="inlineStr">
         <is>
           <t>鉄道顧客の機密 (色番号等) は除外</t>
         </is>
       </c>
-      <c r="X9" s="14" t="inlineStr"/>
-      <c r="Y9" s="7" t="inlineStr"/>
-      <c r="Z9" s="8" t="inlineStr">
+      <c r="Y9" s="15" t="inlineStr"/>
+      <c r="Z9" s="7" t="inlineStr"/>
+      <c r="AA9" s="8" t="inlineStr">
         <is>
           <t>鉄道車両用塗料のリファレンス</t>
         </is>
       </c>
     </row>
     <row r="10" ht="68" customHeight="1">
-      <c r="A10" s="19" t="n">
+      <c r="A10" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>中堅総合</t>
         </is>
@@ -1867,117 +1918,118 @@
           <t>日本特殊塗料 (NTC)</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr"/>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>東京都北区</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>東証スタンダード</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>約580億円</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>約1,800人(連結)</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>建築防音材・自動車防音・特殊塗料</t>
         </is>
       </c>
-      <c r="I10" s="15" t="inlineStr">
+      <c r="J10" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="J10" s="16" t="inlineStr">
+      <c r="K10" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="K10" s="20" t="inlineStr">
+      <c r="L10" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="L10" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M10" s="20" t="inlineStr">
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="N10" s="8" t="inlineStr">
+      <c r="O10" s="8" t="inlineStr">
         <is>
           <t>東京・愛知・滋賀 ほか</t>
         </is>
       </c>
-      <c r="O10" s="17" t="inlineStr">
+      <c r="P10" s="18" t="inlineStr">
         <is>
           <t>https://www.ntpaint.co.jp/</t>
         </is>
       </c>
-      <c r="P10" s="7" t="inlineStr">
+      <c r="Q10" s="7" t="inlineStr">
         <is>
           <t>IR室</t>
         </is>
       </c>
-      <c r="Q10" s="14" t="inlineStr">
+      <c r="R10" s="15" t="inlineStr">
         <is>
           <t>中〜高</t>
         </is>
       </c>
-      <c r="R10" s="8" t="inlineStr">
+      <c r="S10" s="8" t="inlineStr">
         <is>
           <t>建築防水塗料・自動車制振塗料の③④⑤</t>
         </is>
       </c>
-      <c r="S10" s="8" t="inlineStr">
+      <c r="T10" s="8" t="inlineStr">
         <is>
           <t>厚膜塗料の塗布量、車両用制振材の充填</t>
         </is>
       </c>
-      <c r="T10" s="21" t="n">
+      <c r="U10" s="23" t="n">
         <v>78</v>
       </c>
-      <c r="U10" s="8" t="inlineStr">
+      <c r="V10" s="8" t="inlineStr">
         <is>
           <t>IR / 技術部門</t>
         </is>
       </c>
-      <c r="V10" s="8" t="inlineStr">
+      <c r="W10" s="8" t="inlineStr">
         <is>
           <t>建築・自動車業界経由</t>
         </is>
       </c>
-      <c r="W10" s="8" t="inlineStr">
+      <c r="X10" s="8" t="inlineStr">
         <is>
           <t>防音材事業との切り分けが必要</t>
         </is>
       </c>
-      <c r="X10" s="14" t="inlineStr"/>
-      <c r="Y10" s="7" t="inlineStr"/>
-      <c r="Z10" s="8" t="inlineStr">
+      <c r="Y10" s="15" t="inlineStr"/>
+      <c r="Z10" s="7" t="inlineStr"/>
+      <c r="AA10" s="8" t="inlineStr">
         <is>
           <t>防音・制振との複合用途が特徴</t>
         </is>
       </c>
     </row>
     <row r="11" ht="68" customHeight="1">
-      <c r="A11" s="19" t="n">
+      <c r="A11" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>中堅総合</t>
         </is>
@@ -1987,117 +2039,118 @@
           <t>エスケー化研 (SK化研)</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr"/>
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>大阪府茨木市</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="F11" s="15" t="inlineStr">
         <is>
           <t>非上場(独立系)</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>約1,800億円(推定)</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>約1,400人</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr">
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>建築用塗料 国内首位</t>
         </is>
       </c>
-      <c r="I11" s="16" t="inlineStr">
+      <c r="J11" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J11" s="15" t="inlineStr">
+      <c r="K11" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="K11" s="20" t="inlineStr">
+      <c r="L11" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="L11" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="M11" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N11" s="8" t="inlineStr">
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O11" s="8" t="inlineStr">
         <is>
           <t>大阪・茨木 ほか全国</t>
         </is>
       </c>
-      <c r="O11" s="17" t="inlineStr">
+      <c r="P11" s="18" t="inlineStr">
         <is>
           <t>https://www.sk-kaken.co.jp/</t>
         </is>
       </c>
-      <c r="P11" s="7" t="inlineStr">
+      <c r="Q11" s="7" t="inlineStr">
         <is>
           <t>本社・各支店</t>
         </is>
       </c>
-      <c r="Q11" s="14" t="inlineStr">
+      <c r="R11" s="15" t="inlineStr">
         <is>
           <t>中 (非上場のためIR限定的)</t>
         </is>
       </c>
-      <c r="R11" s="8" t="inlineStr">
+      <c r="S11" s="8" t="inlineStr">
         <is>
           <t>水性塗料 ②③④調色 + ⑥ろ過 + 設備洗浄</t>
         </is>
       </c>
-      <c r="S11" s="8" t="inlineStr">
+      <c r="T11" s="8" t="inlineStr">
         <is>
           <t>水性ベースの歩留、CCM普及率、防腐剤添加量</t>
         </is>
       </c>
-      <c r="T11" s="18" t="n">
+      <c r="U11" s="19" t="n">
         <v>88</v>
       </c>
-      <c r="U11" s="8" t="inlineStr">
+      <c r="V11" s="8" t="inlineStr">
         <is>
           <t>技術部門 / 営業窓口</t>
         </is>
       </c>
-      <c r="V11" s="8" t="inlineStr">
+      <c r="W11" s="8" t="inlineStr">
         <is>
           <t>業界団体 (JPMA) 経由が確実</t>
         </is>
       </c>
-      <c r="W11" s="8" t="inlineStr">
+      <c r="X11" s="8" t="inlineStr">
         <is>
           <t>非上場のため定量データ開示範囲を要相談</t>
         </is>
       </c>
-      <c r="X11" s="14" t="inlineStr"/>
-      <c r="Y11" s="7" t="inlineStr"/>
-      <c r="Z11" s="8" t="inlineStr">
+      <c r="Y11" s="15" t="inlineStr"/>
+      <c r="Z11" s="7" t="inlineStr"/>
+      <c r="AA11" s="8" t="inlineStr">
         <is>
           <t>建築用水性塗料のリファレンスとして最重要</t>
         </is>
       </c>
     </row>
     <row r="12" ht="68" customHeight="1">
-      <c r="A12" s="19" t="n">
+      <c r="A12" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>中堅総合</t>
         </is>
@@ -2107,46 +2160,46 @@
           <t>ロックペイント</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>大阪市西淀川区</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="F12" s="15" t="inlineStr">
         <is>
           <t>非上場</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>約220億円規模(推定)</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>約700人</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>自動車補修・建築・工業</t>
         </is>
       </c>
-      <c r="I12" s="15" t="inlineStr">
+      <c r="J12" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="J12" s="16" t="inlineStr">
+      <c r="K12" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="K12" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="L12" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -2157,67 +2210,72 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N12" s="8" t="inlineStr">
+      <c r="N12" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O12" s="8" t="inlineStr">
         <is>
           <t>大阪・名古屋</t>
         </is>
       </c>
-      <c r="O12" s="17" t="inlineStr">
+      <c r="P12" s="18" t="inlineStr">
         <is>
           <t>https://www.rockpaint.co.jp/</t>
         </is>
       </c>
-      <c r="P12" s="7" t="inlineStr">
+      <c r="Q12" s="7" t="inlineStr">
         <is>
           <t>営業本部</t>
         </is>
       </c>
-      <c r="Q12" s="14" t="inlineStr">
+      <c r="R12" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="R12" s="8" t="inlineStr">
+      <c r="S12" s="8" t="inlineStr">
         <is>
           <t>2液型補修塗料の④⑤調色・⑧充填</t>
         </is>
       </c>
-      <c r="S12" s="8" t="inlineStr">
+      <c r="T12" s="8" t="inlineStr">
         <is>
           <t>2液型のポットライフ管理・小ロットCCM導入率</t>
         </is>
       </c>
-      <c r="T12" s="21" t="n">
+      <c r="U12" s="23" t="n">
         <v>78</v>
       </c>
-      <c r="U12" s="8" t="inlineStr">
+      <c r="V12" s="8" t="inlineStr">
         <is>
           <t>営業 / 補修工場経由</t>
         </is>
       </c>
-      <c r="V12" s="8" t="inlineStr">
+      <c r="W12" s="8" t="inlineStr">
         <is>
           <t>ディーラー・板金工場経由</t>
         </is>
       </c>
-      <c r="W12" s="8" t="inlineStr">
+      <c r="X12" s="8" t="inlineStr">
         <is>
           <t>色見本データは機密性高</t>
         </is>
       </c>
-      <c r="X12" s="14" t="inlineStr"/>
-      <c r="Y12" s="7" t="inlineStr"/>
-      <c r="Z12" s="8" t="inlineStr">
+      <c r="Y12" s="15" t="inlineStr"/>
+      <c r="Z12" s="7" t="inlineStr"/>
+      <c r="AA12" s="8" t="inlineStr">
         <is>
           <t>自動車補修の代表的リファレンス</t>
         </is>
       </c>
     </row>
     <row r="13" ht="68" customHeight="1">
-      <c r="A13" s="19" t="n">
+      <c r="A13" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>中堅総合</t>
         </is>
@@ -2227,117 +2285,118 @@
           <t>武蔵塗料ホールディングス</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr"/>
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>東京都北区</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="F13" s="15" t="inlineStr">
         <is>
           <t>非上場</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>約300億円規模(推定)</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>約800人(連結)</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
+      <c r="I13" s="8" t="inlineStr">
         <is>
           <t>工業用・電子部品・粉体・海外展開</t>
         </is>
       </c>
-      <c r="I13" s="16" t="inlineStr">
+      <c r="J13" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J13" s="16" t="inlineStr">
+      <c r="K13" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="K13" s="15" t="inlineStr">
+      <c r="L13" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="L13" s="20" t="inlineStr">
+      <c r="M13" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="M13" s="16" t="inlineStr">
+      <c r="N13" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="N13" s="8" t="inlineStr">
+      <c r="O13" s="8" t="inlineStr">
         <is>
           <t>栃木・東京・海外(中国・東南アジア)</t>
         </is>
       </c>
-      <c r="O13" s="17" t="inlineStr">
+      <c r="P13" s="18" t="inlineStr">
         <is>
           <t>https://www.musashipaint.co.jp/</t>
         </is>
       </c>
-      <c r="P13" s="7" t="inlineStr">
+      <c r="Q13" s="7" t="inlineStr">
         <is>
           <t>本社</t>
         </is>
       </c>
-      <c r="Q13" s="14" t="inlineStr">
+      <c r="R13" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="R13" s="8" t="inlineStr">
+      <c r="S13" s="8" t="inlineStr">
         <is>
           <t>粉体塗料の①〜⑦, 海外工場比較</t>
         </is>
       </c>
-      <c r="S13" s="8" t="inlineStr">
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>押出機消費電力・粉砕粒度管理・分級ロス率</t>
         </is>
       </c>
-      <c r="T13" s="21" t="n">
+      <c r="U13" s="23" t="n">
         <v>80</v>
       </c>
-      <c r="U13" s="8" t="inlineStr">
+      <c r="V13" s="8" t="inlineStr">
         <is>
           <t>技術部門 / 海外拠点</t>
         </is>
       </c>
-      <c r="V13" s="8" t="inlineStr">
+      <c r="W13" s="8" t="inlineStr">
         <is>
           <t>家電・電子業界経由</t>
         </is>
       </c>
-      <c r="W13" s="8" t="inlineStr">
+      <c r="X13" s="8" t="inlineStr">
         <is>
           <t>海外グループの統一データ取得は難</t>
         </is>
       </c>
-      <c r="X13" s="14" t="inlineStr"/>
-      <c r="Y13" s="7" t="inlineStr"/>
-      <c r="Z13" s="8" t="inlineStr">
+      <c r="Y13" s="15" t="inlineStr"/>
+      <c r="Z13" s="7" t="inlineStr"/>
+      <c r="AA13" s="8" t="inlineStr">
         <is>
           <t>粉体塗料の代表ヒアリング先</t>
         </is>
       </c>
     </row>
     <row r="14" ht="68" customHeight="1">
-      <c r="A14" s="19" t="n">
+      <c r="A14" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>中堅総合</t>
         </is>
@@ -2347,117 +2406,118 @@
           <t>立川塗料</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr"/>
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>兵庫県川西市</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="F14" s="15" t="inlineStr">
         <is>
           <t>非上場</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>約100億円規模(推定)</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>約300人</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>工業用・自動車部品・建設機械</t>
         </is>
       </c>
-      <c r="I14" s="15" t="inlineStr">
+      <c r="J14" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="J14" s="16" t="inlineStr">
+      <c r="K14" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="K14" s="20" t="inlineStr">
+      <c r="L14" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="L14" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N14" s="8" t="inlineStr">
+      <c r="N14" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O14" s="8" t="inlineStr">
         <is>
           <t>川西・三田</t>
         </is>
       </c>
-      <c r="O14" s="17" t="inlineStr">
+      <c r="P14" s="18" t="inlineStr">
         <is>
           <t>https://www.tachikawatoryo.co.jp/</t>
         </is>
       </c>
-      <c r="P14" s="7" t="inlineStr">
+      <c r="Q14" s="7" t="inlineStr">
         <is>
           <t>本社窓口</t>
         </is>
       </c>
-      <c r="Q14" s="14" t="inlineStr">
+      <c r="R14" s="15" t="inlineStr">
         <is>
           <t>低 (非上場・コーポレートサイトのみ)</t>
         </is>
       </c>
-      <c r="R14" s="8" t="inlineStr">
+      <c r="S14" s="8" t="inlineStr">
         <is>
           <t>工業用塗料の①計量〜⑧充填</t>
         </is>
       </c>
-      <c r="S14" s="8" t="inlineStr">
+      <c r="T14" s="8" t="inlineStr">
         <is>
           <t>中ロット工業塗料の歩留・在庫回転</t>
         </is>
       </c>
-      <c r="T14" s="22" t="n">
+      <c r="U14" s="24" t="n">
         <v>65</v>
       </c>
-      <c r="U14" s="8" t="inlineStr">
+      <c r="V14" s="8" t="inlineStr">
         <is>
           <t>業界団体経由・取引先紹介</t>
         </is>
       </c>
-      <c r="V14" s="8" t="inlineStr">
+      <c r="W14" s="8" t="inlineStr">
         <is>
           <t>建機メーカー経由</t>
         </is>
       </c>
-      <c r="W14" s="8" t="inlineStr">
+      <c r="X14" s="8" t="inlineStr">
         <is>
           <t>中小規模のため工場見学受入余力要確認</t>
         </is>
       </c>
-      <c r="X14" s="14" t="inlineStr"/>
-      <c r="Y14" s="7" t="inlineStr"/>
-      <c r="Z14" s="8" t="inlineStr">
+      <c r="Y14" s="15" t="inlineStr"/>
+      <c r="Z14" s="7" t="inlineStr"/>
+      <c r="AA14" s="8" t="inlineStr">
         <is>
           <t>中堅独立系の代表例</t>
         </is>
       </c>
     </row>
     <row r="15" ht="68" customHeight="1">
-      <c r="A15" s="23" t="n">
+      <c r="A15" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="25" t="inlineStr">
         <is>
           <t>自動車補修</t>
         </is>
@@ -2467,46 +2527,42 @@
           <t>イサム塗料</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr"/>
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>大阪市住之江区</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="F15" s="15" t="inlineStr">
         <is>
           <t>非上場</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>約160億円規模(推定)</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>約450人</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
+      <c r="I15" s="8" t="inlineStr">
         <is>
           <t>自動車補修・工業</t>
         </is>
       </c>
-      <c r="I15" s="15" t="inlineStr">
+      <c r="J15" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="J15" s="20" t="inlineStr">
+      <c r="K15" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="K15" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="L15" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -2517,67 +2573,72 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N15" s="8" t="inlineStr">
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O15" s="8" t="inlineStr">
         <is>
           <t>大阪・茨城</t>
         </is>
       </c>
-      <c r="O15" s="17" t="inlineStr">
+      <c r="P15" s="18" t="inlineStr">
         <is>
           <t>https://www.isamu.co.jp/</t>
         </is>
       </c>
-      <c r="P15" s="7" t="inlineStr">
+      <c r="Q15" s="7" t="inlineStr">
         <is>
           <t>本社問合せ</t>
         </is>
       </c>
-      <c r="Q15" s="14" t="inlineStr">
+      <c r="R15" s="15" t="inlineStr">
         <is>
           <t>低〜中</t>
         </is>
       </c>
-      <c r="R15" s="8" t="inlineStr">
+      <c r="S15" s="8" t="inlineStr">
         <is>
           <t>補修塗料の④⑤調色・⑥ろ過</t>
         </is>
       </c>
-      <c r="S15" s="8" t="inlineStr">
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>小ロット調色のサンプル廃棄率</t>
         </is>
       </c>
-      <c r="T15" s="22" t="n">
+      <c r="U15" s="24" t="n">
         <v>70</v>
       </c>
-      <c r="U15" s="8" t="inlineStr">
+      <c r="V15" s="8" t="inlineStr">
         <is>
           <t>営業・既存取引</t>
         </is>
       </c>
-      <c r="V15" s="8" t="inlineStr">
+      <c r="W15" s="8" t="inlineStr">
         <is>
           <t>板金塗装業界経由</t>
         </is>
       </c>
-      <c r="W15" s="8" t="inlineStr">
+      <c r="X15" s="8" t="inlineStr">
         <is>
           <t>ロックペイントと役割が重なる場合あり</t>
         </is>
       </c>
-      <c r="X15" s="14" t="inlineStr"/>
-      <c r="Y15" s="7" t="inlineStr"/>
-      <c r="Z15" s="8" t="inlineStr">
+      <c r="Y15" s="15" t="inlineStr"/>
+      <c r="Z15" s="7" t="inlineStr"/>
+      <c r="AA15" s="8" t="inlineStr">
         <is>
           <t>ロックペイントとの比較対象</t>
         </is>
       </c>
     </row>
     <row r="16" ht="68" customHeight="1">
-      <c r="A16" s="23" t="n">
+      <c r="A16" s="25" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>自動車補修</t>
         </is>
@@ -2587,46 +2648,42 @@
           <t>ホーマー技研</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr"/>
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>東京都品川区</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr">
+      <c r="F16" s="15" t="inlineStr">
         <is>
           <t>非上場</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>数十億円規模(推定)</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>約100人(推定)</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>自動車補修副資材・特殊塗料</t>
         </is>
       </c>
-      <c r="I16" s="16" t="inlineStr">
+      <c r="J16" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J16" s="20" t="inlineStr">
+      <c r="K16" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="K16" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="L16" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -2637,67 +2694,72 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N16" s="8" t="inlineStr">
+      <c r="N16" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O16" s="8" t="inlineStr">
         <is>
           <t>(要確認)</t>
         </is>
       </c>
-      <c r="O16" s="17" t="inlineStr">
+      <c r="P16" s="18" t="inlineStr">
         <is>
           <t>https://www.homer-jp.com/</t>
         </is>
       </c>
-      <c r="P16" s="7" t="inlineStr">
+      <c r="Q16" s="7" t="inlineStr">
         <is>
           <t>本社問合せ</t>
         </is>
       </c>
-      <c r="Q16" s="24" t="inlineStr">
+      <c r="R16" s="26" t="inlineStr">
         <is>
           <t>低 (要確認)</t>
         </is>
       </c>
-      <c r="R16" s="8" t="inlineStr">
+      <c r="S16" s="8" t="inlineStr">
         <is>
           <t>補修副資材の充填工程</t>
         </is>
       </c>
-      <c r="S16" s="8" t="inlineStr">
+      <c r="T16" s="8" t="inlineStr">
         <is>
           <t>副資材の SKU 数・小ロット運用</t>
         </is>
       </c>
-      <c r="T16" s="25" t="n">
+      <c r="U16" s="27" t="n">
         <v>55</v>
       </c>
-      <c r="U16" s="8" t="inlineStr">
+      <c r="V16" s="8" t="inlineStr">
         <is>
           <t>営業窓口</t>
         </is>
       </c>
-      <c r="V16" s="8" t="inlineStr">
+      <c r="W16" s="8" t="inlineStr">
         <is>
           <t>板金塗装業界経由</t>
         </is>
       </c>
-      <c r="W16" s="8" t="inlineStr">
+      <c r="X16" s="8" t="inlineStr">
         <is>
           <t>塗料本体ではなく補修副資材寄りの可能性</t>
         </is>
       </c>
-      <c r="X16" s="14" t="inlineStr"/>
-      <c r="Y16" s="7" t="inlineStr"/>
-      <c r="Z16" s="8" t="inlineStr">
+      <c r="Y16" s="15" t="inlineStr"/>
+      <c r="Z16" s="7" t="inlineStr"/>
+      <c r="AA16" s="8" t="inlineStr">
         <is>
           <t>周辺領域として参考</t>
         </is>
       </c>
     </row>
     <row r="17" ht="68" customHeight="1">
-      <c r="A17" s="26" t="n">
+      <c r="A17" s="28" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="26" t="inlineStr">
+      <c r="B17" s="28" t="inlineStr">
         <is>
           <t>建築・仕上塗材</t>
         </is>
@@ -2707,117 +2769,118 @@
           <t>スズカファイン</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr"/>
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>三重県鈴鹿市</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="F17" s="15" t="inlineStr">
         <is>
           <t>非上場</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>約230億円規模(推定)</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>約600人</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
+      <c r="I17" s="8" t="inlineStr">
         <is>
           <t>建築仕上塗材・水性塗料</t>
         </is>
       </c>
-      <c r="I17" s="16" t="inlineStr">
+      <c r="J17" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J17" s="15" t="inlineStr">
+      <c r="K17" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="K17" s="20" t="inlineStr">
+      <c r="L17" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="L17" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="M17" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N17" s="8" t="inlineStr">
+      <c r="N17" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O17" s="8" t="inlineStr">
         <is>
           <t>鈴鹿・関東</t>
         </is>
       </c>
-      <c r="O17" s="17" t="inlineStr">
+      <c r="P17" s="18" t="inlineStr">
         <is>
           <t>https://www.suzukafine.co.jp/</t>
         </is>
       </c>
-      <c r="P17" s="7" t="inlineStr">
+      <c r="Q17" s="7" t="inlineStr">
         <is>
           <t>本社問合せ</t>
         </is>
       </c>
-      <c r="Q17" s="14" t="inlineStr">
+      <c r="R17" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="R17" s="8" t="inlineStr">
+      <c r="S17" s="8" t="inlineStr">
         <is>
           <t>仕上塗材の②分散・⑤調色</t>
         </is>
       </c>
-      <c r="S17" s="8" t="inlineStr">
+      <c r="T17" s="8" t="inlineStr">
         <is>
           <t>仕上塗材の粒径管理・水性化率</t>
         </is>
       </c>
-      <c r="T17" s="21" t="n">
+      <c r="U17" s="23" t="n">
         <v>76</v>
       </c>
-      <c r="U17" s="8" t="inlineStr">
+      <c r="V17" s="8" t="inlineStr">
         <is>
           <t>技術部門</t>
         </is>
       </c>
-      <c r="V17" s="8" t="inlineStr">
+      <c r="W17" s="8" t="inlineStr">
         <is>
           <t>ゼネコン経由</t>
         </is>
       </c>
-      <c r="W17" s="8" t="inlineStr">
+      <c r="X17" s="8" t="inlineStr">
         <is>
           <t>仕上塗材は塗料分類で特殊な扱い</t>
         </is>
       </c>
-      <c r="X17" s="14" t="inlineStr"/>
-      <c r="Y17" s="7" t="inlineStr"/>
-      <c r="Z17" s="8" t="inlineStr">
+      <c r="Y17" s="15" t="inlineStr"/>
+      <c r="Z17" s="7" t="inlineStr"/>
+      <c r="AA17" s="8" t="inlineStr">
         <is>
           <t>建築仕上塗材の代表</t>
         </is>
       </c>
     </row>
     <row r="18" ht="68" customHeight="1">
-      <c r="A18" s="26" t="n">
+      <c r="A18" s="28" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>建築・仕上塗材</t>
         </is>
@@ -2827,117 +2890,118 @@
           <t>菊水化学工業</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr"/>
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>名古屋市中区</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr">
+      <c r="F18" s="15" t="inlineStr">
         <is>
           <t>東証スタンダード</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t>約220億円</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>約500人(連結)</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="I18" s="8" t="inlineStr">
         <is>
           <t>建築仕上塗材・防水・耐火塗料</t>
         </is>
       </c>
-      <c r="I18" s="16" t="inlineStr">
+      <c r="J18" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J18" s="15" t="inlineStr">
+      <c r="K18" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="K18" s="20" t="inlineStr">
+      <c r="L18" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="L18" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="M18" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N18" s="8" t="inlineStr">
+      <c r="N18" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O18" s="8" t="inlineStr">
         <is>
           <t>愛知・茨城</t>
         </is>
       </c>
-      <c r="O18" s="17" t="inlineStr">
+      <c r="P18" s="18" t="inlineStr">
         <is>
           <t>https://www.kikusui-chem.co.jp/</t>
         </is>
       </c>
-      <c r="P18" s="7" t="inlineStr">
+      <c r="Q18" s="7" t="inlineStr">
         <is>
           <t>IR担当</t>
         </is>
       </c>
-      <c r="Q18" s="14" t="inlineStr">
+      <c r="R18" s="15" t="inlineStr">
         <is>
           <t>中〜高</t>
         </is>
       </c>
-      <c r="R18" s="8" t="inlineStr">
+      <c r="S18" s="8" t="inlineStr">
         <is>
           <t>仕上塗材・防水材の③④⑤</t>
         </is>
       </c>
-      <c r="S18" s="8" t="inlineStr">
+      <c r="T18" s="8" t="inlineStr">
         <is>
           <t>防水材の固形分管理、耐火塗料の塗膜厚</t>
         </is>
       </c>
-      <c r="T18" s="22" t="n">
+      <c r="U18" s="24" t="n">
         <v>74</v>
       </c>
-      <c r="U18" s="8" t="inlineStr">
+      <c r="V18" s="8" t="inlineStr">
         <is>
           <t>IR / 技術部門</t>
         </is>
       </c>
-      <c r="V18" s="8" t="inlineStr">
+      <c r="W18" s="8" t="inlineStr">
         <is>
           <t>ゼネコン経由</t>
         </is>
       </c>
-      <c r="W18" s="8" t="inlineStr">
+      <c r="X18" s="8" t="inlineStr">
         <is>
           <t>耐火塗料は機密性高</t>
         </is>
       </c>
-      <c r="X18" s="14" t="inlineStr"/>
-      <c r="Y18" s="7" t="inlineStr"/>
-      <c r="Z18" s="8" t="inlineStr">
+      <c r="Y18" s="15" t="inlineStr"/>
+      <c r="Z18" s="7" t="inlineStr"/>
+      <c r="AA18" s="8" t="inlineStr">
         <is>
           <t>上場の建築特化メーカー</t>
         </is>
       </c>
     </row>
     <row r="19" ht="68" customHeight="1">
-      <c r="A19" s="26" t="n">
+      <c r="A19" s="28" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="26" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>建築・仕上塗材</t>
         </is>
@@ -2947,117 +3011,118 @@
           <t>フッコー</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr"/>
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>兵庫県神戸市</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="F19" s="15" t="inlineStr">
         <is>
           <t>非上場</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>約60億円規模(推定)</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>約200人</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>建築仕上塗材</t>
         </is>
       </c>
-      <c r="I19" s="20" t="inlineStr">
+      <c r="J19" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="J19" s="15" t="inlineStr">
+      <c r="K19" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="K19" s="20" t="inlineStr">
+      <c r="L19" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="L19" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="M19" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N19" s="8" t="inlineStr">
+      <c r="N19" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O19" s="8" t="inlineStr">
         <is>
           <t>兵庫・関東</t>
         </is>
       </c>
-      <c r="O19" s="17" t="inlineStr">
+      <c r="P19" s="18" t="inlineStr">
         <is>
           <t>https://www.fukko.co.jp/</t>
         </is>
       </c>
-      <c r="P19" s="7" t="inlineStr">
+      <c r="Q19" s="7" t="inlineStr">
         <is>
           <t>本社問合せ</t>
         </is>
       </c>
-      <c r="Q19" s="14" t="inlineStr">
+      <c r="R19" s="15" t="inlineStr">
         <is>
           <t>低〜中</t>
         </is>
       </c>
-      <c r="R19" s="8" t="inlineStr">
+      <c r="S19" s="8" t="inlineStr">
         <is>
           <t>仕上塗材の②分散・⑤調色</t>
         </is>
       </c>
-      <c r="S19" s="8" t="inlineStr">
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>仕上塗材中小プラントの規模感</t>
         </is>
       </c>
-      <c r="T19" s="25" t="n">
+      <c r="U19" s="27" t="n">
         <v>58</v>
       </c>
-      <c r="U19" s="8" t="inlineStr">
+      <c r="V19" s="8" t="inlineStr">
         <is>
           <t>営業窓口</t>
         </is>
       </c>
-      <c r="V19" s="8" t="inlineStr">
+      <c r="W19" s="8" t="inlineStr">
         <is>
           <t>建材販売店経由</t>
         </is>
       </c>
-      <c r="W19" s="8" t="inlineStr">
+      <c r="X19" s="8" t="inlineStr">
         <is>
           <t>中小規模ゆえスケール感に注意</t>
         </is>
       </c>
-      <c r="X19" s="14" t="inlineStr"/>
-      <c r="Y19" s="7" t="inlineStr"/>
-      <c r="Z19" s="8" t="inlineStr">
+      <c r="Y19" s="15" t="inlineStr"/>
+      <c r="Z19" s="7" t="inlineStr"/>
+      <c r="AA19" s="8" t="inlineStr">
         <is>
           <t>中小建築塗材の補強</t>
         </is>
       </c>
     </row>
     <row r="20" ht="68" customHeight="1">
-      <c r="A20" s="26" t="n">
+      <c r="A20" s="28" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="26" t="inlineStr">
+      <c r="B20" s="28" t="inlineStr">
         <is>
           <t>建築・仕上塗材</t>
         </is>
@@ -3067,117 +3132,118 @@
           <t>アトミクス</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="14" t="inlineStr"/>
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>東京都荒川区</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr">
+      <c r="F20" s="15" t="inlineStr">
         <is>
           <t>非上場</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="G20" s="7" t="inlineStr">
         <is>
           <t>約180億円規模(推定)</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>約500人</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
+      <c r="I20" s="8" t="inlineStr">
         <is>
           <t>床用塗料・建築・水性</t>
         </is>
       </c>
-      <c r="I20" s="15" t="inlineStr">
+      <c r="J20" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="J20" s="15" t="inlineStr">
+      <c r="K20" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="K20" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="L20" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M20" s="20" t="inlineStr">
+      <c r="M20" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="N20" s="8" t="inlineStr">
+      <c r="O20" s="8" t="inlineStr">
         <is>
           <t>茨城・千葉</t>
         </is>
       </c>
-      <c r="O20" s="17" t="inlineStr">
+      <c r="P20" s="18" t="inlineStr">
         <is>
           <t>https://www.atomix.co.jp/</t>
         </is>
       </c>
-      <c r="P20" s="7" t="inlineStr">
+      <c r="Q20" s="7" t="inlineStr">
         <is>
           <t>本社問合せ</t>
         </is>
       </c>
-      <c r="Q20" s="14" t="inlineStr">
+      <c r="R20" s="15" t="inlineStr">
         <is>
           <t>低〜中</t>
         </is>
       </c>
-      <c r="R20" s="8" t="inlineStr">
+      <c r="S20" s="8" t="inlineStr">
         <is>
           <t>水性床塗料の②分散・⑤調色</t>
         </is>
       </c>
-      <c r="S20" s="8" t="inlineStr">
+      <c r="T20" s="8" t="inlineStr">
         <is>
           <t>床用塗料の固形分・耐摩耗性管理</t>
         </is>
       </c>
-      <c r="T20" s="22" t="n">
+      <c r="U20" s="24" t="n">
         <v>68</v>
       </c>
-      <c r="U20" s="8" t="inlineStr">
+      <c r="V20" s="8" t="inlineStr">
         <is>
           <t>営業・技術窓口</t>
         </is>
       </c>
-      <c r="V20" s="8" t="inlineStr">
+      <c r="W20" s="8" t="inlineStr">
         <is>
           <t>ゼネコン経由</t>
         </is>
       </c>
-      <c r="W20" s="8" t="inlineStr">
+      <c r="X20" s="8" t="inlineStr">
         <is>
           <t>床塗料特化のため一般用との差異に注意</t>
         </is>
       </c>
-      <c r="X20" s="14" t="inlineStr"/>
-      <c r="Y20" s="7" t="inlineStr"/>
-      <c r="Z20" s="8" t="inlineStr">
+      <c r="Y20" s="15" t="inlineStr"/>
+      <c r="Z20" s="7" t="inlineStr"/>
+      <c r="AA20" s="8" t="inlineStr">
         <is>
           <t>床塗料のニッチ事例</t>
         </is>
       </c>
     </row>
     <row r="21" ht="68" customHeight="1">
-      <c r="A21" s="26" t="n">
+      <c r="A21" s="28" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="26" t="inlineStr">
+      <c r="B21" s="28" t="inlineStr">
         <is>
           <t>建築・仕上塗材</t>
         </is>
@@ -3187,117 +3253,118 @@
           <t>大同塗料</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D21" s="14" t="inlineStr"/>
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>大阪市西成区</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="F21" s="15" t="inlineStr">
         <is>
           <t>非上場</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="G21" s="7" t="inlineStr">
         <is>
           <t>約100億円規模(推定)</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>約300人</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
+      <c r="I21" s="8" t="inlineStr">
         <is>
           <t>建築・橋梁・構造物</t>
         </is>
       </c>
-      <c r="I21" s="15" t="inlineStr">
+      <c r="J21" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="J21" s="16" t="inlineStr">
+      <c r="K21" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="K21" s="20" t="inlineStr">
+      <c r="L21" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="L21" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="M21" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N21" s="8" t="inlineStr">
+      <c r="N21" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O21" s="8" t="inlineStr">
         <is>
           <t>大阪・茨城</t>
         </is>
       </c>
-      <c r="O21" s="17" t="inlineStr">
+      <c r="P21" s="18" t="inlineStr">
         <is>
           <t>https://www.daidotoryo.co.jp/</t>
         </is>
       </c>
-      <c r="P21" s="7" t="inlineStr">
+      <c r="Q21" s="7" t="inlineStr">
         <is>
           <t>本社問合せ</t>
         </is>
       </c>
-      <c r="Q21" s="14" t="inlineStr">
+      <c r="R21" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="R21" s="8" t="inlineStr">
+      <c r="S21" s="8" t="inlineStr">
         <is>
           <t>重防食塗料の③④⑤・⑧充填</t>
         </is>
       </c>
-      <c r="S21" s="8" t="inlineStr">
+      <c r="T21" s="8" t="inlineStr">
         <is>
           <t>重防食塗料の固形分管理</t>
         </is>
       </c>
-      <c r="T21" s="25" t="n">
+      <c r="U21" s="27" t="n">
         <v>64</v>
       </c>
-      <c r="U21" s="8" t="inlineStr">
+      <c r="V21" s="8" t="inlineStr">
         <is>
           <t>営業窓口</t>
         </is>
       </c>
-      <c r="V21" s="8" t="inlineStr">
+      <c r="W21" s="8" t="inlineStr">
         <is>
           <t>橋梁・構造物業界経由</t>
         </is>
       </c>
-      <c r="W21" s="8" t="inlineStr">
+      <c r="X21" s="8" t="inlineStr">
         <is>
           <t>DNTと顧客領域が重なる</t>
         </is>
       </c>
-      <c r="X21" s="14" t="inlineStr"/>
-      <c r="Y21" s="7" t="inlineStr"/>
-      <c r="Z21" s="8" t="inlineStr">
+      <c r="Y21" s="15" t="inlineStr"/>
+      <c r="Z21" s="7" t="inlineStr"/>
+      <c r="AA21" s="8" t="inlineStr">
         <is>
           <t>中堅防食メーカーの補強</t>
         </is>
       </c>
     </row>
     <row r="22" ht="68" customHeight="1">
-      <c r="A22" s="27" t="n">
+      <c r="A22" s="29" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="27" t="inlineStr">
+      <c r="B22" s="29" t="inlineStr">
         <is>
           <t>機能・特殊</t>
         </is>
@@ -3307,117 +3374,118 @@
           <t>オキツモ</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D22" s="14" t="inlineStr"/>
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>三重県名張市</t>
         </is>
       </c>
-      <c r="E22" s="14" t="inlineStr">
+      <c r="F22" s="15" t="inlineStr">
         <is>
           <t>非上場</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>約60億円規模(推定)</t>
         </is>
       </c>
-      <c r="G22" s="7" t="inlineStr">
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>約200人</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr">
+      <c r="I22" s="8" t="inlineStr">
         <is>
           <t>耐熱塗料・特殊塗料</t>
         </is>
       </c>
-      <c r="I22" s="15" t="inlineStr">
+      <c r="J22" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="J22" s="16" t="inlineStr">
+      <c r="K22" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="K22" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="L22" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M22" s="20" t="inlineStr">
+      <c r="M22" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="N22" s="8" t="inlineStr">
+      <c r="O22" s="8" t="inlineStr">
         <is>
           <t>三重・名張</t>
         </is>
       </c>
-      <c r="O22" s="17" t="inlineStr">
+      <c r="P22" s="18" t="inlineStr">
         <is>
           <t>https://www.okitsumo.co.jp/</t>
         </is>
       </c>
-      <c r="P22" s="7" t="inlineStr">
+      <c r="Q22" s="7" t="inlineStr">
         <is>
           <t>本社問合せ</t>
         </is>
       </c>
-      <c r="Q22" s="14" t="inlineStr">
+      <c r="R22" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="R22" s="8" t="inlineStr">
+      <c r="S22" s="8" t="inlineStr">
         <is>
           <t>耐熱塗料の③分散・⑦検査 (耐熱試験)</t>
         </is>
       </c>
-      <c r="S22" s="8" t="inlineStr">
+      <c r="T22" s="8" t="inlineStr">
         <is>
           <t>シリコーン樹脂取扱、耐熱顔料の分散</t>
         </is>
       </c>
-      <c r="T22" s="25" t="n">
+      <c r="U22" s="27" t="n">
         <v>60</v>
       </c>
-      <c r="U22" s="8" t="inlineStr">
+      <c r="V22" s="8" t="inlineStr">
         <is>
           <t>技術部門</t>
         </is>
       </c>
-      <c r="V22" s="8" t="inlineStr">
+      <c r="W22" s="8" t="inlineStr">
         <is>
           <t>プラント・自動車排気系経由</t>
         </is>
       </c>
-      <c r="W22" s="8" t="inlineStr">
+      <c r="X22" s="8" t="inlineStr">
         <is>
           <t>ニッチ専業のため一般化に注意</t>
         </is>
       </c>
-      <c r="X22" s="14" t="inlineStr"/>
-      <c r="Y22" s="7" t="inlineStr"/>
-      <c r="Z22" s="8" t="inlineStr">
+      <c r="Y22" s="15" t="inlineStr"/>
+      <c r="Z22" s="7" t="inlineStr"/>
+      <c r="AA22" s="8" t="inlineStr">
         <is>
           <t>耐熱塗料のニッチ事例</t>
         </is>
       </c>
     </row>
     <row r="23" ht="68" customHeight="1">
-      <c r="A23" s="27" t="n">
+      <c r="A23" s="29" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="27" t="inlineStr">
+      <c r="B23" s="29" t="inlineStr">
         <is>
           <t>機能・特殊</t>
         </is>
@@ -3427,117 +3495,122 @@
           <t>シンロイヒ</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>東京都品川区</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr">
+      <c r="F23" s="15" t="inlineStr">
         <is>
           <t>非上場</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>約30億円規模(推定)</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>約100人</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr">
+      <c r="I23" s="8" t="inlineStr">
         <is>
           <t>蛍光塗料・特殊塗料</t>
         </is>
       </c>
-      <c r="I23" s="15" t="inlineStr">
+      <c r="J23" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="J23" s="20" t="inlineStr">
+      <c r="K23" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="K23" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="L23" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M23" s="20" t="inlineStr">
+      <c r="M23" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="N23" s="8" t="inlineStr">
+      <c r="O23" s="8" t="inlineStr">
         <is>
           <t>栃木</t>
         </is>
       </c>
-      <c r="O23" s="17" t="inlineStr">
+      <c r="P23" s="18" t="inlineStr">
         <is>
           <t>https://www.sinloihi.co.jp/</t>
         </is>
       </c>
-      <c r="P23" s="7" t="inlineStr">
+      <c r="Q23" s="7" t="inlineStr">
         <is>
           <t>本社問合せ</t>
         </is>
       </c>
-      <c r="Q23" s="14" t="inlineStr">
+      <c r="R23" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="R23" s="8" t="inlineStr">
+      <c r="S23" s="8" t="inlineStr">
         <is>
           <t>蛍光顔料の分散・希釈・充填</t>
         </is>
       </c>
-      <c r="S23" s="8" t="inlineStr">
+      <c r="T23" s="8" t="inlineStr">
         <is>
           <t>蛍光顔料の取扱・退色管理</t>
         </is>
       </c>
-      <c r="T23" s="25" t="n">
+      <c r="U23" s="27" t="n">
         <v>58</v>
       </c>
-      <c r="U23" s="8" t="inlineStr">
+      <c r="V23" s="8" t="inlineStr">
         <is>
           <t>技術部門</t>
         </is>
       </c>
-      <c r="V23" s="8" t="inlineStr">
+      <c r="W23" s="8" t="inlineStr">
         <is>
           <t>安全標識・印刷業界経由</t>
         </is>
       </c>
-      <c r="W23" s="8" t="inlineStr">
+      <c r="X23" s="8" t="inlineStr">
         <is>
           <t>蛍光特殊で一般化困難</t>
         </is>
       </c>
-      <c r="X23" s="14" t="inlineStr"/>
-      <c r="Y23" s="7" t="inlineStr"/>
-      <c r="Z23" s="8" t="inlineStr">
+      <c r="Y23" s="15" t="inlineStr"/>
+      <c r="Z23" s="7" t="inlineStr"/>
+      <c r="AA23" s="8" t="inlineStr">
         <is>
           <t>蛍光特殊事例</t>
         </is>
       </c>
     </row>
     <row r="24" ht="68" customHeight="1">
-      <c r="A24" s="27" t="n">
+      <c r="A24" s="29" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="27" t="inlineStr">
+      <c r="B24" s="29" t="inlineStr">
         <is>
           <t>機能・特殊</t>
         </is>
@@ -3547,117 +3620,122 @@
           <t>ナトコ</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>名古屋市西区</t>
         </is>
       </c>
-      <c r="E24" s="14" t="inlineStr">
+      <c r="F24" s="15" t="inlineStr">
         <is>
           <t>非上場</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="G24" s="7" t="inlineStr">
         <is>
           <t>約170億円規模(推定)</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>約450人</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
+      <c r="I24" s="8" t="inlineStr">
         <is>
           <t>機能性塗料・特殊コーティング</t>
         </is>
       </c>
-      <c r="I24" s="15" t="inlineStr">
+      <c r="J24" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="J24" s="16" t="inlineStr">
+      <c r="K24" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="K24" s="20" t="inlineStr">
+      <c r="L24" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="L24" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M24" s="16" t="inlineStr">
+      <c r="M24" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="N24" s="8" t="inlineStr">
+      <c r="O24" s="8" t="inlineStr">
         <is>
           <t>愛知・茨城</t>
         </is>
       </c>
-      <c r="O24" s="17" t="inlineStr">
+      <c r="P24" s="18" t="inlineStr">
         <is>
           <t>https://www.natoco.co.jp/</t>
         </is>
       </c>
-      <c r="P24" s="7" t="inlineStr">
+      <c r="Q24" s="7" t="inlineStr">
         <is>
           <t>本社問合せ</t>
         </is>
       </c>
-      <c r="Q24" s="14" t="inlineStr">
+      <c r="R24" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="R24" s="8" t="inlineStr">
+      <c r="S24" s="8" t="inlineStr">
         <is>
           <t>機能塗料の③分散・⑦検査</t>
         </is>
       </c>
-      <c r="S24" s="8" t="inlineStr">
+      <c r="T24" s="8" t="inlineStr">
         <is>
           <t>機能塗料の品質規格・小ロット運用</t>
         </is>
       </c>
-      <c r="T24" s="22" t="n">
+      <c r="U24" s="24" t="n">
         <v>72</v>
       </c>
-      <c r="U24" s="8" t="inlineStr">
+      <c r="V24" s="8" t="inlineStr">
         <is>
           <t>技術部門</t>
         </is>
       </c>
-      <c r="V24" s="8" t="inlineStr">
+      <c r="W24" s="8" t="inlineStr">
         <is>
           <t>電子・自動車・建材業界経由</t>
         </is>
       </c>
-      <c r="W24" s="8" t="inlineStr">
+      <c r="X24" s="8" t="inlineStr">
         <is>
           <t>機能特化のため標準フローと差異あり</t>
         </is>
       </c>
-      <c r="X24" s="14" t="inlineStr"/>
-      <c r="Y24" s="7" t="inlineStr"/>
-      <c r="Z24" s="8" t="inlineStr">
+      <c r="Y24" s="15" t="inlineStr"/>
+      <c r="Z24" s="7" t="inlineStr"/>
+      <c r="AA24" s="8" t="inlineStr">
         <is>
           <t>機能塗料の補強</t>
         </is>
       </c>
     </row>
     <row r="25" ht="68" customHeight="1">
-      <c r="A25" s="27" t="n">
+      <c r="A25" s="29" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="27" t="inlineStr">
+      <c r="B25" s="29" t="inlineStr">
         <is>
           <t>機能・特殊</t>
         </is>
@@ -3667,117 +3745,122 @@
           <t>大日精化工業</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>東京都中央区</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="F25" s="15" t="inlineStr">
         <is>
           <t>東証プライム</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>約1,300億円</t>
         </is>
       </c>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>約3,000人(連結)</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
+      <c r="I25" s="8" t="inlineStr">
         <is>
           <t>顔料・着色剤・UV インキ・特殊塗料</t>
         </is>
       </c>
-      <c r="I25" s="16" t="inlineStr">
+      <c r="J25" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J25" s="16" t="inlineStr">
+      <c r="K25" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="K25" s="20" t="inlineStr">
+      <c r="L25" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="L25" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M25" s="15" t="inlineStr">
+      <c r="M25" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="N25" s="8" t="inlineStr">
+      <c r="O25" s="8" t="inlineStr">
         <is>
           <t>千葉・茨城 ほか</t>
         </is>
       </c>
-      <c r="O25" s="17" t="inlineStr">
+      <c r="P25" s="18" t="inlineStr">
         <is>
           <t>https://www.daicolorchem.com/</t>
         </is>
       </c>
-      <c r="P25" s="7" t="inlineStr">
+      <c r="Q25" s="7" t="inlineStr">
         <is>
           <t>IR室</t>
         </is>
       </c>
-      <c r="Q25" s="14" t="inlineStr">
+      <c r="R25" s="15" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="R25" s="8" t="inlineStr">
+      <c r="S25" s="8" t="inlineStr">
         <is>
           <t>顔料分散③ + UV 硬化塗料の①〜⑦</t>
         </is>
       </c>
-      <c r="S25" s="8" t="inlineStr">
+      <c r="T25" s="8" t="inlineStr">
         <is>
           <t>顔料分散のビーズ条件・UV ドーズ</t>
         </is>
       </c>
-      <c r="T25" s="21" t="n">
+      <c r="U25" s="23" t="n">
         <v>82</v>
       </c>
-      <c r="U25" s="8" t="inlineStr">
+      <c r="V25" s="8" t="inlineStr">
         <is>
           <t>技術部門 / IR</t>
         </is>
       </c>
-      <c r="V25" s="8" t="inlineStr">
+      <c r="W25" s="8" t="inlineStr">
         <is>
           <t>印刷インキ業界経由</t>
         </is>
       </c>
-      <c r="W25" s="8" t="inlineStr">
+      <c r="X25" s="8" t="inlineStr">
         <is>
           <t>インキ事業との切り分けが必要</t>
         </is>
       </c>
-      <c r="X25" s="14" t="inlineStr"/>
-      <c r="Y25" s="7" t="inlineStr"/>
-      <c r="Z25" s="8" t="inlineStr">
+      <c r="Y25" s="15" t="inlineStr"/>
+      <c r="Z25" s="7" t="inlineStr"/>
+      <c r="AA25" s="8" t="inlineStr">
         <is>
           <t>顔料-塗料の上下流連結の例</t>
         </is>
       </c>
     </row>
     <row r="26" ht="68" customHeight="1">
-      <c r="A26" s="27" t="n">
+      <c r="A26" s="29" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="27" t="inlineStr">
+      <c r="B26" s="29" t="inlineStr">
         <is>
           <t>機能・特殊</t>
         </is>
@@ -3787,46 +3870,42 @@
           <t>染めQテクノロジィ</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D26" s="14" t="inlineStr"/>
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>千葉県四街道市</t>
         </is>
       </c>
-      <c r="E26" s="14" t="inlineStr">
+      <c r="F26" s="15" t="inlineStr">
         <is>
           <t>非上場</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>約30億円規模(推定)</t>
         </is>
       </c>
-      <c r="G26" s="7" t="inlineStr">
+      <c r="H26" s="7" t="inlineStr">
         <is>
           <t>約100人</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr">
+      <c r="I26" s="8" t="inlineStr">
         <is>
           <t>ナノテク特殊塗料・密着剤</t>
         </is>
       </c>
-      <c r="I26" s="15" t="inlineStr">
+      <c r="J26" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="J26" s="20" t="inlineStr">
+      <c r="K26" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="K26" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="L26" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -3837,67 +3916,72 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N26" s="8" t="inlineStr">
+      <c r="N26" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O26" s="8" t="inlineStr">
         <is>
           <t>千葉</t>
         </is>
       </c>
-      <c r="O26" s="17" t="inlineStr">
+      <c r="P26" s="18" t="inlineStr">
         <is>
           <t>https://somayq.com/</t>
         </is>
       </c>
-      <c r="P26" s="7" t="inlineStr">
+      <c r="Q26" s="7" t="inlineStr">
         <is>
           <t>本社問合せ</t>
         </is>
       </c>
-      <c r="Q26" s="14" t="inlineStr">
+      <c r="R26" s="15" t="inlineStr">
         <is>
           <t>低〜中</t>
         </is>
       </c>
-      <c r="R26" s="8" t="inlineStr">
+      <c r="S26" s="8" t="inlineStr">
         <is>
           <t>特殊塗料の②分散・⑤調色・⑧充填(エアゾール)</t>
         </is>
       </c>
-      <c r="S26" s="8" t="inlineStr">
+      <c r="T26" s="8" t="inlineStr">
         <is>
           <t>密着剤の薄膜形成、エアゾール充填精度</t>
         </is>
       </c>
-      <c r="T26" s="25" t="n">
+      <c r="U26" s="27" t="n">
         <v>60</v>
       </c>
-      <c r="U26" s="8" t="inlineStr">
+      <c r="V26" s="8" t="inlineStr">
         <is>
           <t>営業窓口</t>
         </is>
       </c>
-      <c r="V26" s="8" t="inlineStr">
+      <c r="W26" s="8" t="inlineStr">
         <is>
           <t>DIY・補修業界経由</t>
         </is>
       </c>
-      <c r="W26" s="8" t="inlineStr">
+      <c r="X26" s="8" t="inlineStr">
         <is>
           <t>エアゾール充填が含まれ標準フローと一部異なる</t>
         </is>
       </c>
-      <c r="X26" s="14" t="inlineStr"/>
-      <c r="Y26" s="7" t="inlineStr"/>
-      <c r="Z26" s="8" t="inlineStr">
+      <c r="Y26" s="15" t="inlineStr"/>
+      <c r="Z26" s="7" t="inlineStr"/>
+      <c r="AA26" s="8" t="inlineStr">
         <is>
           <t>ナノテク特殊事例</t>
         </is>
       </c>
     </row>
     <row r="27" ht="68" customHeight="1">
-      <c r="A27" s="27" t="n">
+      <c r="A27" s="29" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="27" t="inlineStr">
+      <c r="B27" s="29" t="inlineStr">
         <is>
           <t>機能・特殊</t>
         </is>
@@ -3907,46 +3991,42 @@
           <t>AGCコーテック</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr"/>
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>東京都千代田区</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
+      <c r="F27" s="15" t="inlineStr">
         <is>
           <t>非上場(AGC系)</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="G27" s="7" t="inlineStr">
         <is>
           <t>約60億円規模(推定)</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>約200人</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr">
+      <c r="I27" s="8" t="inlineStr">
         <is>
           <t>フッ素樹脂塗料・耐候性塗料</t>
         </is>
       </c>
-      <c r="I27" s="15" t="inlineStr">
+      <c r="J27" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="J27" s="16" t="inlineStr">
+      <c r="K27" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="K27" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="L27" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -3957,67 +4037,72 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N27" s="8" t="inlineStr">
+      <c r="N27" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O27" s="8" t="inlineStr">
         <is>
           <t>千葉・福岡</t>
         </is>
       </c>
-      <c r="O27" s="17" t="inlineStr">
+      <c r="P27" s="18" t="inlineStr">
         <is>
           <t>https://www.agccoatech.co.jp/</t>
         </is>
       </c>
-      <c r="P27" s="7" t="inlineStr">
+      <c r="Q27" s="7" t="inlineStr">
         <is>
           <t>本社問合せ</t>
         </is>
       </c>
-      <c r="Q27" s="14" t="inlineStr">
+      <c r="R27" s="15" t="inlineStr">
         <is>
           <t>中 (AGC連結に含む)</t>
         </is>
       </c>
-      <c r="R27" s="8" t="inlineStr">
+      <c r="S27" s="8" t="inlineStr">
         <is>
           <t>フッ素樹脂塗料の③④⑤</t>
         </is>
       </c>
-      <c r="S27" s="8" t="inlineStr">
+      <c r="T27" s="8" t="inlineStr">
         <is>
           <t>フッ素樹脂取扱・耐候性試験</t>
         </is>
       </c>
-      <c r="T27" s="22" t="n">
+      <c r="U27" s="24" t="n">
         <v>70</v>
       </c>
-      <c r="U27" s="8" t="inlineStr">
+      <c r="V27" s="8" t="inlineStr">
         <is>
           <t>技術部門 / AGC経由</t>
         </is>
       </c>
-      <c r="V27" s="8" t="inlineStr">
+      <c r="W27" s="8" t="inlineStr">
         <is>
           <t>建築・インフラ業界経由</t>
         </is>
       </c>
-      <c r="W27" s="8" t="inlineStr">
+      <c r="X27" s="8" t="inlineStr">
         <is>
           <t>フッ素樹脂特化のため一般化に注意</t>
         </is>
       </c>
-      <c r="X27" s="14" t="inlineStr"/>
-      <c r="Y27" s="7" t="inlineStr"/>
-      <c r="Z27" s="8" t="inlineStr">
+      <c r="Y27" s="15" t="inlineStr"/>
+      <c r="Z27" s="7" t="inlineStr"/>
+      <c r="AA27" s="8" t="inlineStr">
         <is>
           <t>高耐候塗料のニッチ事例</t>
         </is>
       </c>
     </row>
     <row r="28" ht="68" customHeight="1">
-      <c r="A28" s="28" t="n">
+      <c r="A28" s="30" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="28" t="inlineStr">
+      <c r="B28" s="30" t="inlineStr">
         <is>
           <t>UV・印刷インキ</t>
         </is>
@@ -4027,117 +4112,118 @@
           <t>十条ケミカル</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D28" s="14" t="inlineStr"/>
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>東京都北区</t>
         </is>
       </c>
-      <c r="E28" s="14" t="inlineStr">
+      <c r="F28" s="15" t="inlineStr">
         <is>
           <t>非上場</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="G28" s="7" t="inlineStr">
         <is>
           <t>約100億円規模(推定)</t>
         </is>
       </c>
-      <c r="G28" s="7" t="inlineStr">
+      <c r="H28" s="7" t="inlineStr">
         <is>
           <t>約300人</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr">
+      <c r="I28" s="8" t="inlineStr">
         <is>
           <t>UV インキ・UV 塗料・印刷</t>
         </is>
       </c>
-      <c r="I28" s="20" t="inlineStr">
+      <c r="J28" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="J28" s="20" t="inlineStr">
+      <c r="K28" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="K28" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="L28" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M28" s="15" t="inlineStr">
+      <c r="M28" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="N28" s="8" t="inlineStr">
+      <c r="O28" s="8" t="inlineStr">
         <is>
           <t>東京・埼玉</t>
         </is>
       </c>
-      <c r="O28" s="17" t="inlineStr">
+      <c r="P28" s="18" t="inlineStr">
         <is>
           <t>https://www.jujochemical.co.jp/</t>
         </is>
       </c>
-      <c r="P28" s="7" t="inlineStr">
+      <c r="Q28" s="7" t="inlineStr">
         <is>
           <t>本社問合せ</t>
         </is>
       </c>
-      <c r="Q28" s="14" t="inlineStr">
+      <c r="R28" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="R28" s="8" t="inlineStr">
+      <c r="S28" s="8" t="inlineStr">
         <is>
           <t>UV塗料の①遮光下計量・②分散・⑤ろ過・⑦充填</t>
         </is>
       </c>
-      <c r="S28" s="8" t="inlineStr">
+      <c r="T28" s="8" t="inlineStr">
         <is>
           <t>光開始剤の取扱・UV照射ドーズ・遮光容器仕様</t>
         </is>
       </c>
-      <c r="T28" s="21" t="n">
+      <c r="U28" s="23" t="n">
         <v>78</v>
       </c>
-      <c r="U28" s="8" t="inlineStr">
+      <c r="V28" s="8" t="inlineStr">
         <is>
           <t>技術 / 営業</t>
         </is>
       </c>
-      <c r="V28" s="8" t="inlineStr">
+      <c r="W28" s="8" t="inlineStr">
         <is>
           <t>印刷業界経由</t>
         </is>
       </c>
-      <c r="W28" s="8" t="inlineStr">
+      <c r="X28" s="8" t="inlineStr">
         <is>
           <t>UVインキとUV塗料の境界に注意</t>
         </is>
       </c>
-      <c r="X28" s="14" t="inlineStr"/>
-      <c r="Y28" s="7" t="inlineStr"/>
-      <c r="Z28" s="8" t="inlineStr">
+      <c r="Y28" s="15" t="inlineStr"/>
+      <c r="Z28" s="7" t="inlineStr"/>
+      <c r="AA28" s="8" t="inlineStr">
         <is>
           <t>UV硬化の最重要ヒアリング先</t>
         </is>
       </c>
     </row>
     <row r="29" ht="68" customHeight="1">
-      <c r="A29" s="28" t="n">
+      <c r="A29" s="30" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="28" t="inlineStr">
+      <c r="B29" s="30" t="inlineStr">
         <is>
           <t>UV・印刷インキ</t>
         </is>
@@ -4147,117 +4233,118 @@
           <t>太陽ホールディングス</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D29" s="14" t="inlineStr"/>
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>埼玉県嵐山町</t>
         </is>
       </c>
-      <c r="E29" s="14" t="inlineStr">
+      <c r="F29" s="15" t="inlineStr">
         <is>
           <t>東証プライム</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="G29" s="7" t="inlineStr">
         <is>
           <t>約820億円</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>約2,200人(連結)</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr">
+      <c r="I29" s="8" t="inlineStr">
         <is>
           <t>電子用UVインキ・ソルダーレジスト・UV塗料</t>
         </is>
       </c>
-      <c r="I29" s="20" t="inlineStr">
+      <c r="J29" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="J29" s="20" t="inlineStr">
+      <c r="K29" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="K29" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="L29" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M29" s="15" t="inlineStr">
+      <c r="M29" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="N29" s="8" t="inlineStr">
+      <c r="O29" s="8" t="inlineStr">
         <is>
           <t>埼玉・台湾・中国</t>
         </is>
       </c>
-      <c r="O29" s="17" t="inlineStr">
+      <c r="P29" s="18" t="inlineStr">
         <is>
           <t>https://www.taiyo-hd.co.jp/</t>
         </is>
       </c>
-      <c r="P29" s="7" t="inlineStr">
+      <c r="Q29" s="7" t="inlineStr">
         <is>
           <t>IR室</t>
         </is>
       </c>
-      <c r="Q29" s="14" t="inlineStr">
+      <c r="R29" s="15" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="R29" s="8" t="inlineStr">
+      <c r="S29" s="8" t="inlineStr">
         <is>
           <t>電子用UV塗料の③分散・⑤ろ過・⑦充填</t>
         </is>
       </c>
-      <c r="S29" s="8" t="inlineStr">
+      <c r="T29" s="8" t="inlineStr">
         <is>
           <t>電子用の微粒子分散・高純度フィルター</t>
         </is>
       </c>
-      <c r="T29" s="21" t="n">
+      <c r="U29" s="23" t="n">
         <v>80</v>
       </c>
-      <c r="U29" s="8" t="inlineStr">
+      <c r="V29" s="8" t="inlineStr">
         <is>
           <t>IR / 技術部門</t>
         </is>
       </c>
-      <c r="V29" s="8" t="inlineStr">
+      <c r="W29" s="8" t="inlineStr">
         <is>
           <t>電子業界経由</t>
         </is>
       </c>
-      <c r="W29" s="8" t="inlineStr">
+      <c r="X29" s="8" t="inlineStr">
         <is>
           <t>電子用は機密性高</t>
         </is>
       </c>
-      <c r="X29" s="14" t="inlineStr"/>
-      <c r="Y29" s="7" t="inlineStr"/>
-      <c r="Z29" s="8" t="inlineStr">
+      <c r="Y29" s="15" t="inlineStr"/>
+      <c r="Z29" s="7" t="inlineStr"/>
+      <c r="AA29" s="8" t="inlineStr">
         <is>
           <t>電子用UVのリファレンス</t>
         </is>
       </c>
     </row>
     <row r="30" ht="68" customHeight="1">
-      <c r="A30" s="28" t="n">
+      <c r="A30" s="30" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="28" t="inlineStr">
+      <c r="B30" s="30" t="inlineStr">
         <is>
           <t>UV・印刷インキ</t>
         </is>
@@ -4267,117 +4354,118 @@
           <t>帝国インキ製造</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D30" s="14" t="inlineStr"/>
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>埼玉県川口市</t>
         </is>
       </c>
-      <c r="E30" s="14" t="inlineStr">
+      <c r="F30" s="15" t="inlineStr">
         <is>
           <t>東証スタンダード</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>約180億円</t>
         </is>
       </c>
-      <c r="G30" s="7" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>約450人(連結)</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr">
+      <c r="I30" s="8" t="inlineStr">
         <is>
           <t>印刷インキ・UV インキ・特殊塗料</t>
         </is>
       </c>
-      <c r="I30" s="20" t="inlineStr">
+      <c r="J30" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="J30" s="20" t="inlineStr">
+      <c r="K30" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="K30" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="L30" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M30" s="15" t="inlineStr">
+      <c r="M30" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="N30" s="8" t="inlineStr">
+      <c r="O30" s="8" t="inlineStr">
         <is>
           <t>川口・千葉</t>
         </is>
       </c>
-      <c r="O30" s="17" t="inlineStr">
+      <c r="P30" s="18" t="inlineStr">
         <is>
           <t>https://www.teikokuink.com/</t>
         </is>
       </c>
-      <c r="P30" s="7" t="inlineStr">
+      <c r="Q30" s="7" t="inlineStr">
         <is>
           <t>IR室</t>
         </is>
       </c>
-      <c r="Q30" s="14" t="inlineStr">
+      <c r="R30" s="15" t="inlineStr">
         <is>
           <t>中〜高</t>
         </is>
       </c>
-      <c r="R30" s="8" t="inlineStr">
+      <c r="S30" s="8" t="inlineStr">
         <is>
           <t>UVインキの③分散・⑦充填</t>
         </is>
       </c>
-      <c r="S30" s="8" t="inlineStr">
+      <c r="T30" s="8" t="inlineStr">
         <is>
           <t>UVインキの分散条件・歩留</t>
         </is>
       </c>
-      <c r="T30" s="22" t="n">
+      <c r="U30" s="24" t="n">
         <v>70</v>
       </c>
-      <c r="U30" s="8" t="inlineStr">
+      <c r="V30" s="8" t="inlineStr">
         <is>
           <t>IR / 技術</t>
         </is>
       </c>
-      <c r="V30" s="8" t="inlineStr">
+      <c r="W30" s="8" t="inlineStr">
         <is>
           <t>印刷業界経由</t>
         </is>
       </c>
-      <c r="W30" s="8" t="inlineStr">
+      <c r="X30" s="8" t="inlineStr">
         <is>
           <t>塗料との境界線</t>
         </is>
       </c>
-      <c r="X30" s="14" t="inlineStr"/>
-      <c r="Y30" s="7" t="inlineStr"/>
-      <c r="Z30" s="8" t="inlineStr">
+      <c r="Y30" s="15" t="inlineStr"/>
+      <c r="Z30" s="7" t="inlineStr"/>
+      <c r="AA30" s="8" t="inlineStr">
         <is>
           <t>UV インキ視点の補強</t>
         </is>
       </c>
     </row>
     <row r="31" ht="68" customHeight="1">
-      <c r="A31" s="28" t="n">
+      <c r="A31" s="30" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="28" t="inlineStr">
+      <c r="B31" s="30" t="inlineStr">
         <is>
           <t>UV・印刷インキ</t>
         </is>
@@ -4387,117 +4475,118 @@
           <t>T&amp;K TOKA</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D31" s="14" t="inlineStr"/>
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>埼玉県狭山市</t>
         </is>
       </c>
-      <c r="E31" s="14" t="inlineStr">
+      <c r="F31" s="15" t="inlineStr">
         <is>
           <t>東証スタンダード</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>約260億円</t>
         </is>
       </c>
-      <c r="G31" s="7" t="inlineStr">
+      <c r="H31" s="7" t="inlineStr">
         <is>
           <t>約700人(連結)</t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr">
+      <c r="I31" s="8" t="inlineStr">
         <is>
           <t>印刷インキ・UV インキ・コーティング</t>
         </is>
       </c>
-      <c r="I31" s="20" t="inlineStr">
+      <c r="J31" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="J31" s="20" t="inlineStr">
+      <c r="K31" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="K31" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="L31" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M31" s="15" t="inlineStr">
+      <c r="M31" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="N31" s="8" t="inlineStr">
+      <c r="O31" s="8" t="inlineStr">
         <is>
           <t>埼玉・大阪</t>
         </is>
       </c>
-      <c r="O31" s="17" t="inlineStr">
+      <c r="P31" s="18" t="inlineStr">
         <is>
           <t>https://www.tk-toka.co.jp/</t>
         </is>
       </c>
-      <c r="P31" s="7" t="inlineStr">
+      <c r="Q31" s="7" t="inlineStr">
         <is>
           <t>IR室</t>
         </is>
       </c>
-      <c r="Q31" s="14" t="inlineStr">
+      <c r="R31" s="15" t="inlineStr">
         <is>
           <t>中〜高</t>
         </is>
       </c>
-      <c r="R31" s="8" t="inlineStr">
+      <c r="S31" s="8" t="inlineStr">
         <is>
           <t>UVコーティングの②分散・⑦充填</t>
         </is>
       </c>
-      <c r="S31" s="8" t="inlineStr">
+      <c r="T31" s="8" t="inlineStr">
         <is>
           <t>UV コーティングのドーズ・密着試験</t>
         </is>
       </c>
-      <c r="T31" s="22" t="n">
+      <c r="U31" s="24" t="n">
         <v>70</v>
       </c>
-      <c r="U31" s="8" t="inlineStr">
+      <c r="V31" s="8" t="inlineStr">
         <is>
           <t>IR / 技術</t>
         </is>
       </c>
-      <c r="V31" s="8" t="inlineStr">
+      <c r="W31" s="8" t="inlineStr">
         <is>
           <t>印刷業界経由</t>
         </is>
       </c>
-      <c r="W31" s="8" t="inlineStr">
+      <c r="X31" s="8" t="inlineStr">
         <is>
           <t>塗料との境界が曖昧</t>
         </is>
       </c>
-      <c r="X31" s="14" t="inlineStr"/>
-      <c r="Y31" s="7" t="inlineStr"/>
-      <c r="Z31" s="8" t="inlineStr">
+      <c r="Y31" s="15" t="inlineStr"/>
+      <c r="Z31" s="7" t="inlineStr"/>
+      <c r="AA31" s="8" t="inlineStr">
         <is>
           <t>UV コーティング系の補強</t>
         </is>
       </c>
     </row>
     <row r="32" ht="68" customHeight="1">
-      <c r="A32" s="28" t="n">
+      <c r="A32" s="30" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="28" t="inlineStr">
+      <c r="B32" s="30" t="inlineStr">
         <is>
           <t>UV・印刷インキ</t>
         </is>
@@ -4507,117 +4596,118 @@
           <t>東洋インキSCホールディングス</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D32" s="14" t="inlineStr"/>
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>東京都中央区</t>
         </is>
       </c>
-      <c r="E32" s="14" t="inlineStr">
+      <c r="F32" s="15" t="inlineStr">
         <is>
           <t>東証プライム</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr">
+      <c r="G32" s="7" t="inlineStr">
         <is>
           <t>約3,400億円(連結)</t>
         </is>
       </c>
-      <c r="G32" s="7" t="inlineStr">
+      <c r="H32" s="7" t="inlineStr">
         <is>
           <t>約8,000人(連結)</t>
         </is>
       </c>
-      <c r="H32" s="8" t="inlineStr">
+      <c r="I32" s="8" t="inlineStr">
         <is>
           <t>印刷インキ・コーティング・ポリマー・色材</t>
         </is>
       </c>
-      <c r="I32" s="16" t="inlineStr">
+      <c r="J32" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J32" s="16" t="inlineStr">
+      <c r="K32" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="K32" s="20" t="inlineStr">
+      <c r="L32" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="L32" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M32" s="15" t="inlineStr">
+      <c r="M32" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="N32" s="8" t="inlineStr">
+      <c r="O32" s="8" t="inlineStr">
         <is>
           <t>埼玉・茨城 ほか</t>
         </is>
       </c>
-      <c r="O32" s="17" t="inlineStr">
+      <c r="P32" s="18" t="inlineStr">
         <is>
           <t>https://schd.toyoinkgroup.com/</t>
         </is>
       </c>
-      <c r="P32" s="7" t="inlineStr">
+      <c r="Q32" s="7" t="inlineStr">
         <is>
           <t>IR室</t>
         </is>
       </c>
-      <c r="Q32" s="14" t="inlineStr">
+      <c r="R32" s="15" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="R32" s="8" t="inlineStr">
+      <c r="S32" s="8" t="inlineStr">
         <is>
           <t>色材③分散 + UV/水性塗料の②〜⑦</t>
         </is>
       </c>
-      <c r="S32" s="8" t="inlineStr">
+      <c r="T32" s="8" t="inlineStr">
         <is>
           <t>顔料分散のスケール、ポリマー設計</t>
         </is>
       </c>
-      <c r="T32" s="21" t="n">
+      <c r="U32" s="23" t="n">
         <v>82</v>
       </c>
-      <c r="U32" s="8" t="inlineStr">
+      <c r="V32" s="8" t="inlineStr">
         <is>
           <t>IR / 技術部門</t>
         </is>
       </c>
-      <c r="V32" s="8" t="inlineStr">
+      <c r="W32" s="8" t="inlineStr">
         <is>
           <t>印刷インキ業界経由</t>
         </is>
       </c>
-      <c r="W32" s="8" t="inlineStr">
+      <c r="X32" s="8" t="inlineStr">
         <is>
           <t>塗料はグループ事業の一部</t>
         </is>
       </c>
-      <c r="X32" s="14" t="inlineStr"/>
-      <c r="Y32" s="7" t="inlineStr"/>
-      <c r="Z32" s="8" t="inlineStr">
+      <c r="Y32" s="15" t="inlineStr"/>
+      <c r="Z32" s="7" t="inlineStr"/>
+      <c r="AA32" s="8" t="inlineStr">
         <is>
           <t>インキ大手の塗料領域比較対象</t>
         </is>
       </c>
     </row>
     <row r="33" ht="68" customHeight="1">
-      <c r="A33" s="28" t="n">
+      <c r="A33" s="30" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="28" t="inlineStr">
+      <c r="B33" s="30" t="inlineStr">
         <is>
           <t>UV・印刷インキ</t>
         </is>
@@ -4627,117 +4717,122 @@
           <t>サカタインクス</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>大阪市西区</t>
         </is>
       </c>
-      <c r="E33" s="14" t="inlineStr">
+      <c r="F33" s="15" t="inlineStr">
         <is>
           <t>東証プライム</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="G33" s="7" t="inlineStr">
         <is>
           <t>約1,700億円(連結)</t>
         </is>
       </c>
-      <c r="G33" s="7" t="inlineStr">
+      <c r="H33" s="7" t="inlineStr">
         <is>
           <t>約4,000人(連結)</t>
         </is>
       </c>
-      <c r="H33" s="8" t="inlineStr">
+      <c r="I33" s="8" t="inlineStr">
         <is>
           <t>印刷インキ・UV インキ・コーティング</t>
         </is>
       </c>
-      <c r="I33" s="20" t="inlineStr">
+      <c r="J33" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="J33" s="20" t="inlineStr">
+      <c r="K33" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="K33" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="L33" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M33" s="15" t="inlineStr">
+      <c r="M33" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="N33" s="8" t="inlineStr">
+      <c r="O33" s="8" t="inlineStr">
         <is>
           <t>大阪・東京 ほか</t>
         </is>
       </c>
-      <c r="O33" s="17" t="inlineStr">
+      <c r="P33" s="18" t="inlineStr">
         <is>
           <t>https://www.inx.co.jp/</t>
         </is>
       </c>
-      <c r="P33" s="7" t="inlineStr">
+      <c r="Q33" s="7" t="inlineStr">
         <is>
           <t>IR室</t>
         </is>
       </c>
-      <c r="Q33" s="14" t="inlineStr">
+      <c r="R33" s="15" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="R33" s="8" t="inlineStr">
+      <c r="S33" s="8" t="inlineStr">
         <is>
           <t>UVインキの②分散・⑤ろ過・⑦充填</t>
         </is>
       </c>
-      <c r="S33" s="8" t="inlineStr">
+      <c r="T33" s="8" t="inlineStr">
         <is>
           <t>印刷インキ生産の歩留・廃棄物</t>
         </is>
       </c>
-      <c r="T33" s="21" t="n">
+      <c r="U33" s="23" t="n">
         <v>75</v>
       </c>
-      <c r="U33" s="8" t="inlineStr">
+      <c r="V33" s="8" t="inlineStr">
         <is>
           <t>IR / 技術</t>
         </is>
       </c>
-      <c r="V33" s="8" t="inlineStr">
+      <c r="W33" s="8" t="inlineStr">
         <is>
           <t>印刷業界経由</t>
         </is>
       </c>
-      <c r="W33" s="8" t="inlineStr">
+      <c r="X33" s="8" t="inlineStr">
         <is>
           <t>塗料事業は限定的</t>
         </is>
       </c>
-      <c r="X33" s="14" t="inlineStr"/>
-      <c r="Y33" s="7" t="inlineStr"/>
-      <c r="Z33" s="8" t="inlineStr">
+      <c r="Y33" s="15" t="inlineStr"/>
+      <c r="Z33" s="7" t="inlineStr"/>
+      <c r="AA33" s="8" t="inlineStr">
         <is>
           <t>インキ大手の比較材料</t>
         </is>
       </c>
     </row>
     <row r="34" ht="68" customHeight="1">
-      <c r="A34" s="28" t="n">
+      <c r="A34" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="28" t="inlineStr">
+      <c r="B34" s="30" t="inlineStr">
         <is>
           <t>UV・印刷インキ</t>
         </is>
@@ -4747,117 +4842,118 @@
           <t>オリジン</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D34" s="14" t="inlineStr"/>
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>東京都板橋区</t>
         </is>
       </c>
-      <c r="E34" s="14" t="inlineStr">
+      <c r="F34" s="15" t="inlineStr">
         <is>
           <t>東証スタンダード</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="G34" s="7" t="inlineStr">
         <is>
           <t>約260億円</t>
         </is>
       </c>
-      <c r="G34" s="7" t="inlineStr">
+      <c r="H34" s="7" t="inlineStr">
         <is>
           <t>約800人(連結)</t>
         </is>
       </c>
-      <c r="H34" s="8" t="inlineStr">
+      <c r="I34" s="8" t="inlineStr">
         <is>
           <t>UV 塗料・電着・電子用塗料</t>
         </is>
       </c>
-      <c r="I34" s="16" t="inlineStr">
+      <c r="J34" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J34" s="16" t="inlineStr">
+      <c r="K34" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="K34" s="20" t="inlineStr">
+      <c r="L34" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="L34" s="16" t="inlineStr">
+      <c r="M34" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="M34" s="15" t="inlineStr">
+      <c r="N34" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="N34" s="8" t="inlineStr">
+      <c r="O34" s="8" t="inlineStr">
         <is>
           <t>東京・神奈川</t>
         </is>
       </c>
-      <c r="O34" s="17" t="inlineStr">
+      <c r="P34" s="18" t="inlineStr">
         <is>
           <t>https://www.origin.co.jp/</t>
         </is>
       </c>
-      <c r="P34" s="7" t="inlineStr">
+      <c r="Q34" s="7" t="inlineStr">
         <is>
           <t>IR室</t>
         </is>
       </c>
-      <c r="Q34" s="14" t="inlineStr">
+      <c r="R34" s="15" t="inlineStr">
         <is>
           <t>中〜高</t>
         </is>
       </c>
-      <c r="R34" s="8" t="inlineStr">
+      <c r="S34" s="8" t="inlineStr">
         <is>
           <t>UV・電着塗料の②③⑤⑦</t>
         </is>
       </c>
-      <c r="S34" s="8" t="inlineStr">
+      <c r="T34" s="8" t="inlineStr">
         <is>
           <t>UV ドーズ管理、電着の電気伝導度</t>
         </is>
       </c>
-      <c r="T34" s="21" t="n">
+      <c r="U34" s="23" t="n">
         <v>80</v>
       </c>
-      <c r="U34" s="8" t="inlineStr">
+      <c r="V34" s="8" t="inlineStr">
         <is>
           <t>IR / 技術</t>
         </is>
       </c>
-      <c r="V34" s="8" t="inlineStr">
+      <c r="W34" s="8" t="inlineStr">
         <is>
           <t>電子業界経由</t>
         </is>
       </c>
-      <c r="W34" s="8" t="inlineStr">
+      <c r="X34" s="8" t="inlineStr">
         <is>
           <t>電気事業との切り分け</t>
         </is>
       </c>
-      <c r="X34" s="14" t="inlineStr"/>
-      <c r="Y34" s="7" t="inlineStr"/>
-      <c r="Z34" s="8" t="inlineStr">
+      <c r="Y34" s="15" t="inlineStr"/>
+      <c r="Z34" s="7" t="inlineStr"/>
+      <c r="AA34" s="8" t="inlineStr">
         <is>
           <t>UV と電着の双方を持つ稀少例</t>
         </is>
       </c>
     </row>
     <row r="35" ht="68" customHeight="1">
-      <c r="A35" s="28" t="n">
+      <c r="A35" s="30" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="28" t="inlineStr">
+      <c r="B35" s="30" t="inlineStr">
         <is>
           <t>UV・印刷インキ</t>
         </is>
@@ -4867,117 +4963,118 @@
           <t>DICグラフィックス</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D35" s="14" t="inlineStr"/>
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>東京都中央区</t>
         </is>
       </c>
-      <c r="E35" s="14" t="inlineStr">
+      <c r="F35" s="15" t="inlineStr">
         <is>
           <t>非上場(DIC子会社)</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr">
+      <c r="G35" s="7" t="inlineStr">
         <is>
           <t>約2,000億円規模(推定)</t>
         </is>
       </c>
-      <c r="G35" s="7" t="inlineStr">
+      <c r="H35" s="7" t="inlineStr">
         <is>
           <t>約3,000人</t>
         </is>
       </c>
-      <c r="H35" s="8" t="inlineStr">
+      <c r="I35" s="8" t="inlineStr">
         <is>
           <t>印刷インキ・UV・特殊インキ</t>
         </is>
       </c>
-      <c r="I35" s="16" t="inlineStr">
+      <c r="J35" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J35" s="20" t="inlineStr">
+      <c r="K35" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="K35" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="L35" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M35" s="16" t="inlineStr">
+      <c r="M35" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="N35" s="8" t="inlineStr">
+      <c r="O35" s="8" t="inlineStr">
         <is>
           <t>千葉・滋賀 ほか</t>
         </is>
       </c>
-      <c r="O35" s="17" t="inlineStr">
+      <c r="P35" s="18" t="inlineStr">
         <is>
           <t>https://www.dic-graphics.co.jp/</t>
         </is>
       </c>
-      <c r="P35" s="7" t="inlineStr">
+      <c r="Q35" s="7" t="inlineStr">
         <is>
           <t>DIC IR経由</t>
         </is>
       </c>
-      <c r="Q35" s="14" t="inlineStr">
+      <c r="R35" s="15" t="inlineStr">
         <is>
           <t>中〜高 (DIC連結に含む)</t>
         </is>
       </c>
-      <c r="R35" s="8" t="inlineStr">
+      <c r="S35" s="8" t="inlineStr">
         <is>
           <t>UV/水性インキの②③⑦</t>
         </is>
       </c>
-      <c r="S35" s="8" t="inlineStr">
+      <c r="T35" s="8" t="inlineStr">
         <is>
           <t>印刷インキの大量生産工程</t>
         </is>
       </c>
-      <c r="T35" s="22" t="n">
+      <c r="U35" s="24" t="n">
         <v>72</v>
       </c>
-      <c r="U35" s="8" t="inlineStr">
+      <c r="V35" s="8" t="inlineStr">
         <is>
           <t>親会社(DIC) 経由</t>
         </is>
       </c>
-      <c r="V35" s="8" t="inlineStr">
+      <c r="W35" s="8" t="inlineStr">
         <is>
           <t>印刷業界経由</t>
         </is>
       </c>
-      <c r="W35" s="8" t="inlineStr">
+      <c r="X35" s="8" t="inlineStr">
         <is>
           <t>塗料との境界が曖昧</t>
         </is>
       </c>
-      <c r="X35" s="14" t="inlineStr"/>
-      <c r="Y35" s="7" t="inlineStr"/>
-      <c r="Z35" s="8" t="inlineStr">
+      <c r="Y35" s="15" t="inlineStr"/>
+      <c r="Z35" s="7" t="inlineStr"/>
+      <c r="AA35" s="8" t="inlineStr">
         <is>
           <t>DIC系のインキ生産規模感</t>
         </is>
       </c>
     </row>
     <row r="36" ht="68" customHeight="1">
-      <c r="A36" s="28" t="n">
+      <c r="A36" s="30" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="28" t="inlineStr">
+      <c r="B36" s="30" t="inlineStr">
         <is>
           <t>UV・印刷インキ</t>
         </is>
@@ -4987,117 +5084,122 @@
           <t>トウペ</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D36" s="20" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>大阪市平野区</t>
         </is>
       </c>
-      <c r="E36" s="14" t="inlineStr">
+      <c r="F36" s="15" t="inlineStr">
         <is>
           <t>非上場</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr">
+      <c r="G36" s="7" t="inlineStr">
         <is>
           <t>約120億円規模(推定)</t>
         </is>
       </c>
-      <c r="G36" s="7" t="inlineStr">
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>約400人</t>
         </is>
       </c>
-      <c r="H36" s="8" t="inlineStr">
+      <c r="I36" s="8" t="inlineStr">
         <is>
           <t>工業用塗料・UV 塗料・電子部品向け</t>
         </is>
       </c>
-      <c r="I36" s="16" t="inlineStr">
+      <c r="J36" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J36" s="16" t="inlineStr">
+      <c r="K36" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="K36" s="20" t="inlineStr">
+      <c r="L36" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="L36" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M36" s="16" t="inlineStr">
+      <c r="M36" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="N36" s="8" t="inlineStr">
+      <c r="O36" s="8" t="inlineStr">
         <is>
           <t>大阪・栃木</t>
         </is>
       </c>
-      <c r="O36" s="17" t="inlineStr">
+      <c r="P36" s="18" t="inlineStr">
         <is>
           <t>https://www.toupe.co.jp/</t>
         </is>
       </c>
-      <c r="P36" s="7" t="inlineStr">
+      <c r="Q36" s="7" t="inlineStr">
         <is>
           <t>本社問合せ</t>
         </is>
       </c>
-      <c r="Q36" s="14" t="inlineStr">
+      <c r="R36" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="R36" s="8" t="inlineStr">
+      <c r="S36" s="8" t="inlineStr">
         <is>
           <t>工業用塗料の②③④, UV ⑤⑦</t>
         </is>
       </c>
-      <c r="S36" s="8" t="inlineStr">
+      <c r="T36" s="8" t="inlineStr">
         <is>
           <t>電子向け工業塗料の小ロット運用</t>
         </is>
       </c>
-      <c r="T36" s="22" t="n">
+      <c r="U36" s="24" t="n">
         <v>65</v>
       </c>
-      <c r="U36" s="8" t="inlineStr">
+      <c r="V36" s="8" t="inlineStr">
         <is>
           <t>営業・技術</t>
         </is>
       </c>
-      <c r="V36" s="8" t="inlineStr">
+      <c r="W36" s="8" t="inlineStr">
         <is>
           <t>電子・自動車部品業界経由</t>
         </is>
       </c>
-      <c r="W36" s="8" t="inlineStr">
+      <c r="X36" s="8" t="inlineStr">
         <is>
           <t>ニッチ工業塗料は機密性高</t>
         </is>
       </c>
-      <c r="X36" s="14" t="inlineStr"/>
-      <c r="Y36" s="7" t="inlineStr"/>
-      <c r="Z36" s="8" t="inlineStr">
+      <c r="Y36" s="15" t="inlineStr"/>
+      <c r="Z36" s="7" t="inlineStr"/>
+      <c r="AA36" s="8" t="inlineStr">
         <is>
           <t>工業×UVの中堅事例</t>
         </is>
       </c>
     </row>
     <row r="37" ht="68" customHeight="1">
-      <c r="A37" s="29" t="n">
+      <c r="A37" s="31" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="29" t="inlineStr">
+      <c r="B37" s="31" t="inlineStr">
         <is>
           <t>DIY・小口</t>
         </is>
@@ -5107,117 +5209,118 @@
           <t>アサヒペン</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D37" s="14" t="inlineStr"/>
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>大阪市鶴見区</t>
         </is>
       </c>
-      <c r="E37" s="14" t="inlineStr">
+      <c r="F37" s="15" t="inlineStr">
         <is>
           <t>非上場</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr">
+      <c r="G37" s="7" t="inlineStr">
         <is>
           <t>約280億円規模(推定)</t>
         </is>
       </c>
-      <c r="G37" s="7" t="inlineStr">
+      <c r="H37" s="7" t="inlineStr">
         <is>
           <t>約600人</t>
         </is>
       </c>
-      <c r="H37" s="8" t="inlineStr">
+      <c r="I37" s="8" t="inlineStr">
         <is>
           <t>DIY・小口・ホームセンター</t>
         </is>
       </c>
-      <c r="I37" s="15" t="inlineStr">
+      <c r="J37" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="J37" s="15" t="inlineStr">
+      <c r="K37" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="K37" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="L37" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M37" s="20" t="inlineStr">
+      <c r="M37" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="N37" s="8" t="inlineStr">
+      <c r="O37" s="8" t="inlineStr">
         <is>
           <t>大阪・茨城</t>
         </is>
       </c>
-      <c r="O37" s="17" t="inlineStr">
+      <c r="P37" s="18" t="inlineStr">
         <is>
           <t>https://www.asahipen.jp/</t>
         </is>
       </c>
-      <c r="P37" s="7" t="inlineStr">
+      <c r="Q37" s="7" t="inlineStr">
         <is>
           <t>本社問合せ</t>
         </is>
       </c>
-      <c r="Q37" s="14" t="inlineStr">
+      <c r="R37" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="R37" s="8" t="inlineStr">
+      <c r="S37" s="8" t="inlineStr">
         <is>
           <t>小容量缶(1L/4L)の⑧充填・⑨保管</t>
         </is>
       </c>
-      <c r="S37" s="8" t="inlineStr">
+      <c r="T37" s="8" t="inlineStr">
         <is>
           <t>小容量充填のスループット・歩留</t>
         </is>
       </c>
-      <c r="T37" s="25" t="n">
+      <c r="U37" s="27" t="n">
         <v>60</v>
       </c>
-      <c r="U37" s="8" t="inlineStr">
+      <c r="V37" s="8" t="inlineStr">
         <is>
           <t>営業窓口</t>
         </is>
       </c>
-      <c r="V37" s="8" t="inlineStr">
+      <c r="W37" s="8" t="inlineStr">
         <is>
           <t>ホームセンター経由</t>
         </is>
       </c>
-      <c r="W37" s="8" t="inlineStr">
+      <c r="X37" s="8" t="inlineStr">
         <is>
           <t>プロ向けと差別化必要</t>
         </is>
       </c>
-      <c r="X37" s="14" t="inlineStr"/>
-      <c r="Y37" s="7" t="inlineStr"/>
-      <c r="Z37" s="8" t="inlineStr">
+      <c r="Y37" s="15" t="inlineStr"/>
+      <c r="Z37" s="7" t="inlineStr"/>
+      <c r="AA37" s="8" t="inlineStr">
         <is>
           <t>DIY 流通の代表</t>
         </is>
       </c>
     </row>
     <row r="38" ht="68" customHeight="1">
-      <c r="A38" s="29" t="n">
+      <c r="A38" s="31" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="29" t="inlineStr">
+      <c r="B38" s="31" t="inlineStr">
         <is>
           <t>DIY・小口</t>
         </is>
@@ -5227,46 +5330,42 @@
           <t>カンペハピオ</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D38" s="14" t="inlineStr"/>
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>大阪市東淀川区</t>
         </is>
       </c>
-      <c r="E38" s="14" t="inlineStr">
+      <c r="F38" s="15" t="inlineStr">
         <is>
           <t>非上場(関ペ系列)</t>
         </is>
       </c>
-      <c r="F38" s="7" t="inlineStr">
+      <c r="G38" s="7" t="inlineStr">
         <is>
           <t>数百億円規模</t>
         </is>
       </c>
-      <c r="G38" s="7" t="inlineStr">
+      <c r="H38" s="7" t="inlineStr">
         <is>
           <t>数百人</t>
         </is>
       </c>
-      <c r="H38" s="8" t="inlineStr">
+      <c r="I38" s="8" t="inlineStr">
         <is>
           <t>DIY・ホームセンター・小口</t>
         </is>
       </c>
-      <c r="I38" s="15" t="inlineStr">
+      <c r="J38" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="J38" s="15" t="inlineStr">
+      <c r="K38" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="K38" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="L38" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -5277,67 +5376,72 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N38" s="8" t="inlineStr">
+      <c r="N38" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O38" s="8" t="inlineStr">
         <is>
           <t>大阪・関ペ工場併設</t>
         </is>
       </c>
-      <c r="O38" s="17" t="inlineStr">
+      <c r="P38" s="18" t="inlineStr">
         <is>
           <t>https://www.kanpe.co.jp/</t>
         </is>
       </c>
-      <c r="P38" s="7" t="inlineStr">
+      <c r="Q38" s="7" t="inlineStr">
         <is>
           <t>関ペ広報経由</t>
         </is>
       </c>
-      <c r="Q38" s="14" t="inlineStr">
+      <c r="R38" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="R38" s="8" t="inlineStr">
+      <c r="S38" s="8" t="inlineStr">
         <is>
           <t>DIY 缶の⑤調色・⑧充填</t>
         </is>
       </c>
-      <c r="S38" s="8" t="inlineStr">
+      <c r="T38" s="8" t="inlineStr">
         <is>
           <t>小容量缶のSKU・色種数・回転</t>
         </is>
       </c>
-      <c r="T38" s="25" t="n">
+      <c r="U38" s="27" t="n">
         <v>58</v>
       </c>
-      <c r="U38" s="8" t="inlineStr">
+      <c r="V38" s="8" t="inlineStr">
         <is>
           <t>親会社(関ペ) 経由</t>
         </is>
       </c>
-      <c r="V38" s="8" t="inlineStr">
+      <c r="W38" s="8" t="inlineStr">
         <is>
           <t>ホームセンター業界経由</t>
         </is>
       </c>
-      <c r="W38" s="8" t="inlineStr">
+      <c r="X38" s="8" t="inlineStr">
         <is>
           <t>親会社の方針に従う</t>
         </is>
       </c>
-      <c r="X38" s="14" t="inlineStr"/>
-      <c r="Y38" s="7" t="inlineStr"/>
-      <c r="Z38" s="8" t="inlineStr">
+      <c r="Y38" s="15" t="inlineStr"/>
+      <c r="Z38" s="7" t="inlineStr"/>
+      <c r="AA38" s="8" t="inlineStr">
         <is>
           <t>DIY 流通の補強</t>
         </is>
       </c>
     </row>
     <row r="39" ht="68" customHeight="1">
-      <c r="A39" s="29" t="n">
+      <c r="A39" s="31" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="29" t="inlineStr">
+      <c r="B39" s="31" t="inlineStr">
         <is>
           <t>DIY・小口</t>
         </is>
@@ -5347,46 +5451,42 @@
           <t>ニッペホームプロダクツ</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="D39" s="14" t="inlineStr"/>
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>東京都北区</t>
         </is>
       </c>
-      <c r="E39" s="14" t="inlineStr">
+      <c r="F39" s="15" t="inlineStr">
         <is>
           <t>非上場(日ペ系列)</t>
         </is>
       </c>
-      <c r="F39" s="7" t="inlineStr">
+      <c r="G39" s="7" t="inlineStr">
         <is>
           <t>数百億円規模</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr">
+      <c r="H39" s="7" t="inlineStr">
         <is>
           <t>数百人</t>
         </is>
       </c>
-      <c r="H39" s="8" t="inlineStr">
+      <c r="I39" s="8" t="inlineStr">
         <is>
           <t>DIY・小口・ホームセンター</t>
         </is>
       </c>
-      <c r="I39" s="15" t="inlineStr">
+      <c r="J39" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="J39" s="15" t="inlineStr">
+      <c r="K39" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="K39" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="L39" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -5397,67 +5497,72 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N39" s="8" t="inlineStr">
+      <c r="N39" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O39" s="8" t="inlineStr">
         <is>
           <t>東京・関東</t>
         </is>
       </c>
-      <c r="O39" s="17" t="inlineStr">
+      <c r="P39" s="18" t="inlineStr">
         <is>
           <t>https://www.nippehome.co.jp/</t>
         </is>
       </c>
-      <c r="P39" s="7" t="inlineStr">
+      <c r="Q39" s="7" t="inlineStr">
         <is>
           <t>日ペ広報経由</t>
         </is>
       </c>
-      <c r="Q39" s="14" t="inlineStr">
+      <c r="R39" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="R39" s="8" t="inlineStr">
+      <c r="S39" s="8" t="inlineStr">
         <is>
           <t>DIY 缶の⑤調色・⑧充填</t>
         </is>
       </c>
-      <c r="S39" s="8" t="inlineStr">
+      <c r="T39" s="8" t="inlineStr">
         <is>
           <t>DIY SKU・小容量充填</t>
         </is>
       </c>
-      <c r="T39" s="25" t="n">
+      <c r="U39" s="27" t="n">
         <v>58</v>
       </c>
-      <c r="U39" s="8" t="inlineStr">
+      <c r="V39" s="8" t="inlineStr">
         <is>
           <t>親会社(日ペHD) 経由</t>
         </is>
       </c>
-      <c r="V39" s="8" t="inlineStr">
+      <c r="W39" s="8" t="inlineStr">
         <is>
           <t>ホームセンター業界経由</t>
         </is>
       </c>
-      <c r="W39" s="8" t="inlineStr">
+      <c r="X39" s="8" t="inlineStr">
         <is>
           <t>親会社の方針に従う</t>
         </is>
       </c>
-      <c r="X39" s="14" t="inlineStr"/>
-      <c r="Y39" s="7" t="inlineStr"/>
-      <c r="Z39" s="8" t="inlineStr">
+      <c r="Y39" s="15" t="inlineStr"/>
+      <c r="Z39" s="7" t="inlineStr"/>
+      <c r="AA39" s="8" t="inlineStr">
         <is>
           <t>DIY 流通の補強(日ペ系)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="68" customHeight="1">
-      <c r="A40" s="30" t="n">
+      <c r="A40" s="32" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="30" t="inlineStr">
+      <c r="B40" s="32" t="inlineStr">
         <is>
           <t>日ペグループ</t>
         </is>
@@ -5467,117 +5572,118 @@
           <t>日本ペイント・オートモーティブコーティングス</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D40" s="14" t="inlineStr"/>
+      <c r="E40" s="7" t="inlineStr">
         <is>
           <t>大阪市北区(日ペHD系)</t>
         </is>
       </c>
-      <c r="E40" s="14" t="inlineStr">
+      <c r="F40" s="15" t="inlineStr">
         <is>
           <t>非上場(子会社)</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr">
+      <c r="G40" s="7" t="inlineStr">
         <is>
           <t>日ペHD連結内</t>
         </is>
       </c>
-      <c r="G40" s="7" t="inlineStr">
+      <c r="H40" s="7" t="inlineStr">
         <is>
           <t>数千人(日ペ系列)</t>
         </is>
       </c>
-      <c r="H40" s="8" t="inlineStr">
+      <c r="I40" s="8" t="inlineStr">
         <is>
           <t>自動車OEM 塗料 (世界トップクラス)</t>
         </is>
       </c>
-      <c r="I40" s="16" t="inlineStr">
+      <c r="J40" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J40" s="16" t="inlineStr">
+      <c r="K40" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="K40" s="16" t="inlineStr">
+      <c r="L40" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="L40" s="15" t="inlineStr">
+      <c r="M40" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="M40" s="20" t="inlineStr">
+      <c r="N40" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="N40" s="8" t="inlineStr">
+      <c r="O40" s="8" t="inlineStr">
         <is>
           <t>東京・愛知・大阪</t>
         </is>
       </c>
-      <c r="O40" s="17" t="inlineStr">
+      <c r="P40" s="18" t="inlineStr">
         <is>
           <t>https://www.nipponpaint-automotive.com/</t>
         </is>
       </c>
-      <c r="P40" s="7" t="inlineStr">
+      <c r="Q40" s="7" t="inlineStr">
         <is>
           <t>日ペHD IR経由</t>
         </is>
       </c>
-      <c r="Q40" s="14" t="inlineStr">
+      <c r="R40" s="15" t="inlineStr">
         <is>
           <t>中 (親会社IRに含む)</t>
         </is>
       </c>
-      <c r="R40" s="8" t="inlineStr">
+      <c r="S40" s="8" t="inlineStr">
         <is>
           <t>OEM 向け電着・中塗り・上塗りの①〜⑥</t>
         </is>
       </c>
-      <c r="S40" s="8" t="inlineStr">
+      <c r="T40" s="8" t="inlineStr">
         <is>
           <t>OEM JIT配送、塗着効率、CCM</t>
         </is>
       </c>
-      <c r="T40" s="18" t="n">
+      <c r="U40" s="19" t="n">
         <v>92</v>
       </c>
-      <c r="U40" s="8" t="inlineStr">
+      <c r="V40" s="8" t="inlineStr">
         <is>
           <t>親会社(日ペHD) 経由</t>
         </is>
       </c>
-      <c r="V40" s="8" t="inlineStr">
+      <c r="W40" s="8" t="inlineStr">
         <is>
           <t>自動車OEM経由</t>
         </is>
       </c>
-      <c r="W40" s="8" t="inlineStr">
+      <c r="X40" s="8" t="inlineStr">
         <is>
           <t>親会社の方針に従う</t>
         </is>
       </c>
-      <c r="X40" s="14" t="inlineStr"/>
-      <c r="Y40" s="7" t="inlineStr"/>
-      <c r="Z40" s="8" t="inlineStr">
+      <c r="Y40" s="15" t="inlineStr"/>
+      <c r="Z40" s="7" t="inlineStr"/>
+      <c r="AA40" s="8" t="inlineStr">
         <is>
           <t>自動車OEM の最重要</t>
         </is>
       </c>
     </row>
     <row r="41" ht="68" customHeight="1">
-      <c r="A41" s="30" t="n">
+      <c r="A41" s="32" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="30" t="inlineStr">
+      <c r="B41" s="32" t="inlineStr">
         <is>
           <t>日ペグループ</t>
         </is>
@@ -5587,117 +5693,122 @@
           <t>日本ペイント・インダストリアルコーティングス</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="D41" s="20" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>大阪市北区(日ペHD系)</t>
         </is>
       </c>
-      <c r="E41" s="14" t="inlineStr">
+      <c r="F41" s="15" t="inlineStr">
         <is>
           <t>非上場(子会社)</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr">
+      <c r="G41" s="7" t="inlineStr">
         <is>
           <t>日ペHD連結内</t>
         </is>
       </c>
-      <c r="G41" s="7" t="inlineStr">
+      <c r="H41" s="7" t="inlineStr">
         <is>
           <t>数千人</t>
         </is>
       </c>
-      <c r="H41" s="8" t="inlineStr">
+      <c r="I41" s="8" t="inlineStr">
         <is>
           <t>工業・電着・特殊塗料</t>
         </is>
       </c>
-      <c r="I41" s="16" t="inlineStr">
+      <c r="J41" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J41" s="16" t="inlineStr">
+      <c r="K41" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="K41" s="16" t="inlineStr">
+      <c r="L41" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="L41" s="15" t="inlineStr">
+      <c r="M41" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="M41" s="20" t="inlineStr">
+      <c r="N41" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="N41" s="8" t="inlineStr">
+      <c r="O41" s="8" t="inlineStr">
         <is>
           <t>東京・愛知・大阪</t>
         </is>
       </c>
-      <c r="O41" s="17" t="inlineStr">
+      <c r="P41" s="18" t="inlineStr">
         <is>
           <t>https://www.nipponpaint-industrialcoatings.co.jp/</t>
         </is>
       </c>
-      <c r="P41" s="7" t="inlineStr">
+      <c r="Q41" s="7" t="inlineStr">
         <is>
           <t>日ペHD IR経由</t>
         </is>
       </c>
-      <c r="Q41" s="14" t="inlineStr">
+      <c r="R41" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="R41" s="8" t="inlineStr">
+      <c r="S41" s="8" t="inlineStr">
         <is>
           <t>工業塗料 ①〜⑨, 電着の特殊工程</t>
         </is>
       </c>
-      <c r="S41" s="8" t="inlineStr">
+      <c r="T41" s="8" t="inlineStr">
         <is>
           <t>電着MEQ・UF・塗着効率、工業ライン</t>
         </is>
       </c>
-      <c r="T41" s="18" t="n">
+      <c r="U41" s="19" t="n">
         <v>88</v>
       </c>
-      <c r="U41" s="8" t="inlineStr">
+      <c r="V41" s="8" t="inlineStr">
         <is>
           <t>親会社経由</t>
         </is>
       </c>
-      <c r="V41" s="8" t="inlineStr">
+      <c r="W41" s="8" t="inlineStr">
         <is>
           <t>工業顧客経由</t>
         </is>
       </c>
-      <c r="W41" s="8" t="inlineStr">
+      <c r="X41" s="8" t="inlineStr">
         <is>
           <t>親会社の方針に従う</t>
         </is>
       </c>
-      <c r="X41" s="14" t="inlineStr"/>
-      <c r="Y41" s="7" t="inlineStr"/>
-      <c r="Z41" s="8" t="inlineStr">
+      <c r="Y41" s="15" t="inlineStr"/>
+      <c r="Z41" s="7" t="inlineStr"/>
+      <c r="AA41" s="8" t="inlineStr">
         <is>
           <t>電着・工業の最重要</t>
         </is>
       </c>
     </row>
     <row r="42" ht="68" customHeight="1">
-      <c r="A42" s="30" t="n">
+      <c r="A42" s="32" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="30" t="inlineStr">
+      <c r="B42" s="32" t="inlineStr">
         <is>
           <t>日ペグループ</t>
         </is>
@@ -5707,46 +5818,42 @@
           <t>日本ペイントマリン</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D42" s="14" t="inlineStr"/>
+      <c r="E42" s="7" t="inlineStr">
         <is>
           <t>兵庫県神戸市(日ペHD系)</t>
         </is>
       </c>
-      <c r="E42" s="14" t="inlineStr">
+      <c r="F42" s="15" t="inlineStr">
         <is>
           <t>非上場(子会社)</t>
         </is>
       </c>
-      <c r="F42" s="7" t="inlineStr">
+      <c r="G42" s="7" t="inlineStr">
         <is>
           <t>日ペHD連結内</t>
         </is>
       </c>
-      <c r="G42" s="7" t="inlineStr">
+      <c r="H42" s="7" t="inlineStr">
         <is>
           <t>数千人</t>
         </is>
       </c>
-      <c r="H42" s="8" t="inlineStr">
+      <c r="I42" s="8" t="inlineStr">
         <is>
           <t>船舶用塗料</t>
         </is>
       </c>
-      <c r="I42" s="15" t="inlineStr">
+      <c r="J42" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="J42" s="16" t="inlineStr">
+      <c r="K42" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="K42" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="L42" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -5757,67 +5864,72 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N42" s="8" t="inlineStr">
+      <c r="N42" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O42" s="8" t="inlineStr">
         <is>
           <t>兵庫・愛媛</t>
         </is>
       </c>
-      <c r="O42" s="17" t="inlineStr">
+      <c r="P42" s="18" t="inlineStr">
         <is>
           <t>https://www.nipponpaint-marine.com/</t>
         </is>
       </c>
-      <c r="P42" s="7" t="inlineStr">
+      <c r="Q42" s="7" t="inlineStr">
         <is>
           <t>日ペHD IR経由</t>
         </is>
       </c>
-      <c r="Q42" s="14" t="inlineStr">
+      <c r="R42" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="R42" s="8" t="inlineStr">
+      <c r="S42" s="8" t="inlineStr">
         <is>
           <t>船舶塗料の③④(防汚機能の分散)</t>
         </is>
       </c>
-      <c r="S42" s="8" t="inlineStr">
+      <c r="T42" s="8" t="inlineStr">
         <is>
           <t>防汚剤・低摩擦塗料の組成</t>
         </is>
       </c>
-      <c r="T42" s="21" t="n">
+      <c r="U42" s="23" t="n">
         <v>78</v>
       </c>
-      <c r="U42" s="8" t="inlineStr">
+      <c r="V42" s="8" t="inlineStr">
         <is>
           <t>親会社経由</t>
         </is>
       </c>
-      <c r="V42" s="8" t="inlineStr">
+      <c r="W42" s="8" t="inlineStr">
         <is>
           <t>造船業界経由</t>
         </is>
       </c>
-      <c r="W42" s="8" t="inlineStr">
+      <c r="X42" s="8" t="inlineStr">
         <is>
           <t>中国塗料・関ペマリンと競合</t>
         </is>
       </c>
-      <c r="X42" s="14" t="inlineStr"/>
-      <c r="Y42" s="7" t="inlineStr"/>
-      <c r="Z42" s="8" t="inlineStr">
+      <c r="Y42" s="15" t="inlineStr"/>
+      <c r="Z42" s="7" t="inlineStr"/>
+      <c r="AA42" s="8" t="inlineStr">
         <is>
           <t>船舶塗料の比較対象</t>
         </is>
       </c>
     </row>
     <row r="43" ht="68" customHeight="1">
-      <c r="A43" s="30" t="n">
+      <c r="A43" s="32" t="n">
         <v>39</v>
       </c>
-      <c r="B43" s="30" t="inlineStr">
+      <c r="B43" s="32" t="inlineStr">
         <is>
           <t>日ペグループ</t>
         </is>
@@ -5827,46 +5939,42 @@
           <t>日本ペイント・サーフケミカルズ</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="D43" s="14" t="inlineStr"/>
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>大阪市北区(日ペHD系)</t>
         </is>
       </c>
-      <c r="E43" s="14" t="inlineStr">
+      <c r="F43" s="15" t="inlineStr">
         <is>
           <t>非上場(子会社)</t>
         </is>
       </c>
-      <c r="F43" s="7" t="inlineStr">
+      <c r="G43" s="7" t="inlineStr">
         <is>
           <t>日ペHD連結内</t>
         </is>
       </c>
-      <c r="G43" s="7" t="inlineStr">
+      <c r="H43" s="7" t="inlineStr">
         <is>
           <t>数百人</t>
         </is>
       </c>
-      <c r="H43" s="8" t="inlineStr">
+      <c r="I43" s="8" t="inlineStr">
         <is>
           <t>表面処理薬剤(塗装前処理)</t>
         </is>
       </c>
-      <c r="I43" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J43" s="16" t="inlineStr">
+      <c r="J43" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="K43" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="L43" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -5877,67 +5985,72 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N43" s="8" t="inlineStr">
+      <c r="N43" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O43" s="8" t="inlineStr">
         <is>
           <t>東京・大阪</t>
         </is>
       </c>
-      <c r="O43" s="17" t="inlineStr">
+      <c r="P43" s="18" t="inlineStr">
         <is>
           <t>https://www.nipponpaint-surf.co.jp/</t>
         </is>
       </c>
-      <c r="P43" s="7" t="inlineStr">
+      <c r="Q43" s="7" t="inlineStr">
         <is>
           <t>日ペHD IR経由</t>
         </is>
       </c>
-      <c r="Q43" s="14" t="inlineStr">
+      <c r="R43" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="R43" s="8" t="inlineStr">
+      <c r="S43" s="8" t="inlineStr">
         <is>
           <t>塗装前処理薬剤の③配合・⑤希釈</t>
         </is>
       </c>
-      <c r="S43" s="8" t="inlineStr">
+      <c r="T43" s="8" t="inlineStr">
         <is>
           <t>前処理薬剤の濃度管理、リンス回収</t>
         </is>
       </c>
-      <c r="T43" s="22" t="n">
+      <c r="U43" s="24" t="n">
         <v>68</v>
       </c>
-      <c r="U43" s="8" t="inlineStr">
+      <c r="V43" s="8" t="inlineStr">
         <is>
           <t>親会社経由</t>
         </is>
       </c>
-      <c r="V43" s="8" t="inlineStr">
+      <c r="W43" s="8" t="inlineStr">
         <is>
           <t>OEM・工業顧客経由</t>
         </is>
       </c>
-      <c r="W43" s="8" t="inlineStr">
+      <c r="X43" s="8" t="inlineStr">
         <is>
           <t>塗料本体ではなく前処理特化</t>
         </is>
       </c>
-      <c r="X43" s="14" t="inlineStr"/>
-      <c r="Y43" s="7" t="inlineStr"/>
-      <c r="Z43" s="8" t="inlineStr">
+      <c r="Y43" s="15" t="inlineStr"/>
+      <c r="Z43" s="7" t="inlineStr"/>
+      <c r="AA43" s="8" t="inlineStr">
         <is>
           <t>前処理工程の補強</t>
         </is>
       </c>
     </row>
     <row r="44" ht="68" customHeight="1">
-      <c r="A44" s="30" t="n">
+      <c r="A44" s="32" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="30" t="inlineStr">
+      <c r="B44" s="32" t="inlineStr">
         <is>
           <t>日ペグループ</t>
         </is>
@@ -5947,46 +6060,42 @@
           <t>ニッペ・オートリフィニッシュ</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
+      <c r="D44" s="14" t="inlineStr"/>
+      <c r="E44" s="7" t="inlineStr">
         <is>
           <t>大阪市北区(日ペHD系)</t>
         </is>
       </c>
-      <c r="E44" s="14" t="inlineStr">
+      <c r="F44" s="15" t="inlineStr">
         <is>
           <t>非上場(子会社)</t>
         </is>
       </c>
-      <c r="F44" s="7" t="inlineStr">
+      <c r="G44" s="7" t="inlineStr">
         <is>
           <t>日ペHD連結内</t>
         </is>
       </c>
-      <c r="G44" s="7" t="inlineStr">
+      <c r="H44" s="7" t="inlineStr">
         <is>
           <t>数百人</t>
         </is>
       </c>
-      <c r="H44" s="8" t="inlineStr">
+      <c r="I44" s="8" t="inlineStr">
         <is>
           <t>自動車補修塗料</t>
         </is>
       </c>
-      <c r="I44" s="15" t="inlineStr">
+      <c r="J44" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="J44" s="16" t="inlineStr">
+      <c r="K44" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="K44" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="L44" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -5997,67 +6106,72 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N44" s="8" t="inlineStr">
+      <c r="N44" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O44" s="8" t="inlineStr">
         <is>
           <t>東京・大阪</t>
         </is>
       </c>
-      <c r="O44" s="17" t="inlineStr">
+      <c r="P44" s="18" t="inlineStr">
         <is>
           <t>https://www.nipponpaint-autorefinish.com/</t>
         </is>
       </c>
-      <c r="P44" s="7" t="inlineStr">
+      <c r="Q44" s="7" t="inlineStr">
         <is>
           <t>日ペHD IR経由</t>
         </is>
       </c>
-      <c r="Q44" s="14" t="inlineStr">
+      <c r="R44" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="R44" s="8" t="inlineStr">
+      <c r="S44" s="8" t="inlineStr">
         <is>
           <t>補修塗料の④⑤調色・⑧充填</t>
         </is>
       </c>
-      <c r="S44" s="8" t="inlineStr">
+      <c r="T44" s="8" t="inlineStr">
         <is>
           <t>小ロット補修の歩留、CCM</t>
         </is>
       </c>
-      <c r="T44" s="21" t="n">
+      <c r="U44" s="23" t="n">
         <v>75</v>
       </c>
-      <c r="U44" s="8" t="inlineStr">
+      <c r="V44" s="8" t="inlineStr">
         <is>
           <t>親会社経由</t>
         </is>
       </c>
-      <c r="V44" s="8" t="inlineStr">
+      <c r="W44" s="8" t="inlineStr">
         <is>
           <t>板金塗装業界経由</t>
         </is>
       </c>
-      <c r="W44" s="8" t="inlineStr">
+      <c r="X44" s="8" t="inlineStr">
         <is>
           <t>ロックペイント・イサムと競合</t>
         </is>
       </c>
-      <c r="X44" s="14" t="inlineStr"/>
-      <c r="Y44" s="7" t="inlineStr"/>
-      <c r="Z44" s="8" t="inlineStr">
+      <c r="Y44" s="15" t="inlineStr"/>
+      <c r="Z44" s="7" t="inlineStr"/>
+      <c r="AA44" s="8" t="inlineStr">
         <is>
           <t>自動車補修の比較対象</t>
         </is>
       </c>
     </row>
     <row r="45" ht="68" customHeight="1">
-      <c r="A45" s="31" t="n">
+      <c r="A45" s="33" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="31" t="inlineStr">
+      <c r="B45" s="33" t="inlineStr">
         <is>
           <t>関ペグループ</t>
         </is>
@@ -6067,46 +6181,42 @@
           <t>関西ペイントマリン</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="D45" s="14" t="inlineStr"/>
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>大阪市中央区(関ペ系)</t>
         </is>
       </c>
-      <c r="E45" s="14" t="inlineStr">
+      <c r="F45" s="15" t="inlineStr">
         <is>
           <t>非上場(関ペ系)</t>
         </is>
       </c>
-      <c r="F45" s="7" t="inlineStr">
+      <c r="G45" s="7" t="inlineStr">
         <is>
           <t>関ペ連結内</t>
         </is>
       </c>
-      <c r="G45" s="7" t="inlineStr">
+      <c r="H45" s="7" t="inlineStr">
         <is>
           <t>数百人</t>
         </is>
       </c>
-      <c r="H45" s="8" t="inlineStr">
+      <c r="I45" s="8" t="inlineStr">
         <is>
           <t>船舶用塗料</t>
         </is>
       </c>
-      <c r="I45" s="15" t="inlineStr">
+      <c r="J45" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="J45" s="16" t="inlineStr">
+      <c r="K45" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="K45" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="L45" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -6117,67 +6227,72 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N45" s="8" t="inlineStr">
+      <c r="N45" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O45" s="8" t="inlineStr">
         <is>
           <t>大阪・神奈川</t>
         </is>
       </c>
-      <c r="O45" s="17" t="inlineStr">
+      <c r="P45" s="18" t="inlineStr">
         <is>
           <t>https://www.kansaipaint-marine.com/</t>
         </is>
       </c>
-      <c r="P45" s="7" t="inlineStr">
+      <c r="Q45" s="7" t="inlineStr">
         <is>
           <t>関ペ広報経由</t>
         </is>
       </c>
-      <c r="Q45" s="14" t="inlineStr">
+      <c r="R45" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="R45" s="8" t="inlineStr">
+      <c r="S45" s="8" t="inlineStr">
         <is>
           <t>船舶塗料の③④(防汚機能の分散)</t>
         </is>
       </c>
-      <c r="S45" s="8" t="inlineStr">
+      <c r="T45" s="8" t="inlineStr">
         <is>
           <t>防汚剤管理、厚膜塗装</t>
         </is>
       </c>
-      <c r="T45" s="21" t="n">
+      <c r="U45" s="23" t="n">
         <v>76</v>
       </c>
-      <c r="U45" s="8" t="inlineStr">
+      <c r="V45" s="8" t="inlineStr">
         <is>
           <t>親会社経由</t>
         </is>
       </c>
-      <c r="V45" s="8" t="inlineStr">
+      <c r="W45" s="8" t="inlineStr">
         <is>
           <t>造船業界経由</t>
         </is>
       </c>
-      <c r="W45" s="8" t="inlineStr">
+      <c r="X45" s="8" t="inlineStr">
         <is>
           <t>中国塗料・日ペマリンと競合</t>
         </is>
       </c>
-      <c r="X45" s="14" t="inlineStr"/>
-      <c r="Y45" s="7" t="inlineStr"/>
-      <c r="Z45" s="8" t="inlineStr">
+      <c r="Y45" s="15" t="inlineStr"/>
+      <c r="Z45" s="7" t="inlineStr"/>
+      <c r="AA45" s="8" t="inlineStr">
         <is>
           <t>船舶塗料の比較対象</t>
         </is>
       </c>
     </row>
     <row r="46" ht="68" customHeight="1">
-      <c r="A46" s="32" t="n">
+      <c r="A46" s="34" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="32" t="inlineStr">
+      <c r="B46" s="34" t="inlineStr">
         <is>
           <t>外資系・日本法人</t>
         </is>
@@ -6187,117 +6302,118 @@
           <t>PPGコーティングスジャパン</t>
         </is>
       </c>
-      <c r="D46" s="7" t="inlineStr">
+      <c r="D46" s="14" t="inlineStr"/>
+      <c r="E46" s="7" t="inlineStr">
         <is>
           <t>大阪市住之江区</t>
         </is>
       </c>
-      <c r="E46" s="14" t="inlineStr">
+      <c r="F46" s="15" t="inlineStr">
         <is>
           <t>非上場(米PPG子会社)</t>
         </is>
       </c>
-      <c r="F46" s="7" t="inlineStr">
+      <c r="G46" s="7" t="inlineStr">
         <is>
           <t>PPG 連結内</t>
         </is>
       </c>
-      <c r="G46" s="7" t="inlineStr">
+      <c r="H46" s="7" t="inlineStr">
         <is>
           <t>数千人(日本)</t>
         </is>
       </c>
-      <c r="H46" s="8" t="inlineStr">
+      <c r="I46" s="8" t="inlineStr">
         <is>
           <t>自動車補修・工業・航空・船舶</t>
         </is>
       </c>
-      <c r="I46" s="15" t="inlineStr">
+      <c r="J46" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="J46" s="15" t="inlineStr">
+      <c r="K46" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="K46" s="16" t="inlineStr">
+      <c r="L46" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="L46" s="15" t="inlineStr">
+      <c r="M46" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="M46" s="16" t="inlineStr">
+      <c r="N46" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="N46" s="8" t="inlineStr">
+      <c r="O46" s="8" t="inlineStr">
         <is>
           <t>大阪・愛知 ほか</t>
         </is>
       </c>
-      <c r="O46" s="17" t="inlineStr">
+      <c r="P46" s="18" t="inlineStr">
         <is>
           <t>https://www.ppgpaint.jp/</t>
         </is>
       </c>
-      <c r="P46" s="7" t="inlineStr">
+      <c r="Q46" s="7" t="inlineStr">
         <is>
           <t>本社問合せ</t>
         </is>
       </c>
-      <c r="Q46" s="14" t="inlineStr">
+      <c r="R46" s="15" t="inlineStr">
         <is>
           <t>中 (米親会社IRに開示あり)</t>
         </is>
       </c>
-      <c r="R46" s="8" t="inlineStr">
+      <c r="S46" s="8" t="inlineStr">
         <is>
           <t>OEM・補修・工業塗料の①〜⑦</t>
         </is>
       </c>
-      <c r="S46" s="8" t="inlineStr">
+      <c r="T46" s="8" t="inlineStr">
         <is>
           <t>グローバル標準と日本現場のギャップ</t>
         </is>
       </c>
-      <c r="T46" s="21" t="n">
+      <c r="U46" s="23" t="n">
         <v>82</v>
       </c>
-      <c r="U46" s="8" t="inlineStr">
+      <c r="V46" s="8" t="inlineStr">
         <is>
           <t>技術部門 / 営業</t>
         </is>
       </c>
-      <c r="V46" s="8" t="inlineStr">
+      <c r="W46" s="8" t="inlineStr">
         <is>
           <t>OEM・補修・工業経由</t>
         </is>
       </c>
-      <c r="W46" s="8" t="inlineStr">
+      <c r="X46" s="8" t="inlineStr">
         <is>
           <t>親会社の方針に従う・グローバル機密</t>
         </is>
       </c>
-      <c r="X46" s="14" t="inlineStr"/>
-      <c r="Y46" s="7" t="inlineStr"/>
-      <c r="Z46" s="8" t="inlineStr">
+      <c r="Y46" s="15" t="inlineStr"/>
+      <c r="Z46" s="7" t="inlineStr"/>
+      <c r="AA46" s="8" t="inlineStr">
         <is>
           <t>外資系の代表</t>
         </is>
       </c>
     </row>
     <row r="47" ht="68" customHeight="1">
-      <c r="A47" s="32" t="n">
+      <c r="A47" s="34" t="n">
         <v>43</v>
       </c>
-      <c r="B47" s="32" t="inlineStr">
+      <c r="B47" s="34" t="inlineStr">
         <is>
           <t>外資系・日本法人</t>
         </is>
@@ -6307,117 +6423,118 @@
           <t>アクゾノーベル・ジャパン</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
+      <c r="D47" s="14" t="inlineStr"/>
+      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>東京都港区</t>
         </is>
       </c>
-      <c r="E47" s="14" t="inlineStr">
+      <c r="F47" s="15" t="inlineStr">
         <is>
           <t>非上場(蘭AkzoNobel子会社)</t>
         </is>
       </c>
-      <c r="F47" s="7" t="inlineStr">
+      <c r="G47" s="7" t="inlineStr">
         <is>
           <t>AkzoNobel連結内</t>
         </is>
       </c>
-      <c r="G47" s="7" t="inlineStr">
+      <c r="H47" s="7" t="inlineStr">
         <is>
           <t>数百人(日本)</t>
         </is>
       </c>
-      <c r="H47" s="8" t="inlineStr">
+      <c r="I47" s="8" t="inlineStr">
         <is>
           <t>建築・船舶・工業・粉体</t>
         </is>
       </c>
-      <c r="I47" s="15" t="inlineStr">
+      <c r="J47" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="J47" s="15" t="inlineStr">
+      <c r="K47" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="K47" s="15" t="inlineStr">
+      <c r="L47" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="L47" s="16" t="inlineStr">
+      <c r="M47" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="M47" s="16" t="inlineStr">
+      <c r="N47" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="N47" s="8" t="inlineStr">
+      <c r="O47" s="8" t="inlineStr">
         <is>
           <t>東京・大阪 ほか</t>
         </is>
       </c>
-      <c r="O47" s="17" t="inlineStr">
+      <c r="P47" s="18" t="inlineStr">
         <is>
           <t>https://www.akzonobel.com/ja/</t>
         </is>
       </c>
-      <c r="P47" s="7" t="inlineStr">
+      <c r="Q47" s="7" t="inlineStr">
         <is>
           <t>本社問合せ</t>
         </is>
       </c>
-      <c r="Q47" s="14" t="inlineStr">
+      <c r="R47" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="R47" s="8" t="inlineStr">
+      <c r="S47" s="8" t="inlineStr">
         <is>
           <t>粉体・水性建築塗料の②〜⑦</t>
         </is>
       </c>
-      <c r="S47" s="8" t="inlineStr">
+      <c r="T47" s="8" t="inlineStr">
         <is>
           <t>粉体グローバル標準の歩留・能力</t>
         </is>
       </c>
-      <c r="T47" s="21" t="n">
+      <c r="U47" s="23" t="n">
         <v>78</v>
       </c>
-      <c r="U47" s="8" t="inlineStr">
+      <c r="V47" s="8" t="inlineStr">
         <is>
           <t>技術部門 / 営業</t>
         </is>
       </c>
-      <c r="V47" s="8" t="inlineStr">
+      <c r="W47" s="8" t="inlineStr">
         <is>
           <t>業界団体・OEM経由</t>
         </is>
       </c>
-      <c r="W47" s="8" t="inlineStr">
+      <c r="X47" s="8" t="inlineStr">
         <is>
           <t>親会社方針・グローバル機密</t>
         </is>
       </c>
-      <c r="X47" s="14" t="inlineStr"/>
-      <c r="Y47" s="7" t="inlineStr"/>
-      <c r="Z47" s="8" t="inlineStr">
+      <c r="Y47" s="15" t="inlineStr"/>
+      <c r="Z47" s="7" t="inlineStr"/>
+      <c r="AA47" s="8" t="inlineStr">
         <is>
           <t>粉体の世界トップの日本拠点</t>
         </is>
       </c>
     </row>
     <row r="48" ht="68" customHeight="1">
-      <c r="A48" s="32" t="n">
+      <c r="A48" s="34" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="32" t="inlineStr">
+      <c r="B48" s="34" t="inlineStr">
         <is>
           <t>外資系・日本法人</t>
         </is>
@@ -6427,117 +6544,118 @@
           <t>シャーウィン・ウィリアムズ・ジャパン</t>
         </is>
       </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="D48" s="14" t="inlineStr"/>
+      <c r="E48" s="7" t="inlineStr">
         <is>
           <t>東京都</t>
         </is>
       </c>
-      <c r="E48" s="14" t="inlineStr">
+      <c r="F48" s="15" t="inlineStr">
         <is>
           <t>非上場(米SW子会社)</t>
         </is>
       </c>
-      <c r="F48" s="7" t="inlineStr">
+      <c r="G48" s="7" t="inlineStr">
         <is>
           <t>SW連結内</t>
         </is>
       </c>
-      <c r="G48" s="7" t="inlineStr">
+      <c r="H48" s="7" t="inlineStr">
         <is>
           <t>数百人(日本)</t>
         </is>
       </c>
-      <c r="H48" s="8" t="inlineStr">
+      <c r="I48" s="8" t="inlineStr">
         <is>
           <t>建築・工業・自動車補修</t>
         </is>
       </c>
-      <c r="I48" s="16" t="inlineStr">
+      <c r="J48" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="J48" s="15" t="inlineStr">
+      <c r="K48" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="K48" s="16" t="inlineStr">
+      <c r="L48" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="L48" s="16" t="inlineStr">
+      <c r="M48" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="M48" s="20" t="inlineStr">
+      <c r="N48" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="N48" s="8" t="inlineStr">
+      <c r="O48" s="8" t="inlineStr">
         <is>
           <t>(要確認)</t>
         </is>
       </c>
-      <c r="O48" s="17" t="inlineStr">
+      <c r="P48" s="18" t="inlineStr">
         <is>
           <t>https://www.sherwin-williams.com/</t>
         </is>
       </c>
-      <c r="P48" s="7" t="inlineStr">
+      <c r="Q48" s="7" t="inlineStr">
         <is>
           <t>本社問合せ</t>
         </is>
       </c>
-      <c r="Q48" s="24" t="inlineStr">
+      <c r="R48" s="26" t="inlineStr">
         <is>
           <t>低〜中 (要確認)</t>
         </is>
       </c>
-      <c r="R48" s="8" t="inlineStr">
+      <c r="S48" s="8" t="inlineStr">
         <is>
           <t>建築塗料 (米国基準) と日本基準の比較</t>
         </is>
       </c>
-      <c r="S48" s="8" t="inlineStr">
+      <c r="T48" s="8" t="inlineStr">
         <is>
           <t>米国基準塗料の日本現場運用</t>
         </is>
       </c>
-      <c r="T48" s="22" t="n">
+      <c r="U48" s="24" t="n">
         <v>70</v>
       </c>
-      <c r="U48" s="8" t="inlineStr">
+      <c r="V48" s="8" t="inlineStr">
         <is>
           <t>本社経由</t>
         </is>
       </c>
-      <c r="V48" s="8" t="inlineStr">
+      <c r="W48" s="8" t="inlineStr">
         <is>
           <t>(限定的)</t>
         </is>
       </c>
-      <c r="W48" s="8" t="inlineStr">
+      <c r="X48" s="8" t="inlineStr">
         <is>
           <t>事業規模は要確認</t>
         </is>
       </c>
-      <c r="X48" s="14" t="inlineStr"/>
-      <c r="Y48" s="7" t="inlineStr"/>
-      <c r="Z48" s="8" t="inlineStr">
+      <c r="Y48" s="15" t="inlineStr"/>
+      <c r="Z48" s="7" t="inlineStr"/>
+      <c r="AA48" s="8" t="inlineStr">
         <is>
           <t>外資建築塗料の参考</t>
         </is>
       </c>
     </row>
     <row r="49" ht="68" customHeight="1">
-      <c r="A49" s="32" t="n">
+      <c r="A49" s="34" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="32" t="inlineStr">
+      <c r="B49" s="34" t="inlineStr">
         <is>
           <t>外資系・日本法人</t>
         </is>
@@ -6547,117 +6665,118 @@
           <t>アクサルタコーティングシステムズ・ジャパン</t>
         </is>
       </c>
-      <c r="D49" s="7" t="inlineStr">
+      <c r="D49" s="14" t="inlineStr"/>
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>横浜市</t>
         </is>
       </c>
-      <c r="E49" s="14" t="inlineStr">
+      <c r="F49" s="15" t="inlineStr">
         <is>
           <t>非上場(米Axalta子会社)</t>
         </is>
       </c>
-      <c r="F49" s="7" t="inlineStr">
+      <c r="G49" s="7" t="inlineStr">
         <is>
           <t>Axalta連結内</t>
         </is>
       </c>
-      <c r="G49" s="7" t="inlineStr">
+      <c r="H49" s="7" t="inlineStr">
         <is>
           <t>数百人(日本)</t>
         </is>
       </c>
-      <c r="H49" s="8" t="inlineStr">
+      <c r="I49" s="8" t="inlineStr">
         <is>
           <t>自動車OEM・補修・工業</t>
         </is>
       </c>
-      <c r="I49" s="15" t="inlineStr">
+      <c r="J49" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="J49" s="16" t="inlineStr">
+      <c r="K49" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="K49" s="16" t="inlineStr">
+      <c r="L49" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="L49" s="15" t="inlineStr">
+      <c r="M49" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="M49" s="20" t="inlineStr">
+      <c r="N49" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="N49" s="8" t="inlineStr">
+      <c r="O49" s="8" t="inlineStr">
         <is>
           <t>横浜・大阪</t>
         </is>
       </c>
-      <c r="O49" s="17" t="inlineStr">
+      <c r="P49" s="18" t="inlineStr">
         <is>
           <t>https://www.axalta.com/jp/</t>
         </is>
       </c>
-      <c r="P49" s="7" t="inlineStr">
+      <c r="Q49" s="7" t="inlineStr">
         <is>
           <t>本社問合せ</t>
         </is>
       </c>
-      <c r="Q49" s="14" t="inlineStr">
+      <c r="R49" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="R49" s="8" t="inlineStr">
+      <c r="S49" s="8" t="inlineStr">
         <is>
           <t>OEM・補修・電着の①〜⑥</t>
         </is>
       </c>
-      <c r="S49" s="8" t="inlineStr">
+      <c r="T49" s="8" t="inlineStr">
         <is>
           <t>電着のグローバル標準、OEM JIT</t>
         </is>
       </c>
-      <c r="T49" s="21" t="n">
+      <c r="U49" s="23" t="n">
         <v>78</v>
       </c>
-      <c r="U49" s="8" t="inlineStr">
+      <c r="V49" s="8" t="inlineStr">
         <is>
           <t>技術部門 / 営業</t>
         </is>
       </c>
-      <c r="V49" s="8" t="inlineStr">
+      <c r="W49" s="8" t="inlineStr">
         <is>
           <t>OEM・補修経由</t>
         </is>
       </c>
-      <c r="W49" s="8" t="inlineStr">
+      <c r="X49" s="8" t="inlineStr">
         <is>
           <t>親会社方針・グローバル機密</t>
         </is>
       </c>
-      <c r="X49" s="14" t="inlineStr"/>
-      <c r="Y49" s="7" t="inlineStr"/>
-      <c r="Z49" s="8" t="inlineStr">
+      <c r="Y49" s="15" t="inlineStr"/>
+      <c r="Z49" s="7" t="inlineStr"/>
+      <c r="AA49" s="8" t="inlineStr">
         <is>
           <t>電着・OEM の外資比較対象</t>
         </is>
       </c>
     </row>
     <row r="50" ht="68" customHeight="1">
-      <c r="A50" s="32" t="n">
+      <c r="A50" s="34" t="n">
         <v>46</v>
       </c>
-      <c r="B50" s="32" t="inlineStr">
+      <c r="B50" s="34" t="inlineStr">
         <is>
           <t>外資系・日本法人</t>
         </is>
@@ -6667,117 +6786,118 @@
           <t>BASFジャパン コーティングス事業</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="D50" s="14" t="inlineStr"/>
+      <c r="E50" s="7" t="inlineStr">
         <is>
           <t>東京都中央区</t>
         </is>
       </c>
-      <c r="E50" s="14" t="inlineStr">
+      <c r="F50" s="15" t="inlineStr">
         <is>
           <t>非上場(独BASF子会社)</t>
         </is>
       </c>
-      <c r="F50" s="7" t="inlineStr">
+      <c r="G50" s="7" t="inlineStr">
         <is>
           <t>BASF Coatings連結内</t>
         </is>
       </c>
-      <c r="G50" s="7" t="inlineStr">
+      <c r="H50" s="7" t="inlineStr">
         <is>
           <t>数百人(日本)</t>
         </is>
       </c>
-      <c r="H50" s="8" t="inlineStr">
+      <c r="I50" s="8" t="inlineStr">
         <is>
           <t>自動車OEM・補修・特殊</t>
         </is>
       </c>
-      <c r="I50" s="15" t="inlineStr">
+      <c r="J50" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="J50" s="16" t="inlineStr">
+      <c r="K50" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="K50" s="20" t="inlineStr">
+      <c r="L50" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="L50" s="16" t="inlineStr">
+      <c r="M50" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="M50" s="20" t="inlineStr">
+      <c r="N50" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="N50" s="8" t="inlineStr">
+      <c r="O50" s="8" t="inlineStr">
         <is>
           <t>(要確認・事業再編動向あり)</t>
         </is>
       </c>
-      <c r="O50" s="17" t="inlineStr">
+      <c r="P50" s="18" t="inlineStr">
         <is>
           <t>https://www.basf-coatings.com/</t>
         </is>
       </c>
-      <c r="P50" s="7" t="inlineStr">
+      <c r="Q50" s="7" t="inlineStr">
         <is>
           <t>本社問合せ</t>
         </is>
       </c>
-      <c r="Q50" s="24" t="inlineStr">
+      <c r="R50" s="26" t="inlineStr">
         <is>
           <t>低〜中 (事業再編動向で要確認)</t>
         </is>
       </c>
-      <c r="R50" s="8" t="inlineStr">
+      <c r="S50" s="8" t="inlineStr">
         <is>
           <t>OEM 塗料の①〜⑥</t>
         </is>
       </c>
-      <c r="S50" s="8" t="inlineStr">
+      <c r="T50" s="8" t="inlineStr">
         <is>
           <t>OEM 塗料の高機能化動向</t>
         </is>
       </c>
-      <c r="T50" s="22" t="n">
+      <c r="U50" s="24" t="n">
         <v>72</v>
       </c>
-      <c r="U50" s="8" t="inlineStr">
+      <c r="V50" s="8" t="inlineStr">
         <is>
           <t>本社経由</t>
         </is>
       </c>
-      <c r="V50" s="8" t="inlineStr">
+      <c r="W50" s="8" t="inlineStr">
         <is>
           <t>自動車OEM経由</t>
         </is>
       </c>
-      <c r="W50" s="8" t="inlineStr">
+      <c r="X50" s="8" t="inlineStr">
         <is>
           <t>コーティング事業の売却動向 (2024〜) に注意</t>
         </is>
       </c>
-      <c r="X50" s="14" t="inlineStr"/>
-      <c r="Y50" s="7" t="inlineStr"/>
-      <c r="Z50" s="8" t="inlineStr">
+      <c r="Y50" s="15" t="inlineStr"/>
+      <c r="Z50" s="7" t="inlineStr"/>
+      <c r="AA50" s="8" t="inlineStr">
         <is>
           <t>事業再編動向の継続確認が必要</t>
         </is>
       </c>
     </row>
     <row r="51" ht="68" customHeight="1">
-      <c r="A51" s="32" t="n">
+      <c r="A51" s="34" t="n">
         <v>47</v>
       </c>
-      <c r="B51" s="32" t="inlineStr">
+      <c r="B51" s="34" t="inlineStr">
         <is>
           <t>外資系・日本法人</t>
         </is>
@@ -6787,46 +6907,42 @@
           <t>ヘンペル・ジャパン</t>
         </is>
       </c>
-      <c r="D51" s="7" t="inlineStr">
+      <c r="D51" s="14" t="inlineStr"/>
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>横浜市</t>
         </is>
       </c>
-      <c r="E51" s="14" t="inlineStr">
+      <c r="F51" s="15" t="inlineStr">
         <is>
           <t>非上場(デンマークHempel子会社)</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr">
+      <c r="G51" s="7" t="inlineStr">
         <is>
           <t>Hempel連結内</t>
         </is>
       </c>
-      <c r="G51" s="7" t="inlineStr">
+      <c r="H51" s="7" t="inlineStr">
         <is>
           <t>数十人(日本)</t>
         </is>
       </c>
-      <c r="H51" s="8" t="inlineStr">
+      <c r="I51" s="8" t="inlineStr">
         <is>
           <t>船舶・防食・コンテナ用塗料</t>
         </is>
       </c>
-      <c r="I51" s="15" t="inlineStr">
+      <c r="J51" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="J51" s="16" t="inlineStr">
+      <c r="K51" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="K51" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="L51" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -6837,67 +6953,72 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N51" s="8" t="inlineStr">
+      <c r="N51" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O51" s="8" t="inlineStr">
         <is>
           <t>横浜</t>
         </is>
       </c>
-      <c r="O51" s="17" t="inlineStr">
+      <c r="P51" s="18" t="inlineStr">
         <is>
           <t>https://www.hempel.com/ja-jp/</t>
         </is>
       </c>
-      <c r="P51" s="7" t="inlineStr">
+      <c r="Q51" s="7" t="inlineStr">
         <is>
           <t>本社問合せ</t>
         </is>
       </c>
-      <c r="Q51" s="14" t="inlineStr">
+      <c r="R51" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="R51" s="8" t="inlineStr">
+      <c r="S51" s="8" t="inlineStr">
         <is>
           <t>船舶塗料の③④</t>
         </is>
       </c>
-      <c r="S51" s="8" t="inlineStr">
+      <c r="T51" s="8" t="inlineStr">
         <is>
           <t>船舶塗料グローバル標準</t>
         </is>
       </c>
-      <c r="T51" s="22" t="n">
+      <c r="U51" s="24" t="n">
         <v>65</v>
       </c>
-      <c r="U51" s="8" t="inlineStr">
+      <c r="V51" s="8" t="inlineStr">
         <is>
           <t>本社経由</t>
         </is>
       </c>
-      <c r="V51" s="8" t="inlineStr">
+      <c r="W51" s="8" t="inlineStr">
         <is>
           <t>造船・港湾経由</t>
         </is>
       </c>
-      <c r="W51" s="8" t="inlineStr">
+      <c r="X51" s="8" t="inlineStr">
         <is>
           <t>本社方針優先</t>
         </is>
       </c>
-      <c r="X51" s="14" t="inlineStr"/>
-      <c r="Y51" s="7" t="inlineStr"/>
-      <c r="Z51" s="8" t="inlineStr">
+      <c r="Y51" s="15" t="inlineStr"/>
+      <c r="Z51" s="7" t="inlineStr"/>
+      <c r="AA51" s="8" t="inlineStr">
         <is>
           <t>船舶塗料の欧州比較</t>
         </is>
       </c>
     </row>
     <row r="52" ht="68" customHeight="1">
-      <c r="A52" s="32" t="n">
+      <c r="A52" s="34" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="32" t="inlineStr">
+      <c r="B52" s="34" t="inlineStr">
         <is>
           <t>外資系・日本法人</t>
         </is>
@@ -6907,46 +7028,42 @@
           <t>ヨトゥン・ジャパン</t>
         </is>
       </c>
-      <c r="D52" s="7" t="inlineStr">
+      <c r="D52" s="14" t="inlineStr"/>
+      <c r="E52" s="7" t="inlineStr">
         <is>
           <t>横浜市</t>
         </is>
       </c>
-      <c r="E52" s="14" t="inlineStr">
+      <c r="F52" s="15" t="inlineStr">
         <is>
           <t>非上場(ノルウェーJotun子会社)</t>
         </is>
       </c>
-      <c r="F52" s="7" t="inlineStr">
+      <c r="G52" s="7" t="inlineStr">
         <is>
           <t>Jotun連結内</t>
         </is>
       </c>
-      <c r="G52" s="7" t="inlineStr">
+      <c r="H52" s="7" t="inlineStr">
         <is>
           <t>数十人(日本)</t>
         </is>
       </c>
-      <c r="H52" s="8" t="inlineStr">
+      <c r="I52" s="8" t="inlineStr">
         <is>
           <t>船舶・防食・建築用塗料</t>
         </is>
       </c>
-      <c r="I52" s="15" t="inlineStr">
+      <c r="J52" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="J52" s="16" t="inlineStr">
+      <c r="K52" s="17" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="K52" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="L52" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -6957,67 +7074,72 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N52" s="8" t="inlineStr">
+      <c r="N52" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O52" s="8" t="inlineStr">
         <is>
           <t>横浜</t>
         </is>
       </c>
-      <c r="O52" s="17" t="inlineStr">
+      <c r="P52" s="18" t="inlineStr">
         <is>
           <t>https://www.jotun.com/jp/</t>
         </is>
       </c>
-      <c r="P52" s="7" t="inlineStr">
+      <c r="Q52" s="7" t="inlineStr">
         <is>
           <t>本社問合せ</t>
         </is>
       </c>
-      <c r="Q52" s="14" t="inlineStr">
+      <c r="R52" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="R52" s="8" t="inlineStr">
+      <c r="S52" s="8" t="inlineStr">
         <is>
           <t>船舶塗料の③④, 建築水性②⑤</t>
         </is>
       </c>
-      <c r="S52" s="8" t="inlineStr">
+      <c r="T52" s="8" t="inlineStr">
         <is>
           <t>船舶・建築双方のグローバル標準</t>
         </is>
       </c>
-      <c r="T52" s="22" t="n">
+      <c r="U52" s="24" t="n">
         <v>65</v>
       </c>
-      <c r="U52" s="8" t="inlineStr">
+      <c r="V52" s="8" t="inlineStr">
         <is>
           <t>本社経由</t>
         </is>
       </c>
-      <c r="V52" s="8" t="inlineStr">
+      <c r="W52" s="8" t="inlineStr">
         <is>
           <t>造船・建築業界経由</t>
         </is>
       </c>
-      <c r="W52" s="8" t="inlineStr">
+      <c r="X52" s="8" t="inlineStr">
         <is>
           <t>本社方針優先</t>
         </is>
       </c>
-      <c r="X52" s="14" t="inlineStr"/>
-      <c r="Y52" s="7" t="inlineStr"/>
-      <c r="Z52" s="8" t="inlineStr">
+      <c r="Y52" s="15" t="inlineStr"/>
+      <c r="Z52" s="7" t="inlineStr"/>
+      <c r="AA52" s="8" t="inlineStr">
         <is>
           <t>船舶・建築の欧州比較</t>
         </is>
       </c>
     </row>
     <row r="53" ht="68" customHeight="1">
-      <c r="A53" s="32" t="n">
+      <c r="A53" s="34" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="32" t="inlineStr">
+      <c r="B53" s="34" t="inlineStr">
         <is>
           <t>外資系・日本法人</t>
         </is>
@@ -7027,46 +7149,42 @@
           <t>ベンジャミンムーア・ジャパン</t>
         </is>
       </c>
-      <c r="D53" s="7" t="inlineStr">
+      <c r="D53" s="14" t="inlineStr"/>
+      <c r="E53" s="7" t="inlineStr">
         <is>
           <t>東京都</t>
         </is>
       </c>
-      <c r="E53" s="14" t="inlineStr">
+      <c r="F53" s="15" t="inlineStr">
         <is>
           <t>非上場(米BM子会社)</t>
         </is>
       </c>
-      <c r="F53" s="7" t="inlineStr">
+      <c r="G53" s="7" t="inlineStr">
         <is>
           <t>BM連結内</t>
         </is>
       </c>
-      <c r="G53" s="7" t="inlineStr">
+      <c r="H53" s="7" t="inlineStr">
         <is>
           <t>数十人(日本)</t>
         </is>
       </c>
-      <c r="H53" s="8" t="inlineStr">
+      <c r="I53" s="8" t="inlineStr">
         <is>
           <t>建築用高級水性塗料</t>
         </is>
       </c>
-      <c r="I53" s="20" t="inlineStr">
+      <c r="J53" s="22" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="J53" s="15" t="inlineStr">
+      <c r="K53" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="K53" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="L53" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -7077,67 +7195,72 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N53" s="8" t="inlineStr">
+      <c r="N53" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O53" s="8" t="inlineStr">
         <is>
           <t>(輸入主体)</t>
         </is>
       </c>
-      <c r="O53" s="17" t="inlineStr">
+      <c r="P53" s="18" t="inlineStr">
         <is>
           <t>https://benjaminmoore.jp/</t>
         </is>
       </c>
-      <c r="P53" s="7" t="inlineStr">
+      <c r="Q53" s="7" t="inlineStr">
         <is>
           <t>本社問合せ</t>
         </is>
       </c>
-      <c r="Q53" s="14" t="inlineStr">
+      <c r="R53" s="15" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="R53" s="8" t="inlineStr">
+      <c r="S53" s="8" t="inlineStr">
         <is>
           <t>建築水性塗料の調色・小口販売</t>
         </is>
       </c>
-      <c r="S53" s="8" t="inlineStr">
+      <c r="T53" s="8" t="inlineStr">
         <is>
           <t>米国の調色機普及・小口運用</t>
         </is>
       </c>
-      <c r="T53" s="25" t="n">
+      <c r="U53" s="27" t="n">
         <v>55</v>
       </c>
-      <c r="U53" s="8" t="inlineStr">
+      <c r="V53" s="8" t="inlineStr">
         <is>
           <t>輸入代理店経由</t>
         </is>
       </c>
-      <c r="V53" s="8" t="inlineStr">
+      <c r="W53" s="8" t="inlineStr">
         <is>
           <t>建材専門店経由</t>
         </is>
       </c>
-      <c r="W53" s="8" t="inlineStr">
+      <c r="X53" s="8" t="inlineStr">
         <is>
           <t>輸入主体で国内製造は限定的</t>
         </is>
       </c>
-      <c r="X53" s="14" t="inlineStr"/>
-      <c r="Y53" s="7" t="inlineStr"/>
-      <c r="Z53" s="8" t="inlineStr">
+      <c r="Y53" s="15" t="inlineStr"/>
+      <c r="Z53" s="7" t="inlineStr"/>
+      <c r="AA53" s="8" t="inlineStr">
         <is>
           <t>輸入塗料の参考</t>
         </is>
       </c>
     </row>
     <row r="54" ht="68" customHeight="1">
-      <c r="A54" s="27" t="n">
+      <c r="A54" s="29" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="27" t="inlineStr">
+      <c r="B54" s="29" t="inlineStr">
         <is>
           <t>機能・特殊</t>
         </is>
@@ -7147,46 +7270,42 @@
           <t>ターナー色彩</t>
         </is>
       </c>
-      <c r="D54" s="7" t="inlineStr">
+      <c r="D54" s="14" t="inlineStr"/>
+      <c r="E54" s="7" t="inlineStr">
         <is>
           <t>大阪府吹田市</t>
         </is>
       </c>
-      <c r="E54" s="14" t="inlineStr">
+      <c r="F54" s="15" t="inlineStr">
         <is>
           <t>非上場</t>
         </is>
       </c>
-      <c r="F54" s="7" t="inlineStr">
+      <c r="G54" s="7" t="inlineStr">
         <is>
           <t>約60億円規模(推定)</t>
         </is>
       </c>
-      <c r="G54" s="7" t="inlineStr">
+      <c r="H54" s="7" t="inlineStr">
         <is>
           <t>約200人</t>
         </is>
       </c>
-      <c r="H54" s="8" t="inlineStr">
+      <c r="I54" s="8" t="inlineStr">
         <is>
           <t>アクリル絵具・アート用塗料・建築仕上げ</t>
         </is>
       </c>
-      <c r="I54" s="15" t="inlineStr">
+      <c r="J54" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="J54" s="15" t="inlineStr">
+      <c r="K54" s="16" t="inlineStr">
         <is>
           <t>◎</t>
         </is>
       </c>
-      <c r="K54" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="L54" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -7197,119 +7316,124 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N54" s="8" t="inlineStr">
+      <c r="N54" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O54" s="8" t="inlineStr">
         <is>
           <t>大阪・吹田</t>
         </is>
       </c>
-      <c r="O54" s="17" t="inlineStr">
+      <c r="P54" s="18" t="inlineStr">
         <is>
           <t>https://www.turner.co.jp/</t>
         </is>
       </c>
-      <c r="P54" s="7" t="inlineStr">
+      <c r="Q54" s="7" t="inlineStr">
         <is>
           <t>本社問合せ</t>
         </is>
       </c>
-      <c r="Q54" s="14" t="inlineStr">
+      <c r="R54" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="R54" s="8" t="inlineStr">
+      <c r="S54" s="8" t="inlineStr">
         <is>
           <t>アクリル系塗料の③④⑤⑧(チューブ・ボトル充填)</t>
         </is>
       </c>
-      <c r="S54" s="8" t="inlineStr">
+      <c r="T54" s="8" t="inlineStr">
         <is>
           <t>小ロット多品種(色数)管理、特殊容器充填</t>
         </is>
       </c>
-      <c r="T54" s="25" t="n">
+      <c r="U54" s="27" t="n">
         <v>60</v>
       </c>
-      <c r="U54" s="8" t="inlineStr">
+      <c r="V54" s="8" t="inlineStr">
         <is>
           <t>営業窓口</t>
         </is>
       </c>
-      <c r="V54" s="8" t="inlineStr">
+      <c r="W54" s="8" t="inlineStr">
         <is>
           <t>画材・建材販売店経由</t>
         </is>
       </c>
-      <c r="W54" s="8" t="inlineStr">
+      <c r="X54" s="8" t="inlineStr">
         <is>
           <t>アート用と建築用の両方を持つ特殊性</t>
         </is>
       </c>
-      <c r="X54" s="14" t="inlineStr"/>
-      <c r="Y54" s="7" t="inlineStr"/>
-      <c r="Z54" s="8" t="inlineStr">
+      <c r="Y54" s="15" t="inlineStr"/>
+      <c r="Z54" s="7" t="inlineStr"/>
+      <c r="AA54" s="8" t="inlineStr">
         <is>
           <t>多品種小ロットの極端例</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:Z54"/>
+  <autoFilter ref="A4:AA54"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:Z1"/>
-    <mergeCell ref="A2:Z2"/>
+    <mergeCell ref="A1:AA1"/>
+    <mergeCell ref="A2:AA2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P25" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P28" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P29" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P30" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P33" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P37" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P38" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P42" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P43" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P44" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P45" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P46" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P47" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P48" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P49" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P50" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P51" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P52" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P53" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P54" r:id="rId50"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -7361,7 +7485,7 @@
           <t>カバレッジ (製品タイプ網羅性)</t>
         </is>
       </c>
-      <c r="C5" s="33" t="n">
+      <c r="C5" s="35" t="n">
         <v>30</v>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -7376,7 +7500,7 @@
           <t>規模・代表性</t>
         </is>
       </c>
-      <c r="C6" s="33" t="n">
+      <c r="C6" s="35" t="n">
         <v>20</v>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -7391,7 +7515,7 @@
           <t>公開度 (一次情報の取りやすさ)</t>
         </is>
       </c>
-      <c r="C7" s="33" t="n">
+      <c r="C7" s="35" t="n">
         <v>20</v>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -7406,7 +7530,7 @@
           <t>アクセス容易性</t>
         </is>
       </c>
-      <c r="C8" s="33" t="n">
+      <c r="C8" s="35" t="n">
         <v>15</v>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -7421,7 +7545,7 @@
           <t>専門特化価値</t>
         </is>
       </c>
-      <c r="C9" s="33" t="n">
+      <c r="C9" s="35" t="n">
         <v>15</v>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -7436,10 +7560,10 @@
           <t>合計</t>
         </is>
       </c>
-      <c r="C10" s="34" t="n">
+      <c r="C10" s="36" t="n">
         <v>100</v>
       </c>
-      <c r="D10" s="35" t="inlineStr">
+      <c r="D10" s="37" t="inlineStr">
         <is>
           <t>全社のスコアを合算して並び替え、上位から打診計画を作成</t>
         </is>
@@ -7455,68 +7579,68 @@
       <c r="D12" s="5" t="n"/>
     </row>
     <row r="13" ht="25" customHeight="1">
-      <c r="B13" s="36" t="inlineStr">
+      <c r="B13" s="38" t="inlineStr">
         <is>
           <t>85〜100点</t>
         </is>
       </c>
-      <c r="C13" s="37" t="inlineStr">
+      <c r="C13" s="39" t="inlineStr">
         <is>
           <t>S: 最優先 (まず着手)</t>
         </is>
       </c>
-      <c r="D13" s="37" t="inlineStr">
+      <c r="D13" s="39" t="inlineStr">
         <is>
           <t>業界平均/標準化に最も影響大</t>
         </is>
       </c>
     </row>
     <row r="14" ht="25" customHeight="1">
-      <c r="B14" s="38" t="inlineStr">
+      <c r="B14" s="40" t="inlineStr">
         <is>
           <t>75〜84点</t>
         </is>
       </c>
-      <c r="C14" s="39" t="inlineStr">
+      <c r="C14" s="41" t="inlineStr">
         <is>
           <t>A: 重点候補</t>
         </is>
       </c>
-      <c r="D14" s="39" t="inlineStr">
+      <c r="D14" s="41" t="inlineStr">
         <is>
           <t>代表性ある中堅・特化メーカー</t>
         </is>
       </c>
     </row>
     <row r="15" ht="25" customHeight="1">
-      <c r="B15" s="40" t="inlineStr">
+      <c r="B15" s="42" t="inlineStr">
         <is>
           <t>65〜74点</t>
         </is>
       </c>
-      <c r="C15" s="41" t="inlineStr">
+      <c r="C15" s="43" t="inlineStr">
         <is>
           <t>B: 補強候補</t>
         </is>
       </c>
-      <c r="D15" s="41" t="inlineStr">
+      <c r="D15" s="43" t="inlineStr">
         <is>
           <t>他で取れない補強情報を期待</t>
         </is>
       </c>
     </row>
     <row r="16" ht="25" customHeight="1">
-      <c r="B16" s="42" t="inlineStr">
+      <c r="B16" s="44" t="inlineStr">
         <is>
           <t>〜64点</t>
         </is>
       </c>
-      <c r="C16" s="43" t="inlineStr">
+      <c r="C16" s="45" t="inlineStr">
         <is>
           <t>C: 補完 (必要に応じて)</t>
         </is>
       </c>
-      <c r="D16" s="43" t="inlineStr">
+      <c r="D16" s="45" t="inlineStr">
         <is>
           <t>他社で代替可能ならスキップも可</t>
         </is>
@@ -7608,400 +7732,400 @@
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="B6" s="44" t="inlineStr">
+      <c r="B6" s="46" t="inlineStr">
         <is>
           <t>大手総合</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>◎2 / ○0</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>◎2 / ○0</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>◎1 / ○1</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>◎2 / ○0</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>◎0 / ○2</t>
         </is>
       </c>
-      <c r="H6" s="33" t="n">
+      <c r="H6" s="35" t="n">
         <v>2</v>
       </c>
       <c r="I6" s="7" t="inlineStr"/>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="B7" s="45" t="inlineStr">
+      <c r="B7" s="47" t="inlineStr">
         <is>
           <t>中堅総合</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>◎6 / ○2</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>◎1 / ○7</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>◎1 / ○1</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>◎0 / ○1</t>
         </is>
       </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>◎0 / ○1</t>
         </is>
       </c>
-      <c r="H7" s="33" t="n">
+      <c r="H7" s="35" t="n">
         <v>8</v>
       </c>
       <c r="I7" s="7" t="inlineStr"/>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="B8" s="46" t="inlineStr">
+      <c r="B8" s="48" t="inlineStr">
         <is>
           <t>自動車補修</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>◎1 / ○1</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" s="33" t="n">
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" s="35" t="n">
         <v>2</v>
       </c>
       <c r="I8" s="7" t="inlineStr"/>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="B9" s="47" t="inlineStr">
+      <c r="B9" s="49" t="inlineStr">
         <is>
           <t>建築・仕上塗材</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>◎2 / ○2</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>◎4 / ○1</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" s="33" t="n">
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" s="35" t="n">
         <v>5</v>
       </c>
       <c r="I9" s="7" t="inlineStr"/>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="B10" s="48" t="inlineStr">
+      <c r="B10" s="50" t="inlineStr">
         <is>
           <t>機能・特殊</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>◎6 / ○1</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>◎1 / ○4</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="15" t="inlineStr">
         <is>
           <t>◎1 / ○1</t>
         </is>
       </c>
-      <c r="H10" s="33" t="n">
+      <c r="H10" s="35" t="n">
         <v>7</v>
       </c>
       <c r="I10" s="7" t="inlineStr"/>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="B11" s="49" t="inlineStr">
+      <c r="B11" s="51" t="inlineStr">
         <is>
           <t>UV・印刷インキ</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>◎0 / ○4</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t>◎0 / ○3</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
         <is>
           <t>◎0 / ○1</t>
         </is>
       </c>
-      <c r="G11" s="14" t="inlineStr">
+      <c r="G11" s="15" t="inlineStr">
         <is>
           <t>◎7 / ○2</t>
         </is>
       </c>
-      <c r="H11" s="33" t="n">
+      <c r="H11" s="35" t="n">
         <v>9</v>
       </c>
       <c r="I11" s="7" t="inlineStr"/>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="B12" s="50" t="inlineStr">
+      <c r="B12" s="52" t="inlineStr">
         <is>
           <t>DIY・小口</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>◎3 / ○0</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>◎3 / ○0</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" s="33" t="n">
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" s="35" t="n">
         <v>3</v>
       </c>
       <c r="I12" s="7" t="inlineStr"/>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="B13" s="51" t="inlineStr">
+      <c r="B13" s="53" t="inlineStr">
         <is>
           <t>日ペグループ</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>◎2 / ○2</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>◎0 / ○5</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="15" t="inlineStr">
         <is>
           <t>◎0 / ○2</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr">
+      <c r="F13" s="15" t="inlineStr">
         <is>
           <t>◎2 / ○0</t>
         </is>
       </c>
-      <c r="G13" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" s="33" t="n">
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" s="35" t="n">
         <v>5</v>
       </c>
       <c r="I13" s="7" t="inlineStr"/>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="B14" s="52" t="inlineStr">
+      <c r="B14" s="54" t="inlineStr">
         <is>
           <t>関ペグループ</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <t>◎1 / ○0</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D14" s="15" t="inlineStr">
         <is>
           <t>◎0 / ○1</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" s="33" t="n">
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" s="35" t="n">
         <v>1</v>
       </c>
       <c r="I14" s="7" t="inlineStr"/>
     </row>
     <row r="15" ht="26" customHeight="1">
-      <c r="B15" s="53" t="inlineStr">
+      <c r="B15" s="55" t="inlineStr">
         <is>
           <t>外資系・日本法人</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t>◎6 / ○1</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="15" t="inlineStr">
         <is>
           <t>◎4 / ○4</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="15" t="inlineStr">
         <is>
           <t>◎1 / ○3</t>
         </is>
       </c>
-      <c r="F15" s="14" t="inlineStr">
+      <c r="F15" s="15" t="inlineStr">
         <is>
           <t>◎2 / ○3</t>
         </is>
       </c>
-      <c r="G15" s="14" t="inlineStr">
+      <c r="G15" s="15" t="inlineStr">
         <is>
           <t>◎0 / ○2</t>
         </is>
       </c>
-      <c r="H15" s="33" t="n">
+      <c r="H15" s="35" t="n">
         <v>8</v>
       </c>
       <c r="I15" s="7" t="inlineStr"/>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="B16" s="54" t="inlineStr">
+      <c r="B16" s="56" t="inlineStr">
         <is>
           <t>全社合計</t>
         </is>
       </c>
-      <c r="C16" s="55" t="inlineStr">
+      <c r="C16" s="57" t="inlineStr">
         <is>
           <t>◎29 / ○13</t>
         </is>
       </c>
-      <c r="D16" s="55" t="inlineStr">
+      <c r="D16" s="57" t="inlineStr">
         <is>
           <t>◎15 / ○25</t>
         </is>
       </c>
-      <c r="E16" s="55" t="inlineStr">
+      <c r="E16" s="57" t="inlineStr">
         <is>
           <t>◎3 / ○7</t>
         </is>
       </c>
-      <c r="F16" s="55" t="inlineStr">
+      <c r="F16" s="57" t="inlineStr">
         <is>
           <t>◎6 / ○5</t>
         </is>
       </c>
-      <c r="G16" s="55" t="inlineStr">
+      <c r="G16" s="57" t="inlineStr">
         <is>
           <t>◎8 / ○8</t>
         </is>
       </c>
-      <c r="H16" s="56" t="n">
+      <c r="H16" s="58" t="n">
         <v>50</v>
       </c>
-      <c r="I16" s="35" t="inlineStr">
+      <c r="I16" s="37" t="inlineStr">
         <is>
           <t>◎○ 合計が 5 社未満の製品タイプは要補強</t>
         </is>
